--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9508D8E-A5D9-46CB-822B-CC23D98950FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280B3319-DFA9-4C9D-B144-4EBADE9FD115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-135" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$1:$D$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$1:$D$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="99">
   <si>
     <t>탭</t>
   </si>
@@ -418,10 +418,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>건물 비용 구성 및 예측, 실적 특이사항 기재</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>추이 상 특이점 기재 (증가)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -538,6 +534,71 @@
  - KB증권 200백만, 이촌회계법인 150백만
 특허처리비 105백만 초과 집행 (VVC 예산 누락 영향)</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건물 비용 구성 및 예측, 실적, 특이사항 기재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8월</t>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 2,976백만(120%), 본사 1,825백만(95%), 법인 1,152백만(204%)
+ - 법인 초과: HBR 회계감사수수료 720백만 집행 (1~7월 월 5~31백만)</t>
+  </si>
+  <si>
+    <t>8월 누계</t>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 21,186백만(100%), 본사 14,922백만(94%), 법인 6,264백만(121%)
+ - 예산 초과: HUMAX(공통) 141%(HBR 회계감사수수료, 합병 자문·평가 수수료 등) EVCS(국내) 108%
+ - 예산 미달: 건물 63%(1Q 94%, 2Q 41%, 3Q 51%), STB 95%, EVCS(해외) 90%</t>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 9,566백만(94%), 본사 7,166백만(92%), 법인 2,400백만(100%)
+국내/해외 비중: 1Q 국내 24%/해외 76%, 2Q 국내 29%/해외 71%, 3Q 국내 28%/해외 72%
+ - 개발 그룹 리소스 투입 변화: 해외→국내</t>
+  </si>
+  <si>
+    <t>[지급수수료]
+외주개발용역비 누계 229백만(집행률 30%) — 예산 대비 523백만 미달 (New Aura/iWedia SW이슈로 지연)
+Charter Legal fee/B&amp;M Legal fee 8월 79백만 추가 집행 (누계 206백만, 소송 재개)</t>
+  </si>
+  <si>
+    <t>[인건비]
+주식보상비용 250백만 집행 (예산 외, 일회성)
+[지급수수료]
+8월 HBR 회계감사수수료 720백만 집행
+ - 1~7월 월 5~31백만 대비 급증 — 성격 확인 필요
+합병 자문·평가 수수료 누계 482백만 집행 (7월 350백만, 8월 131백만)
+특허처리비 104백만 초과 집행 (VVC 예산 누락 영향)</t>
+  </si>
+  <si>
+    <t>1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만
+ - 4월: 한화 임대차계약 체결로 구조 변경
+ - 7월: 티맥스수내타워 관리비 집행 시작 · 8월 동일 구조 유지
+8월 1.5억: 건물관리수수료 0.59억, 임차료 0.45억, 감가상각비 0.4억
+ - 용인 0.8억(총 0.9억): 감가상각비 0.4억(총 0.45억), 건물관리수수료 0.27억(총 0.32억), 수도광열비 0.05억(총 0.08억), 보험료 0.06억(총 0.06억)
+ - 분당 0.8억(총 2.5억): 임차료 0.45억(총 1.44억), 수광비 0.01억(총 0.03억: 챔버, 카페), 건물관리수수료 0.01억(총 0.4억: 관리비 0.59억 - 실비수입 0.2억), 건물관리수수료(티맥스) 0.3억(총 0.58억)</t>
+  </si>
+  <si>
+    <t>4월, 5월 트렌드 왜곡
+ - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
+1~5월 평균 476백만 대비 6월 60백만, 7월 45백만 초과 · 8월 66백만 미달
+ - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만, 8월 79백만 집행 (누계 206백만)</t>
+  </si>
+  <si>
+    <t>1월, 3월, 5월, 7월, 8월 일회성 증가
+ - 1월: 26년 외부감사 착수금 200백만
+ - 3월, 5월: 주식보상비용 3월 34백만, 5월 216백만
+ - 7월: 합병 자문·평가 수수료 350백만 (KB증권, 이촌회계법인)
+ - 8월: HBR 회계감사수수료 720백만, 합병 자문 수수료 131백만
+1~6월 평균 611백만 대비 7월 269백만, 8월 747백만 초과</t>
+  </si>
+  <si>
+    <t>계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만
+ - 4월~: 분당 감가상각비 163백만 → 분당 임차료 월 45백만
+ - 7월~: 티맥스수내타워 임대차 관리비 29백만(총 58백만) 신규 반영</t>
   </si>
 </sst>
 </file>
@@ -696,7 +757,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -769,6 +830,15 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -798,7 +868,7 @@
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>98</xdr:row>
+      <xdr:row>107</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2396,7 +2466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}">
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
@@ -2666,7 +2736,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>4</v>
       </c>
@@ -2744,7 +2814,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>4</v>
       </c>
@@ -2849,7 +2919,7 @@
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E34" s="13" t="s">
         <v>65</v>
@@ -2889,7 +2959,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="115.5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="99" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>6</v>
       </c>
@@ -2900,10 +2970,10 @@
         <v>9</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="33" x14ac:dyDescent="0.3">
@@ -2920,7 +2990,7 @@
         <v>54</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="66" x14ac:dyDescent="0.3">
@@ -2937,7 +3007,7 @@
         <v>57</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="33" x14ac:dyDescent="0.3">
@@ -2954,7 +3024,7 @@
         <v>56</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="33" x14ac:dyDescent="0.3">
@@ -2968,10 +3038,10 @@
         <v>9</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -2979,14 +3049,14 @@
         <v>4</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C42" s="14"/>
       <c r="D42" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E42" s="13" t="s">
         <v>72</v>
-      </c>
-      <c r="E42" s="13" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
@@ -2994,14 +3064,14 @@
         <v>4</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
@@ -3009,14 +3079,14 @@
         <v>5</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C44" s="14"/>
       <c r="D44" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E44" s="13" t="s">
         <v>75</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
@@ -3024,16 +3094,16 @@
         <v>6</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C45" s="14" t="s">
         <v>7</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="99" x14ac:dyDescent="0.3">
@@ -3041,16 +3111,16 @@
         <v>6</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C46" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="132" x14ac:dyDescent="0.3">
@@ -3058,16 +3128,16 @@
         <v>6</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C47" s="14" t="s">
         <v>9</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="66" x14ac:dyDescent="0.3">
@@ -3075,16 +3145,16 @@
         <v>62</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C48" s="14" t="s">
         <v>7</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
@@ -3092,16 +3162,16 @@
         <v>62</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C49" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
@@ -3109,83 +3179,254 @@
         <v>62</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C50" s="14" t="s">
         <v>9</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A51" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" s="25"/>
+      <c r="D51" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E51" s="24" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A52" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C52" s="25"/>
+      <c r="D52" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E52" s="24" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="99" x14ac:dyDescent="0.3">
+      <c r="A53" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C53" s="25"/>
+      <c r="D53" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E53" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A54" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C54" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E54" s="24" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="A55" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C55" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E55" s="24" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="132" x14ac:dyDescent="0.3">
+      <c r="A56" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B56" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C56" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="E56" s="24" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+      <c r="A57" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B57" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C57" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="E57" s="24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="99" x14ac:dyDescent="0.3">
+      <c r="A58" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C58" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E58" s="24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A59" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B59" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C59" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E59" s="24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="18"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="19"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="11" t="s">
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="19"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B52" s="18"/>
-      <c r="C52" s="18"/>
-      <c r="D52" s="20"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="22"/>
-      <c r="I52" s="22"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E53" s="21"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="22"/>
-      <c r="H53" s="22"/>
-      <c r="I53" s="22"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E54" s="21"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="22"/>
-      <c r="H54" s="22"/>
-      <c r="I54" s="22"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E55" s="21"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="22"/>
-      <c r="H55" s="22"/>
-      <c r="I55" s="22"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E56" s="21"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="22"/>
-      <c r="H56" s="22"/>
-      <c r="I56" s="22"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E57" s="21"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="22"/>
-      <c r="H57" s="22"/>
-      <c r="I57" s="22"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E58" s="21"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
-      <c r="H58" s="22"/>
-      <c r="I58" s="22"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="20"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="22"/>
+      <c r="I61" s="22"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" s="18"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
+      <c r="H62" s="22"/>
+      <c r="I62" s="22"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A63" s="18"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="19"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A64" s="18"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="22"/>
+      <c r="H64" s="22"/>
+      <c r="I64" s="22"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="22"/>
+      <c r="H65" s="22"/>
+      <c r="I65" s="22"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" s="18"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="19"/>
+      <c r="E66" s="21"/>
+      <c r="F66" s="22"/>
+      <c r="G66" s="22"/>
+      <c r="H66" s="22"/>
+      <c r="I66" s="22"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" s="18"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="19"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D52" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}"/>
+  <autoFilter ref="A1:D61" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280B3319-DFA9-4C9D-B144-4EBADE9FD115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{307B4033-51D7-4276-8FB8-AC963595473D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -550,16 +550,6 @@
     <t>8월 누계</t>
   </si>
   <si>
-    <t>예산 대비 실적 집행률: 합계 21,186백만(100%), 본사 14,922백만(94%), 법인 6,264백만(121%)
- - 예산 초과: HUMAX(공통) 141%(HBR 회계감사수수료, 합병 자문·평가 수수료 등) EVCS(국내) 108%
- - 예산 미달: 건물 63%(1Q 94%, 2Q 41%, 3Q 51%), STB 95%, EVCS(해외) 90%</t>
-  </si>
-  <si>
-    <t>예산 대비 실적 집행률: 합계 9,566백만(94%), 본사 7,166백만(92%), 법인 2,400백만(100%)
-국내/해외 비중: 1Q 국내 24%/해외 76%, 2Q 국내 29%/해외 71%, 3Q 국내 28%/해외 72%
- - 개발 그룹 리소스 투입 변화: 해외→국내</t>
-  </si>
-  <si>
     <t>[지급수수료]
 외주개발용역비 누계 229백만(집행률 30%) — 예산 대비 523백만 미달 (New Aura/iWedia SW이슈로 지연)
 Charter Legal fee/B&amp;M Legal fee 8월 79백만 추가 집행 (누계 206백만, 소송 재개)</t>
@@ -599,6 +589,18 @@
     <t>계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만
  - 4월~: 분당 감가상각비 163백만 → 분당 임차료 월 45백만
  - 7월~: 티맥스수내타워 임대차 관리비 29백만(총 58백만) 신규 반영</t>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 21,186백만(100%), 본사 14,922백만(94%), 법인 6,264백만(121%)
+ - 예산 초과: HUMAX(공통) 141%(HBR 회계감사수수료, 합병 자문·평가 수수료 등) EVCS(국내) 108%
+ - 예산 미달: 건물 63%(1Q 94%, 2Q 41%, 3Q(7~8월) 51%), STB 95%, EVCS(해외) 90%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 9,566백만(94%), 본사 7,166백만(92%), 법인 2,400백만(100%)
+국내/해외 비중: 1Q 국내 24%/해외 76%, 2Q 국내 29%/해외 71%, 3Q(7~8월) 국내 28%/해외 72%
+ - 개발 그룹 리소스 투입 변화: 해외→국내</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3215,7 +3217,7 @@
       </c>
       <c r="C52" s="25"/>
       <c r="D52" s="8" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E52" s="24" t="s">
         <v>72</v>
@@ -3230,7 +3232,7 @@
       </c>
       <c r="C53" s="25"/>
       <c r="D53" s="8" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E53" s="24" t="s">
         <v>75</v>
@@ -3247,7 +3249,7 @@
         <v>7</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E54" s="24" t="s">
         <v>76</v>
@@ -3264,7 +3266,7 @@
         <v>8</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E55" s="24" t="s">
         <v>76</v>
@@ -3281,7 +3283,7 @@
         <v>9</v>
       </c>
       <c r="D56" s="26" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E56" s="24" t="s">
         <v>77</v>
@@ -3298,7 +3300,7 @@
         <v>7</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E57" s="24" t="s">
         <v>78</v>
@@ -3315,7 +3317,7 @@
         <v>8</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E58" s="24" t="s">
         <v>78</v>
@@ -3332,7 +3334,7 @@
         <v>9</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E59" s="24" t="s">
         <v>78</v>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{307B4033-51D7-4276-8FB8-AC963595473D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98132EA1-C71E-43BC-8247-51F54A768E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -543,25 +543,12 @@
     <t>8월</t>
   </si>
   <si>
-    <t>예산 대비 실적 집행률: 합계 2,976백만(120%), 본사 1,825백만(95%), 법인 1,152백만(204%)
- - 법인 초과: HBR 회계감사수수료 720백만 집행 (1~7월 월 5~31백만)</t>
-  </si>
-  <si>
     <t>8월 누계</t>
   </si>
   <si>
     <t>[지급수수료]
 외주개발용역비 누계 229백만(집행률 30%) — 예산 대비 523백만 미달 (New Aura/iWedia SW이슈로 지연)
 Charter Legal fee/B&amp;M Legal fee 8월 79백만 추가 집행 (누계 206백만, 소송 재개)</t>
-  </si>
-  <si>
-    <t>[인건비]
-주식보상비용 250백만 집행 (예산 외, 일회성)
-[지급수수료]
-8월 HBR 회계감사수수료 720백만 집행
- - 1~7월 월 5~31백만 대비 급증 — 성격 확인 필요
-합병 자문·평가 수수료 누계 482백만 집행 (7월 350백만, 8월 131백만)
-특허처리비 104백만 초과 집행 (VVC 예산 누락 영향)</t>
   </si>
   <si>
     <t>1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만
@@ -578,28 +565,44 @@
  - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만, 8월 79백만 집행 (누계 206백만)</t>
   </si>
   <si>
+    <t>계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만
+ - 4월~: 분당 감가상각비 163백만 → 분당 임차료 월 45백만
+ - 7월~: 티맥스수내타워 임대차 관리비 29백만(총 58백만) 신규 반영</t>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 9,566백만(94%), 본사 7,166백만(92%), 법인 2,400백만(100%)
+국내/해외 비중: 1Q 국내 24%/해외 76%, 2Q 국내 29%/해외 71%, 3Q(7~8월) 국내 28%/해외 72%
+ - 개발 그룹 리소스 투입 변화: 해외→국내</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 2,976백만(120%), 본사 1,825백만(95%), 법인 1,152백만(204%)
+ - 법인 초과: HBR 신용거래 수수료 703백만 집행 (회계감사수수료 계정으로 기표)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 21,186백만(100%), 본사 14,922백만(94%), 법인 6,264백만(121%)
+ - 예산 초과: HUMAX(공통) 141%(HBR 신용거래 수수료, 합병 자문·평가 수수료 등) EVCS(국내) 108%
+ - 예산 미달: 건물 63%(1Q 94%, 2Q 41%, 3Q(7~8월) 51%), STB 95%, EVCS(해외) 90%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[인건비]
+주식보상비용 250백만 집행 (예산 외, 일회성)
+[지급수수료]
+8월 HBR 신용거래 수수료 703백만 집행 (회계감사수수료 계정으로 기표)
+ - Artur 555백만, Fair Price 103백만(수수료율 0.85%), CTJ Administrative Services 45백만
+합병 자문·평가 수수료 누계 482백만 집행 (7월 350백만, 8월 131백만)
+특허처리비 104백만 초과 집행 (VVC 예산 누락 영향)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>1월, 3월, 5월, 7월, 8월 일회성 증가
  - 1월: 26년 외부감사 착수금 200백만
  - 3월, 5월: 주식보상비용 3월 34백만, 5월 216백만
  - 7월: 합병 자문·평가 수수료 350백만 (KB증권, 이촌회계법인)
- - 8월: HBR 회계감사수수료 720백만, 합병 자문 수수료 131백만
+ - 8월: HBR 신용거래 수수료 703백만, 합병 자문 수수료 131백만
 1~6월 평균 611백만 대비 7월 269백만, 8월 747백만 초과</t>
-  </si>
-  <si>
-    <t>계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만
- - 4월~: 분당 감가상각비 163백만 → 분당 임차료 월 45백만
- - 7월~: 티맥스수내타워 임대차 관리비 29백만(총 58백만) 신규 반영</t>
-  </si>
-  <si>
-    <t>예산 대비 실적 집행률: 합계 21,186백만(100%), 본사 14,922백만(94%), 법인 6,264백만(121%)
- - 예산 초과: HUMAX(공통) 141%(HBR 회계감사수수료, 합병 자문·평가 수수료 등) EVCS(국내) 108%
- - 예산 미달: 건물 63%(1Q 94%, 2Q 41%, 3Q(7~8월) 51%), STB 95%, EVCS(해외) 90%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>예산 대비 실적 집행률: 합계 9,566백만(94%), 본사 7,166백만(92%), 법인 2,400백만(100%)
-국내/해외 비중: 1Q 국내 24%/해외 76%, 2Q 국내 29%/해외 71%, 3Q(7~8월) 국내 28%/해외 72%
- - 개발 그룹 리소스 투입 변화: 해외→국내</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -856,1319 +859,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{523023D9-85E9-479C-A4E0-221935FF4431}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15373350" y="447675"/>
-          <a:ext cx="4391025" cy="16182975"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFE5"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
-            <a:t>1. Humax</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
-            <a:t>합계</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
-            <a:t>.sheet</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
-            <a:t>당월</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000"/>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
-            <a:t>당월 누계</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000"/>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
-            <a:t>2. EVCS</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
-            <a:t>사업부</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
-            <a:t>.sheet</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
-            <a:t>- </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
-            <a:t>3. Humax</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1"/>
-            <a:t>합계</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
-            <a:t>_</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1"/>
-            <a:t>상세</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
-            <a:t>.sheet</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
-            <a:t>-</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>예산 대비 큰 폭으로 초과</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>, </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>미달 인 경우 → </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>Appendix D</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>- </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>전월 대비 큰 폭으로 증가</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>, </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>감소 한 경우 → 클로드 명령</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1"/>
-            <a:t>▶ </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
-            <a:t>STB</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
-            <a:t>[Staff]</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Charter Legal fee/B&amp;M</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> 6</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>월 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>71</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>백만 집행 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>(</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>예산 외</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>- 26</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>년 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>3</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>월 소송 제기로 올해 비용 지속 예상</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1" baseline="0"/>
-            <a:t>[Media]</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>New</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> Aura/iWedia </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>외주개발용역비 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>6</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>월 누계 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>5.18</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>억원 미집행</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> - SW</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>이슈로 용역비 집행 지연</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>, 2H </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>비용 협상 시도 예정</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>STB License Fee/Nagra </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>조정 시기 오류로 인한 트렌드 왜곡</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>- 4</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>월 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>84</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>백만</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>, 5</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>월 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>-84</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>백만</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>(4</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>월에 기표되었어야함</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1" baseline="0"/>
-            <a:t>[SCM]</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
-            <a:t>삼계리 편성 오류</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
-            <a:t>:</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>매월 감가상각비 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>+6.8</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>백만</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>, </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>임차료 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>-18</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>백만</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>- </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>임차료 제외 후 감가상각비 사용권 자산 반영중 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>(</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>월 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>-11</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>백만</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1" baseline="0"/>
-            <a:t>[HUK]</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Bonus  +1.5</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>억</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>(2</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>억 집행</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>/</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>예산 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>0.5</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>억</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>): STB</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>  +0.2</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>억</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>, EVCS +1.3</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>억</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>리소스 투입률 변동 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>STB</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>↑</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>(New Aura </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>품질이슈</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>) EVCS</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>↓ 으로 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>2Q STB </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>비용 부담 증가</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
-            <a:t>Victor </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
-            <a:t>용역비</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
-            <a:t>/TSG 6</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
-            <a:t>월 누계 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
-            <a:t>+71</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
-            <a:t>백만</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
-            <a:t>(</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
-            <a:t>월 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
-            <a:t>11.8</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
-            <a:t>백만</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
-            <a:t>/</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
-            <a:t>예산 사업그룹</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
-            <a:t>): STB +16</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
-            <a:t>백만</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
-            <a:t>, EVCS +55</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
-            <a:t>백만</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
-            <a:t>[HJP]</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>인건비 외 경비 집행률 저조</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>:</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>광고선전비</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>, </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>여비교통비</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>, </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>회의비</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>, </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>접대비 등</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>5</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>월 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>1</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>명 퇴사로 인건비 예산 대비 감소 지속</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1" baseline="0"/>
-            <a:t>[HUG]</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0" baseline="0"/>
-            <a:t>5</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0" baseline="0"/>
-            <a:t>월 부터 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0" baseline="0"/>
-            <a:t>Fleetup </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0" baseline="0"/>
-            <a:t>비용 부담</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" b="0" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>지급수수료 초과로 예산 대비 초과 집행</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>- Marie </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>용역비 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>(</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>예산 외</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>): 2Q 15</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>백만</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>- KWS </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>용역비 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>(</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>예산 외</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>): 1</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>월 성과급 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>18</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>백만</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>, 2Q </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>용역비 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>12</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>백만</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>- </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>멕시코 장비반송료 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>1</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>월 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>9</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>백만 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>(</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
-            <a:t>예산 외</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
-            <a:t>)</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
-            <a:t>▶ [Humax(</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1"/>
-            <a:t>공통</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
-            <a:t>)]</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
-            <a:t>[Staff]</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>특허처리비 초과 집행 지속 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>6</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>월 누계 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>+105</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>백만 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>(VVC</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>예산 누락</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0"/>
-            <a:t>CEO </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0"/>
-            <a:t>주식보상비 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0"/>
-            <a:t>6</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0"/>
-            <a:t>월 누계 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0"/>
-            <a:t>2.5</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0"/>
-            <a:t>억원 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0"/>
-            <a:t>(</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0"/>
-            <a:t>예산 외</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0"/>
-            <a:t>)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
-            <a:t>[HBR]</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
-            <a:t>인원수 변동 없음</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
-            <a:t>, </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
-            <a:t>회계수수료 및 복리후생비 초과집행중</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
-            <a:t>회계수수료 예산 외 집행</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
-            <a:t> 6</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
-            <a:t>월 누계 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
-            <a:t>+50</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
-            <a:t>백만</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
-            <a:t>복리후생비 초과 집행중 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
-            <a:t>6</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
-            <a:t>월 누계 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
-            <a:t>+9</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
-            <a:t>백만</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
-            <a:t>[</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1"/>
-            <a:t>건물</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
-            <a:t>]</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>1~3</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>월 평균 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>278 → 4~6</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>월 평균 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>126</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>으로 사옥 이전에 따른 계단식 감소</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> 확인</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" b="0">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3202,7 +1892,7 @@
       </c>
       <c r="C51" s="25"/>
       <c r="D51" s="8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E51" s="24" t="s">
         <v>72</v>
@@ -3213,11 +1903,11 @@
         <v>4</v>
       </c>
       <c r="B52" s="25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C52" s="25"/>
       <c r="D52" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E52" s="24" t="s">
         <v>72</v>
@@ -3228,11 +1918,11 @@
         <v>5</v>
       </c>
       <c r="B53" s="25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C53" s="25"/>
       <c r="D53" s="8" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E53" s="24" t="s">
         <v>75</v>
@@ -3243,13 +1933,13 @@
         <v>6</v>
       </c>
       <c r="B54" s="25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C54" s="25" t="s">
         <v>7</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E54" s="24" t="s">
         <v>76</v>
@@ -3260,13 +1950,13 @@
         <v>6</v>
       </c>
       <c r="B55" s="25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C55" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E55" s="24" t="s">
         <v>76</v>
@@ -3277,13 +1967,13 @@
         <v>6</v>
       </c>
       <c r="B56" s="25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C56" s="25" t="s">
         <v>9</v>
       </c>
       <c r="D56" s="26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E56" s="24" t="s">
         <v>77</v>
@@ -3294,13 +1984,13 @@
         <v>62</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C57" s="25" t="s">
         <v>7</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E57" s="24" t="s">
         <v>78</v>
@@ -3311,13 +2001,13 @@
         <v>62</v>
       </c>
       <c r="B58" s="25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C58" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E58" s="24" t="s">
         <v>78</v>
@@ -3328,13 +2018,13 @@
         <v>62</v>
       </c>
       <c r="B59" s="25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C59" s="25" t="s">
         <v>9</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E59" s="24" t="s">
         <v>78</v>
@@ -3432,6 +2122,5 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98132EA1-C71E-43BC-8247-51F54A768E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83539EE2-C3D8-4C1A-AA21-630118B89CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -577,12 +577,12 @@
   </si>
   <si>
     <t>예산 대비 실적 집행률: 합계 2,976백만(120%), 본사 1,825백만(95%), 법인 1,152백만(204%)
- - 법인 초과: HBR 신용거래 수수료 703백만 집행 (회계감사수수료 계정으로 기표)</t>
+ - 법인 초과: HBR 지급수수료 703백만 집행 — 신용거래 수수료 658백만, 신규 대표자 선임 용역 수수료 45백만</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>예산 대비 실적 집행률: 합계 21,186백만(100%), 본사 14,922백만(94%), 법인 6,264백만(121%)
- - 예산 초과: HUMAX(공통) 141%(HBR 신용거래 수수료, 합병 자문·평가 수수료 등) EVCS(국내) 108%
+ - 예산 초과: HUMAX(공통) 141%(HBR 지급수수료, 합병 자문·평가 수수료 등) EVCS(국내) 108%
  - 예산 미달: 건물 63%(1Q 94%, 2Q 41%, 3Q(7~8월) 51%), STB 95%, EVCS(해외) 90%</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -590,8 +590,9 @@
     <t>[인건비]
 주식보상비용 250백만 집행 (예산 외, 일회성)
 [지급수수료]
-8월 HBR 신용거래 수수료 703백만 집행 (회계감사수수료 계정으로 기표)
- - Artur 555백만, Fair Price 103백만(수수료율 0.85%), CTJ Administrative Services 45백만
+8월 HBR 703백만 집행 (회계감사수수료 계정으로 기표)
+ - 신용거래 수수료 658백만: Artur 555백만, Fair Price 103백만(수수료율 0.85%)
+ - 용역 수수료 45백만: CTJ Administrative Services — 브라질 신규 대표자 선임 관련
 합병 자문·평가 수수료 누계 482백만 집행 (7월 350백만, 8월 131백만)
 특허처리비 104백만 초과 집행 (VVC 예산 누락 영향)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -601,7 +602,7 @@
  - 1월: 26년 외부감사 착수금 200백만
  - 3월, 5월: 주식보상비용 3월 34백만, 5월 216백만
  - 7월: 합병 자문·평가 수수료 350백만 (KB증권, 이촌회계법인)
- - 8월: HBR 신용거래 수수료 703백만, 합병 자문 수수료 131백만
+ - 8월: HBR 신용거래 수수료 658백만, 신규 대표자 선임 용역 수수료 45백만, 합병 자문 수수료 131백만
 1~6월 평균 611백만 대비 7월 269백만, 8월 747백만 초과</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1945,7 +1946,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="115.5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" ht="132" x14ac:dyDescent="0.3">
       <c r="A55" s="25" t="s">
         <v>6</v>
       </c>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83539EE2-C3D8-4C1A-AA21-630118B89CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9EBE0FD-70DB-4112-84F6-DFCA899738D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -602,7 +602,7 @@
  - 1월: 26년 외부감사 착수금 200백만
  - 3월, 5월: 주식보상비용 3월 34백만, 5월 216백만
  - 7월: 합병 자문·평가 수수료 350백만 (KB증권, 이촌회계법인)
- - 8월: HBR 신용거래 수수료 658백만, 신규 대표자 선임 용역 수수료 45백만, 합병 자문 수수료 131백만
+ - 8월: HBR 신용거래 수수료 658백만, HBR 신규 대표자 선임 용역 수수료 45백만, 홀딩스 합병 자문 수수료 131백만
 1~6월 평균 611백만 대비 7월 269백만, 8월 747백만 초과</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9EBE0FD-70DB-4112-84F6-DFCA899738D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8341DB91-B85A-45B6-86CB-AED5818F2F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="100">
   <si>
     <t>탭</t>
   </si>
@@ -598,11 +598,16 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1월, 3월, 5월, 7월, 8월 일회성 증가
+    <t xml:space="preserve">                                                          </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일회성 증가 항목
  - 1월: 26년 외부감사 착수금 200백만
  - 3월, 5월: 주식보상비용 3월 34백만, 5월 216백만
  - 7월: 합병 자문·평가 수수료 350백만 (KB증권, 이촌회계법인)
- - 8월: HBR 신용거래 수수료 658백만, HBR 신규 대표자 선임 용역 수수료 45백만, 홀딩스 합병 자문 수수료 131백만
+ - 8월: HBR Artur 세액공제 매각 중개수수료 650백만, HBR CTJ 법정 대표자 보수 54백만, 홀딩스 합병 자문 수수료 131백만
+         (참고) 계약서상 잔금 : HBR Artur 세액공제 매각 중개수수료 6.7억, HBR CTJ 법정 대표자 성공보수 45백만  
 1~6월 평균 611백만 대비 7월 269백만, 8월 747백만 초과</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -611,7 +616,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -702,6 +707,15 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -763,7 +777,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -845,12 +859,20 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF0000FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -860,6 +882,1131 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>158750</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>84667</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>4487333</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E6B206C-2B0E-474E-A77F-08F947C948F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="158750" y="41116250"/>
+          <a:ext cx="8128000" cy="4064000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="0000FF"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>▼상세 메모</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="0000FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="0000FF"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="0000FF"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>아래 내용은 담당자 참고용 상세 메모로 업데이트 시</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="0000FF"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="0000FF"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>지우지 말 것</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="0000FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>[HBR </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
+            <a:t>지급수수료</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>-  CTJ(Ciro) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
+            <a:t>신규 대표자 선임 용역 수수료</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>: 8</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>월 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>BRL 164k (45</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>백만</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>집행</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>법적 절차 종료 시 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>BRL 164k </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>추가 집행 예정</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>    *26.07.01~</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>청산완료까지 계약 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>/ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>세액공제 회수</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>법인 청산</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>법적 대표자 역할 수행</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" baseline="0"/>
+            <a:t>- Artur(Fair Price</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>사 대표자</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" baseline="0"/>
+            <a:t>) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>신용 거래 수수료</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" baseline="0"/>
+            <a:t>: </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>   *</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>세액공제 매각 중개 수수료 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>대출 수수료</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>X) / HBR</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>이 브라질 정부 대상으로 세금 소송을 진행중이며</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>승소시 돌려받을 세액공제 크레딧의 가치에 따라 요율을 적용하여 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>Frai Price</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>에 수수료를 지급하는 계약</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>   *</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>총 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>3</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>회차에 걸쳐 집행</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>: 1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>차 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>BRL 1.99M (5.4</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>억</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>)(8</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>월 집행</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>), </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>2</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>차 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>BRL 1.99M, 3</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>차 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>BRP 0.47M </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>; </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>총 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>BRL 4.44M </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>→ 재판진행에 따라 달라질 수 있으며 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>5</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>년 소요 예상됨 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>세액공제 크레딧 자체를 자산으로 보고 자산에 요율을 곱해서 수수료 산출</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t>1 BRL = 270 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>원</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>105834</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>517374</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>4840</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="13" name="그룹 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF136E2C-CC82-49EB-9186-A2550F841F7E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="222250" y="45582417"/>
+          <a:ext cx="13005707" cy="4344006"/>
+          <a:chOff x="179917" y="45603583"/>
+          <a:chExt cx="13005707" cy="4344006"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="9" name="그룹 8">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE7CDEA9-320F-408B-9C44-E720EFD70C4A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="179917" y="45603583"/>
+            <a:ext cx="13005707" cy="4344006"/>
+            <a:chOff x="264584" y="45550667"/>
+            <a:chExt cx="13005707" cy="4344006"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="4" name="그림 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF9FA254-263E-458E-AC80-17A3316F782C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="264584" y="45550667"/>
+              <a:ext cx="6439799" cy="4344006"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="6" name="TextBox 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFB765A3-C549-4AAC-B451-FBA55D88884B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4603751" y="45582417"/>
+              <a:ext cx="1936750" cy="349250"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+                <a:t>CTJ </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+                <a:t>대표자 선임 계약</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+                <a:t>용역</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+                <a:t>)</a:t>
+              </a:r>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="8" name="그룹 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82DA944C-13D8-4120-BFC1-EB170AC16F4A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="6773334" y="45614165"/>
+              <a:ext cx="6496957" cy="2071442"/>
+              <a:chOff x="6773334" y="45614165"/>
+              <a:chExt cx="6496957" cy="2071442"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="3" name="그림 2">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9FE7AEF-9B2A-4E87-9EED-87CAED95E014}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="6773334" y="45656499"/>
+                <a:ext cx="6496957" cy="2029108"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="7" name="TextBox 6">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E1CE6FF-5F03-4B3C-ABA7-404A4E06E4C1}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="9662584" y="45614165"/>
+                <a:ext cx="1936750" cy="635001"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+              <a:ln w="9525" cmpd="sng">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:shade val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+                  <a:t>Artur</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+                  <a:t> </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+                  <a:t>신용 거래 수수료 </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+                  <a:t>(</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US" sz="1100" baseline="0"/>
+                  <a:t>세액공제 소송 중개 수수료</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+                  <a:t>)</a:t>
+                </a:r>
+                <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="10" name="TextBox 9">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE2AA865-437A-46F9-862D-F6C225B78556}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="433920" y="46302083"/>
+            <a:ext cx="1280582" cy="349250"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="0000FF"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>→ </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="0000FF"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>26</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="0000FF"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>년 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="0000FF"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>8</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="0000FF"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>월 집행</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="11" name="TextBox 10">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20A580F5-52CA-4B33-AA1F-7098987F701E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="9503833" y="46407916"/>
+            <a:ext cx="1344083" cy="349250"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="0000FF"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>→ </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="0000FF"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>26</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="0000FF"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>년 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="0000FF"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>8</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="0000FF"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>월 집행</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>550334</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>21168</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>120492</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>149982</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="18" name="그룹 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1A86C80-5CA4-4D51-B5A8-F1D3AF8F2B25}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="13260917" y="45709418"/>
+          <a:ext cx="6449325" cy="5420481"/>
+          <a:chOff x="13260917" y="45497751"/>
+          <a:chExt cx="6449325" cy="5420481"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="16" name="그림 15">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDDC1630-1099-4580-9CB4-F47FA5C007AD}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="13260917" y="45497751"/>
+            <a:ext cx="6449325" cy="5420481"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="17" name="TextBox 16">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DEE2DE6-9FAA-4789-9C5D-FC0C976F7CE7}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="17526000" y="45508335"/>
+            <a:ext cx="2074333" cy="349252"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFF00"/>
+          </a:solidFill>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+              <a:t>8</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+              <a:t>월 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+              <a:t>HBR </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+              <a:t>지급수수료 증가사유</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1159,7 +2306,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}">
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
@@ -1997,7 +3144,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="99" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A58" s="25" t="s">
         <v>62</v>
       </c>
@@ -2008,7 +3155,7 @@
         <v>8</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E58" s="24" t="s">
         <v>78</v>
@@ -2118,10 +3265,17 @@
       <c r="H67" s="22"/>
       <c r="I67" s="22"/>
     </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="27"/>
+      <c r="D82" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D61" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8341DB91-B85A-45B6-86CB-AED5818F2F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833D0524-D2B9-4578-9011-107B9A53147B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -576,11 +576,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>예산 대비 실적 집행률: 합계 2,976백만(120%), 본사 1,825백만(95%), 법인 1,152백만(204%)
- - 법인 초과: HBR 지급수수료 703백만 집행 — 신용거래 수수료 658백만, 신규 대표자 선임 용역 수수료 45백만</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>예산 대비 실적 집행률: 합계 21,186백만(100%), 본사 14,922백만(94%), 법인 6,264백만(121%)
  - 예산 초과: HUMAX(공통) 141%(HBR 지급수수료, 합병 자문·평가 수수료 등) EVCS(국내) 108%
  - 예산 미달: 건물 63%(1Q 94%, 2Q 41%, 3Q(7~8월) 51%), STB 95%, EVCS(해외) 90%</t>
@@ -609,6 +604,11 @@
  - 8월: HBR Artur 세액공제 매각 중개수수료 650백만, HBR CTJ 법정 대표자 보수 54백만, 홀딩스 합병 자문 수수료 131백만
          (참고) 계약서상 잔금 : HBR Artur 세액공제 매각 중개수수료 6.7억, HBR CTJ 법정 대표자 성공보수 45백만  
 1~6월 평균 611백만 대비 7월 269백만, 8월 747백만 초과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 2,976백만(120%), 본사 1,825백만(95%), 법인 1,152백만(204%)
+ - 법인 초과: HBR 지급수수료 703백만 집행 — HBR Artur 세액공제 매각 중개수수료 650백만, HBR CTJ 법정 대표자 보수 54백만</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="C51" s="25"/>
       <c r="D51" s="8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E51" s="24" t="s">
         <v>72</v>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="C52" s="25"/>
       <c r="D52" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E52" s="24" t="s">
         <v>72</v>
@@ -3104,7 +3104,7 @@
         <v>8</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E55" s="24" t="s">
         <v>76</v>
@@ -3155,7 +3155,7 @@
         <v>8</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E58" s="24" t="s">
         <v>78</v>
@@ -3268,7 +3268,7 @@
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="27"/>
       <c r="D82" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833D0524-D2B9-4578-9011-107B9A53147B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404CAA66-DC12-4F07-AE2A-E20BC229EE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -582,17 +582,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[인건비]
-주식보상비용 250백만 집행 (예산 외, 일회성)
-[지급수수료]
-8월 HBR 703백만 집행 (회계감사수수료 계정으로 기표)
- - 신용거래 수수료 658백만: Artur 555백만, Fair Price 103백만(수수료율 0.85%)
- - 용역 수수료 45백만: CTJ Administrative Services — 브라질 신규 대표자 선임 관련
-합병 자문·평가 수수료 누계 482백만 집행 (7월 350백만, 8월 131백만)
-특허처리비 104백만 초과 집행 (VVC 예산 누락 영향)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">                                                          </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -609,6 +598,15 @@
   <si>
     <t>예산 대비 실적 집행률: 합계 2,976백만(120%), 본사 1,825백만(95%), 법인 1,152백만(204%)
  - 법인 초과: HBR 지급수수료 703백만 집행 — HBR Artur 세액공제 매각 중개수수료 650백만, HBR CTJ 법정 대표자 보수 54백만</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[인건비]
+주식보상비용 250백만 집행 (예산 외, 일회성)
+[지급수수료]
+8월 HBR 703백만 집행 (HBR Artur 세액공제 매각 중개수수료 650백만, HBR CTJ 법정 대표자 보수 54백만)
+합병 자문·평가 수수료 누계 482백만 집행 (7월 350백만, 8월 131백만)
+특허처리비 104백만 초과 집행 (VVC 예산 누락 영향)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1445,7 +1443,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="222250" y="45582417"/>
+          <a:off x="222250" y="45169667"/>
           <a:ext cx="13005707" cy="4344006"/>
           <a:chOff x="179917" y="45603583"/>
           <a:chExt cx="13005707" cy="4344006"/>
@@ -1900,7 +1898,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="13260917" y="45709418"/>
+          <a:off x="13260917" y="45296668"/>
           <a:ext cx="6449325" cy="5420481"/>
           <a:chOff x="13260917" y="45497751"/>
           <a:chExt cx="6449325" cy="5420481"/>
@@ -3040,7 +3038,7 @@
       </c>
       <c r="C51" s="25"/>
       <c r="D51" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E51" s="24" t="s">
         <v>72</v>
@@ -3093,7 +3091,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="132" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" ht="99" x14ac:dyDescent="0.3">
       <c r="A55" s="25" t="s">
         <v>6</v>
       </c>
@@ -3104,7 +3102,7 @@
         <v>8</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E55" s="24" t="s">
         <v>76</v>
@@ -3155,7 +3153,7 @@
         <v>8</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E58" s="24" t="s">
         <v>78</v>
@@ -3268,7 +3266,7 @@
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="27"/>
       <c r="D82" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404CAA66-DC12-4F07-AE2A-E20BC229EE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A33DC3-C4BB-4FC9-952A-508FA8BEF7E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -559,17 +559,6 @@
  - 분당 0.8억(총 2.5억): 임차료 0.45억(총 1.44억), 수광비 0.01억(총 0.03억: 챔버, 카페), 건물관리수수료 0.01억(총 0.4억: 관리비 0.59억 - 실비수입 0.2억), 건물관리수수료(티맥스) 0.3억(총 0.58억)</t>
   </si>
   <si>
-    <t>4월, 5월 트렌드 왜곡
- - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
-1~5월 평균 476백만 대비 6월 60백만, 7월 45백만 초과 · 8월 66백만 미달
- - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만, 8월 79백만 집행 (누계 206백만)</t>
-  </si>
-  <si>
-    <t>계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만
- - 4월~: 분당 감가상각비 163백만 → 분당 임차료 월 45백만
- - 7월~: 티맥스수내타워 임대차 관리비 29백만(총 58백만) 신규 반영</t>
-  </si>
-  <si>
     <t>예산 대비 실적 집행률: 합계 9,566백만(94%), 본사 7,166백만(92%), 법인 2,400백만(100%)
 국내/해외 비중: 1Q 국내 24%/해외 76%, 2Q 국내 29%/해외 71%, 3Q(7~8월) 국내 28%/해외 72%
  - 개발 그룹 리소스 투입 변화: 해외→국내</t>
@@ -583,16 +572,6 @@
   </si>
   <si>
     <t xml:space="preserve">                                                          </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>일회성 증가 항목
- - 1월: 26년 외부감사 착수금 200백만
- - 3월, 5월: 주식보상비용 3월 34백만, 5월 216백만
- - 7월: 합병 자문·평가 수수료 350백만 (KB증권, 이촌회계법인)
- - 8월: HBR Artur 세액공제 매각 중개수수료 650백만, HBR CTJ 법정 대표자 보수 54백만, 홀딩스 합병 자문 수수료 131백만
-         (참고) 계약서상 잔금 : HBR Artur 세액공제 매각 중개수수료 6.7억, HBR CTJ 법정 대표자 성공보수 45백만  
-1~6월 평균 611백만 대비 7월 269백만, 8월 747백만 초과</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -607,6 +586,30 @@
 8월 HBR 703백만 집행 (HBR Artur 세액공제 매각 중개수수료 650백만, HBR CTJ 법정 대표자 보수 54백만)
 합병 자문·평가 수수료 누계 482백만 집행 (7월 350백만, 8월 131백만)
 특허처리비 104백만 초과 집행 (VVC 예산 누락 영향)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만
+ - 4월~: 분당 감가상각비 163백만 → 분당 임차료 월 45백만
+ - 7월~: 티맥스수내타워 임대차 관리비 29백만(총 58백만) 신규 반영</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4월, 5월 트렌드 왜곡
+ - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
+1~5월 평균 476백만 대비 6월 60백만, 7월 45백만 초과 · 8월 66백만 미달
+ - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만, 8월 79백만 집행 (누계 206백만)
+ - HUS 8월 의료보험료 환급 -52백만, 유급휴가 충당금 회수 -28백만, 급여 -26백만 (2Q 7명 → 3Q 5명)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일회성 증가 항목
+ - 1월: 26년 외부감사 착수금 200백만
+ - 3월, 5월: 주식보상비용 3월 34백만, 5월 216백만
+ - 7월: 합병 자문·평가 수수료 350백만 (KB증권, 이촌회계법인)
+ - 8월: HBR Artur 세액공제 매각 중개수수료 650백만, HBR CTJ 법정 대표자 보수 54백만, 홀딩스 합병 자문 수수료 131백만
+(참고) 계약서상 잔금 : HBR Artur 세액공제 매각 중개수수료 6.7억, HBR CTJ 법정 대표자 성공보수 45백만, 홀딩스 합병 자문 수수료 1억(KB증권, 합병기일 후)
+1~6월 평균 611백만 대비 7월 269백만, 8월 747백만 초과</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1443,7 +1446,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="222250" y="45169667"/>
+          <a:off x="222250" y="45582417"/>
           <a:ext cx="13005707" cy="4344006"/>
           <a:chOff x="179917" y="45603583"/>
           <a:chExt cx="13005707" cy="4344006"/>
@@ -1898,7 +1901,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="13260917" y="45296668"/>
+          <a:off x="13260917" y="45709418"/>
           <a:ext cx="6449325" cy="5420481"/>
           <a:chOff x="13260917" y="45497751"/>
           <a:chExt cx="6449325" cy="5420481"/>
@@ -3038,7 +3041,7 @@
       </c>
       <c r="C51" s="25"/>
       <c r="D51" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E51" s="24" t="s">
         <v>72</v>
@@ -3053,7 +3056,7 @@
       </c>
       <c r="C52" s="25"/>
       <c r="D52" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E52" s="24" t="s">
         <v>72</v>
@@ -3068,7 +3071,7 @@
       </c>
       <c r="C53" s="25"/>
       <c r="D53" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E53" s="24" t="s">
         <v>75</v>
@@ -3102,7 +3105,7 @@
         <v>8</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E55" s="24" t="s">
         <v>76</v>
@@ -3125,7 +3128,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A57" s="25" t="s">
         <v>62</v>
       </c>
@@ -3136,13 +3139,13 @@
         <v>7</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E57" s="24" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="115.5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" ht="132" x14ac:dyDescent="0.3">
       <c r="A58" s="25" t="s">
         <v>62</v>
       </c>
@@ -3153,7 +3156,7 @@
         <v>8</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E58" s="24" t="s">
         <v>78</v>
@@ -3170,7 +3173,7 @@
         <v>9</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E59" s="24" t="s">
         <v>78</v>
@@ -3266,7 +3269,7 @@
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="27"/>
       <c r="D82" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A33DC3-C4BB-4FC9-952A-508FA8BEF7E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD24778-964E-4110-BC83-3312F89A134C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -607,8 +607,9 @@
  - 1월: 26년 외부감사 착수금 200백만
  - 3월, 5월: 주식보상비용 3월 34백만, 5월 216백만
  - 7월: 합병 자문·평가 수수료 350백만 (KB증권, 이촌회계법인)
+*(참고) 계약서상 잔금 : 홀딩스 합병 자문 수수료 1억 (KB증권, 합병기일 후)
  - 8월: HBR Artur 세액공제 매각 중개수수료 650백만, HBR CTJ 법정 대표자 보수 54백만, 홀딩스 합병 자문 수수료 131백만
-(참고) 계약서상 잔금 : HBR Artur 세액공제 매각 중개수수료 6.7억, HBR CTJ 법정 대표자 성공보수 45백만, 홀딩스 합병 자문 수수료 1억(KB증권, 합병기일 후)
+*(참고) 계약서상 잔금 : HBR Artur 세액공제 매각 중개수수료 6.7억, HBR CTJ 법정 대표자 성공보수 45백만
 1~6월 평균 611백만 대비 7월 269백만, 8월 747백만 초과</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD24778-964E-4110-BC83-3312F89A134C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0370E2F-4259-4BA7-B2E1-1F8A958F1694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -607,9 +607,9 @@
  - 1월: 26년 외부감사 착수금 200백만
  - 3월, 5월: 주식보상비용 3월 34백만, 5월 216백만
  - 7월: 합병 자문·평가 수수료 350백만 (KB증권, 이촌회계법인)
-*(참고) 계약서상 잔금 : 홀딩스 합병 자문 수수료 1억 (KB증권, 합병기일 후)
+*(참고) 잔금 1억 (KB증권, 합병기일 후)
  - 8월: HBR Artur 세액공제 매각 중개수수료 650백만, HBR CTJ 법정 대표자 보수 54백만, 홀딩스 합병 자문 수수료 131백만
-*(참고) 계약서상 잔금 : HBR Artur 세액공제 매각 중개수수료 6.7억, HBR CTJ 법정 대표자 성공보수 45백만
+*(참고) 잔금 Artur 670백만, CTJ 45백만
 1~6월 평균 611백만 대비 7월 269백만, 8월 747백만 초과</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0370E2F-4259-4BA7-B2E1-1F8A958F1694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A433989E-DB01-4FF6-823B-CB2AA37E267A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -108,51 +108,24 @@
     <t>4월 누계</t>
   </si>
   <si>
-    <t>- 당월 실적 2,818백만(집행률 88%) — 예산 대비 미달
-- 본사 2,020백만(집행률 83%) 미달 주도 · 법인 798백만(집행률 102%) 예산 수준
-- STB 493백만(집행률 49%) 최저 · HUMAX(공통) 760백만 — 외부감사 착수금 200백만 반영</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>- 누계 실적 1,233백만(집행률 100%) · 연간 예산의 8% — 1개월 경과 진도(8%) 부합
 - 국내 269백만 · 연간 예산의 8% — 첫 달, 추이 판단 불가
 - 해외 963백만 · 연간 예산의 9% — 인건비 720백만(58%)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>- 누계 실적 493백만(집행률 49%) — 예산 대비 521백만 미달
-- 예산 대비 Media그룹 -533백만(외주개발용역비 -509) — 미달의 대부분</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>- 누계 실적 760백만(집행률 122%) — 예산 대비 138백만 초과
 - 예산 대비 Staff부문 +138백만 — 특허처리비 +64백만 주원인
 - 1월 일회성 증가: 26년 외부감사 착수금 200백만</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>- 누계 실적 272백만(집행률 91%) — 예산 대비 소폭 미달
-- 예산 대비 Staff부문 -26백만 — 차이 작음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 당월 실적 2,633백만(집행률 103%) — 예산 대비 소폭 초과
-- 본사 1,752백만(집행률 95%) 예산 대비 미달 · 법인 881백만(집행률 121%) 예산 초과
-- HUMAX(공통) 467백만 — 1월(760백만) 대비 293백만 감소(외부감사 착수금 소멸)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>- 누계 실적 2,566백만(집행률 100%) · 연간 예산의 18% — 2개월 경과 진도(17%) 부합
 - 국내 583백만 · 연간 예산의 17% — 월 배부액 269→314백만 증가
 - 해외 1,983백만 · 연간 예산의 18% — 인건비 1,481백만(58%)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>- 누계 실적 975백만(집행률 66%) — 예산 대비 499백만 미달
-- 예산 대비 Media그룹 -527백만(외주개발용역비 -513) 주원인 · 월 배부액 493→483백만 변화 없음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>- 누계 실적 1,227백만(집행률 116%) — 예산 대비 170백만 초과
 - 예산 대비 Staff부문 +180백만 — 특허처리비 +77백만 주원인
 - 1월 일회성 증가: 26년 외부감사 착수금 200백만 — 제외 시 월 560→467백만</t>
@@ -170,11 +143,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>- 누계 실적 1,417백만(집행률 72%) — 예산 대비 541백만 미달
-- 예산 대비 Media그룹 -522백만(외주개발용역비 -533) 주원인 · 월 배부액 493→483→441백만 완만한 감소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>- 누계 실적 1,811백만(집행률 116%) — 예산 대비 245백만 초과
 - 예산 대비 Staff부문 +240백만 — 특허처리비 +90백만 주원인
 - 1월 일회성 증가: 26년 외부감사 착수금 200백만 — 제외 시 월 560→467→584백만, 감소 추세 없음</t>
@@ -186,24 +154,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>- 당월 실적 2,526백만(집행률 96%) — 예산 내 집행
-- 본사 1,868백만(집행률 94%) 예산 대비 미달 · 법인 658백만(집행률 104%) 소폭 초과
-- 건물 135백만 — 1~3월 평균 278백만의 절반 이하</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>- 누계 실적 4,972백만(집행률 95%) · 연간 예산의 34% — 4개월 경과 진도(33%) 부합
 - 국내 1,269백만 · 연간 예산의 36% 진도 상회 — 월 배부액 269→365백만 증가
 - 해외 3,703백만 · 연간 예산의 33% — 인건비 2,817백만(57%)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>- 누계 실적 1,982백만(집행률 83%) — 예산 대비 410백만 미달
-- 예산 대비 Media그룹 -426백만(외주개발용역비 -533) 주원인 · HUK +79백만 초과
-- 4월 트렌드 왜곡: STB License Fee/Nagra 4월 -84백만 (선급비용 결산 조정 지연)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>- 당월 실적 2,444백만(집행률 102%) — 예산 수준
 - 본사 1,804백만(집행률 100%) · 법인 640백만(집행률 108%) 예산 초과
 - HUMAX(공통) 716백만 — 1~4월 평균 602백만 상회 · 건물 121백만 — 4월(135백만)에 이어 낮은 수준</t>
@@ -216,69 +172,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>- 누계 실적 2,381백만(집행률 85%) — 예산 대비 425백만 미달
-- 예산 대비 Media그룹 -469백만(외주개발용역비 -525) 주원인 · 보정 후 월 441~493백만 — 감소 추세 없음
-- 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 2,818백만(집행률 88%) — 예산 내 집행
-- 본사 2,020백만(집행률 83%) 예산 대비 미달 · 법인 798백만(집행률 102%) 예산 수준
-- 항목별 집행률: 예산 초과 HUMAX(공통) 122% / 예산 미달 STB 49% — 차이의 대부분</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 5,451백만(집행률 94%) — 예산 내 집행
-- 본사 3,772백만(집행률 88%) 예산 대비 미달 · 법인 1,679백만(집행률 111%) 초과 — 방향 엇갈림
-- 항목별 집행률: 예산 초과 HUMAX(공통) 116% / 예산 미달 STB 66% — 차이의 대부분</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 당월 실적 2,592백만(집행률 97%) — 예산 내 집행
-- 본사 1,874백만(집행률 94%) 예산 대비 미달 · 법인 718백만(집행률 106%) 초과
-- MOBILITY 101백만 — 1~2월(61, 50백만) 대비 2배</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 8,043백만(집행률 95%) — 예산 내 집행
-- 본사 5,646백만(집행률 90%) 예산 대비 미달 · 법인 2,397백만(집행률 110%) 초과 — 방향 엇갈림
-- 항목별 집행률: 예산 초과 HUMAX(공통) 116%, MOBILITY 143% / 예산 미달 STB 72%, 건물 94%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 10,568백만(집행률 95%) — 예산 내 집행
-- 본사 7,514백만(집행률 91%) 예산 대비 미달 · 법인 3,055백만(집행률 109%) 초과 — 방향 엇갈림
-- 항목별 집행률: 예산 초과 HUMAX(공통) 115%, EVCS(국내) 107% / 예산 미달 건물 81%, STB 83%, EVCS(해외) 92%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>- 누계 실적 2,409백만(집행률 115%) — 예산 대비 321백만 초과
 - 예산 대비 Staff부문 +300백만 — 지급수수료 +106, 특허처리비 +105 주원인
 - 1월 일회성 증가: 26년 외부감사 착수금 200백만 — 제외 시 월 560→467→584→598백만</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>- 누계 실적 968백만(집행률 81%) — 예산 대비 231백만 미달
-- 예산 대비 감가상각비 -163백만, 수도광열비 -75 — 미달 주원인
-- 1~3월 평균 278백만 → 4월 135백만 — 절반 이하</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 13,012백만(집행률 97%) — 예산 내 집행
-- 본사 9,318백만(집행률 93%) 예산 대비 미달 · 법인 3,694백만(집행률 108%) 초과 — 방향 엇갈림
-- 항목별 집행률: 예산 초과 HUMAX(공통) 121%, EVCS(국내) 110% / 예산 미달 건물 72%, STB 85%, EVCS(해외) 92%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>- 누계 실적 3,125백만(집행률 121%) — 예산 대비 552백만 초과
 - 예산 대비 Staff부문 +516백만 — 급여 +208, 특허처리비 +106, 지급수수료 +100 주원인
 - 1월, 5월 일회성 증가: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 1,089백만(집행률 72%) — 예산 대비 416백만 미달
-- 예산 대비 감가상각비 -326백만, 수도광열비 -168 미달 주원인(임차료 +91 초과)
-- 1~3월 평균 278백만 → 4~5월 평균 128백만 — 4월부터 계단식 감소</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -380,12 +282,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>예산 대비 실적 집행률: 합계 15,549백만(97%), 본사 11,065백만(92%), 법인 4,484백만(112%)
- - 예산 초과: HUMAX(공통) 119%(주식보상 비용, VVC특허처리비 등) EVCS(국내) 108%
- - 예산 미달: 건물 67%(1Q 94%, 2Q 41%), STB 90%, EVCS(해외) 94%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[지급수수료]
 New Aura/iWedia 외주개발용역비 518백만 추가 집행 가능성 있음 (SW이슈로 지연)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -506,12 +402,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>예산 대비 실적 집행률: 합계 18,210백만(98%), 본사 13,097백만(94%), 법인 5,112백만(111%)
- - 예산 초과: HUMAX(공통) 127%(합병 자문·평가 수수료, 주식보상 비용, VVC특허처리비 등) EVCS(국내) 108%
- - 예산 미달: 건물 64%(1Q 94%, 2Q 41%, 7월 50%), STB 94%, EVCS(해외) 91%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만
  - 4월~: 분당 감가상각비 163백만 → 분당 임차료 월 45백만
  - 7월~: 티맥스수내타워 임대차 관리비 29백만(총 58백만) 신규 반영</t>
@@ -546,11 +436,6 @@
     <t>8월 누계</t>
   </si>
   <si>
-    <t>[지급수수료]
-외주개발용역비 누계 229백만(집행률 30%) — 예산 대비 523백만 미달 (New Aura/iWedia SW이슈로 지연)
-Charter Legal fee/B&amp;M Legal fee 8월 79백만 추가 집행 (누계 206백만, 소송 재개)</t>
-  </si>
-  <si>
     <t>1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만
  - 4월: 한화 임대차계약 체결로 구조 변경
  - 7월: 티맥스수내타워 관리비 집행 시작 · 8월 동일 구조 유지
@@ -565,12 +450,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>예산 대비 실적 집행률: 합계 21,186백만(100%), 본사 14,922백만(94%), 법인 6,264백만(121%)
- - 예산 초과: HUMAX(공통) 141%(HBR 지급수수료, 합병 자문·평가 수수료 등) EVCS(국내) 108%
- - 예산 미달: 건물 63%(1Q 94%, 2Q 41%, 3Q(7~8월) 51%), STB 95%, EVCS(해외) 90%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">                                                          </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -592,14 +471,6 @@
     <t>계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만
  - 4월~: 분당 감가상각비 163백만 → 분당 임차료 월 45백만
  - 7월~: 티맥스수내타워 임대차 관리비 29백만(총 58백만) 신규 반영</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4월, 5월 트렌드 왜곡
- - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
-1~5월 평균 476백만 대비 6월 60백만, 7월 45백만 초과 · 8월 66백만 미달
- - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만, 8월 79백만 집행 (누계 206백만)
- - HUS 8월 의료보험료 환급 -52백만, 유급휴가 충당금 회수 -28백만, 급여 -26백만 (2Q 7명 → 3Q 5명)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -613,12 +484,142 @@
 1~6월 평균 611백만 대비 7월 269백만, 8월 747백만 초과</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>- 당월 실적 2,818백만(집행률 88%) — 예산 대비 미집행
+- 본사 2,020백만(집행률 83%) 미집행 주도 · 법인 798백만(집행률 102%) 예산 수준
+- STB 493백만(집행률 49%) 최저 · HUMAX(공통) 760백만 — 외부감사 착수금 200백만 반영</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 2,818백만(집행률 88%) — 예산 내 집행
+- 본사 2,020백만(집행률 83%) 예산 대비 미집행 · 법인 798백만(집행률 102%) 예산 수준
+- 항목별 집행률: 예산 초과 HUMAX(공통) 122% / 예산 미집행 STB 49% — 차이의 대부분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 493백만(집행률 49%) — 예산 대비 521백만 미집행
+- 예산 대비 Media그룹 -533백만(외주개발용역비 -509) — 미집행의 대부분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 272백만(집행률 91%) — 예산 대비 소폭 미집행
+- 예산 대비 Staff부문 -26백만 — 차이 작음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 당월 실적 2,633백만(집행률 103%) — 예산 대비 소폭 초과
+- 본사 1,752백만(집행률 95%) 예산 대비 미집행 · 법인 881백만(집행률 121%) 예산 초과
+- HUMAX(공통) 467백만 — 1월(760백만) 대비 293백만 감소(외부감사 착수금 소멸)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 5,451백만(집행률 94%) — 예산 내 집행
+- 본사 3,772백만(집행률 88%) 예산 대비 미집행 · 법인 1,679백만(집행률 111%) 초과 — 방향 엇갈림
+- 항목별 집행률: 예산 초과 HUMAX(공통) 116% / 예산 미집행 STB 66% — 차이의 대부분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 975백만(집행률 66%) — 예산 대비 499백만 미집행
+- 예산 대비 Media그룹 -527백만(외주개발용역비 -513) 주원인 · 월 배부액 493→483백만 변화 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 당월 실적 2,592백만(집행률 97%) — 예산 내 집행
+- 본사 1,874백만(집행률 94%) 예산 대비 미집행 · 법인 718백만(집행률 106%) 초과
+- MOBILITY 101백만 — 1~2월(61, 50백만) 대비 2배</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 8,043백만(집행률 95%) — 예산 내 집행
+- 본사 5,646백만(집행률 90%) 예산 대비 미집행 · 법인 2,397백만(집행률 110%) 초과 — 방향 엇갈림
+- 항목별 집행률: 예산 초과 HUMAX(공통) 116%, MOBILITY 143% / 예산 미집행 STB 72%, 건물 94%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 1,417백만(집행률 72%) — 예산 대비 541백만 미집행
+- 예산 대비 Media그룹 -522백만(외주개발용역비 -533) 주원인 · 월 배부액 493→483→441백만 완만한 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 당월 실적 2,526백만(집행률 96%) — 예산 내 집행
+- 본사 1,868백만(집행률 94%) 예산 대비 미집행 · 법인 658백만(집행률 104%) 소폭 초과
+- 건물 135백만 — 1~3월 평균 278백만의 절반 이하</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 10,568백만(집행률 95%) — 예산 내 집행
+- 본사 7,514백만(집행률 91%) 예산 대비 미집행 · 법인 3,055백만(집행률 109%) 초과 — 방향 엇갈림
+- 항목별 집행률: 예산 초과 HUMAX(공통) 115%, EVCS(국내) 107% / 예산 미집행 건물 81%, STB 83%, EVCS(해외) 92%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 1,982백만(집행률 83%) — 예산 대비 410백만 미집행
+- 예산 대비 Media그룹 -426백만(외주개발용역비 -533) 주원인 · HUK +79백만 초과
+- 4월 트렌드 왜곡: STB License Fee/Nagra 4월 -84백만 (선급비용 결산 조정 지연)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 968백만(집행률 81%) — 예산 대비 231백만 미집행
+- 예산 대비 감가상각비 -163백만, 수도광열비 -75 — 미집행 주원인
+- 1~3월 평균 278백만 → 4월 135백만 — 절반 이하</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 13,012백만(집행률 97%) — 예산 내 집행
+- 본사 9,318백만(집행률 93%) 예산 대비 미집행 · 법인 3,694백만(집행률 108%) 초과 — 방향 엇갈림
+- 항목별 집행률: 예산 초과 HUMAX(공통) 121%, EVCS(국내) 110% / 예산 미집행 건물 72%, STB 85%, EVCS(해외) 92%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 2,381백만(집행률 85%) — 예산 대비 425백만 미집행
+- 예산 대비 Media그룹 -469백만(외주개발용역비 -525) 주원인 · 보정 후 월 441~493백만 — 감소 추세 없음
+- 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 1,089백만(집행률 72%) — 예산 대비 416백만 미집행
+- 예산 대비 감가상각비 -326백만, 수도광열비 -168 미집행 주원인(임차료 +91 초과)
+- 1~3월 평균 278백만 → 4~5월 평균 128백만 — 4월부터 계단식 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 15,549백만(97%), 본사 11,065백만(92%), 법인 4,484백만(112%)
+ - 예산 초과: HUMAX(공통) 119%(주식보상 비용, VVC특허처리비 등) EVCS(국내) 108%
+ - 예산 미집행: 건물 67%(1Q 94%, 2Q 41%), STB 90%, EVCS(해외) 94%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 18,210백만(98%), 본사 13,097백만(94%), 법인 5,112백만(111%)
+ - 예산 초과: HUMAX(공통) 127%(합병 자문·평가 수수료, 주식보상 비용, VVC특허처리비 등) EVCS(국내) 108%
+ - 예산 미집행: 건물 64%(1Q 94%, 2Q 41%, 7월 50%), STB 94%, EVCS(해외) 91%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 21,186백만(100%), 본사 14,922백만(94%), 법인 6,264백만(121%)
+ - 예산 초과: HUMAX(공통) 141%(HBR 지급수수료, 합병 자문·평가 수수료 등) EVCS(국내) 108%
+ - 예산 미집행: 건물 63%(1Q 94%, 2Q 41%, 3Q(7~8월) 51%), STB 95%, EVCS(해외) 90%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[지급수수료]
+외주개발용역비 누계 229백만(집행률 30%) — 예산 대비 523백만 미집행 (New Aura/iWedia SW이슈로 지연)
+Charter Legal fee/B&amp;M Legal fee 8월 79백만 추가 집행 (누계 206백만, 소송 재개)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4월, 5월 트렌드 왜곡
+ - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
+1~5월 평균 476백만 대비 6월 60백만, 7월 45백만 초과 · 8월 66백만 하회
+ - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만, 8월 79백만 집행 (누계 206백만)
+ - HUS 8월 의료보험료 환급 -52백만, 유급휴가 충당금 회수 -28백만, 급여 -26백만 (2Q 7명 → 3Q 5명)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2309,7 +2310,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}">
   <dimension ref="A1:I82"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
     <col min="2" max="2" width="12.625" customWidth="1"/>
@@ -2318,7 +2319,7 @@
     <col min="5" max="5" width="9" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2332,7 +2333,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="49.5">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -2341,10 +2342,10 @@
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="49.5">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -2353,10 +2354,10 @@
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="49.5">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -2365,10 +2366,10 @@
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="33">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -2379,10 +2380,10 @@
         <v>7</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="49.5">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -2393,10 +2394,10 @@
         <v>8</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="33">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -2407,10 +2408,10 @@
         <v>9</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="49.5">
       <c r="A8" s="5" t="s">
         <v>4</v>
       </c>
@@ -2419,10 +2420,10 @@
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="49.5">
       <c r="A9" s="5" t="s">
         <v>4</v>
       </c>
@@ -2431,10 +2432,10 @@
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="49.5">
       <c r="A10" s="5" t="s">
         <v>5</v>
       </c>
@@ -2443,10 +2444,10 @@
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="33">
       <c r="A11" s="5" t="s">
         <v>6</v>
       </c>
@@ -2457,10 +2458,10 @@
         <v>7</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="49.5">
       <c r="A12" s="5" t="s">
         <v>6</v>
       </c>
@@ -2471,10 +2472,10 @@
         <v>8</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="33">
       <c r="A13" s="5" t="s">
         <v>6</v>
       </c>
@@ -2485,10 +2486,10 @@
         <v>9</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="49.5">
       <c r="A14" s="4" t="s">
         <v>4</v>
       </c>
@@ -2497,10 +2498,10 @@
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="49.5">
       <c r="A15" s="4" t="s">
         <v>4</v>
       </c>
@@ -2509,10 +2510,10 @@
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="49.5">
       <c r="A16" s="4" t="s">
         <v>5</v>
       </c>
@@ -2521,10 +2522,10 @@
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="33">
       <c r="A17" s="4" t="s">
         <v>6</v>
       </c>
@@ -2535,10 +2536,10 @@
         <v>7</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="49.5">
       <c r="A18" s="4" t="s">
         <v>6</v>
       </c>
@@ -2549,10 +2550,10 @@
         <v>8</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="33">
       <c r="A19" s="4" t="s">
         <v>6</v>
       </c>
@@ -2563,10 +2564,10 @@
         <v>9</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="49.5">
       <c r="A20" s="5" t="s">
         <v>4</v>
       </c>
@@ -2575,10 +2576,10 @@
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="49.5">
       <c r="A21" s="5" t="s">
         <v>4</v>
       </c>
@@ -2587,10 +2588,10 @@
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="49.5">
       <c r="A22" s="5" t="s">
         <v>5</v>
       </c>
@@ -2599,10 +2600,10 @@
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="49.5">
       <c r="A23" s="5" t="s">
         <v>6</v>
       </c>
@@ -2613,10 +2614,10 @@
         <v>7</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="49.5">
       <c r="A24" s="5" t="s">
         <v>6</v>
       </c>
@@ -2627,10 +2628,10 @@
         <v>8</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="49.5">
       <c r="A25" s="5" t="s">
         <v>6</v>
       </c>
@@ -2641,10 +2642,10 @@
         <v>9</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="49.5">
       <c r="A26" s="4" t="s">
         <v>4</v>
       </c>
@@ -2653,10 +2654,10 @@
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="49.5">
       <c r="A27" s="4" t="s">
         <v>4</v>
       </c>
@@ -2665,10 +2666,10 @@
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="49.5">
       <c r="A28" s="4" t="s">
         <v>5</v>
       </c>
@@ -2677,10 +2678,10 @@
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="49.5">
       <c r="A29" s="4" t="s">
         <v>6</v>
       </c>
@@ -2691,10 +2692,10 @@
         <v>7</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="49.5">
       <c r="A30" s="4" t="s">
         <v>6</v>
       </c>
@@ -2705,10 +2706,10 @@
         <v>8</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="49.5">
       <c r="A31" s="4" t="s">
         <v>6</v>
       </c>
@@ -2719,10 +2720,10 @@
         <v>9</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
         <v>4</v>
       </c>
@@ -2731,13 +2732,13 @@
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="8" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="49.5">
       <c r="A33" s="5" t="s">
         <v>4</v>
       </c>
@@ -2746,13 +2747,13 @@
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="8" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="49.5">
       <c r="A34" s="5" t="s">
         <v>5</v>
       </c>
@@ -2761,13 +2762,13 @@
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="8" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="33">
       <c r="A35" s="5" t="s">
         <v>6</v>
       </c>
@@ -2778,13 +2779,13 @@
         <v>7</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="66">
       <c r="A36" s="5" t="s">
         <v>6</v>
       </c>
@@ -2795,13 +2796,13 @@
         <v>8</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="99" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="99">
       <c r="A37" s="5" t="s">
         <v>6</v>
       </c>
@@ -2812,32 +2813,32 @@
         <v>9</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="33">
       <c r="A38" s="5" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="66">
       <c r="A39" s="5" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>13</v>
@@ -2846,15 +2847,15 @@
         <v>7</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="33">
       <c r="A40" s="5" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>13</v>
@@ -2863,15 +2864,15 @@
         <v>8</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="33">
       <c r="A41" s="5" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>13</v>
@@ -2880,317 +2881,317 @@
         <v>9</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C42" s="14"/>
       <c r="D42" s="15" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="49.5">
       <c r="A43" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="15" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="49.5">
       <c r="A44" s="14" t="s">
         <v>5</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C44" s="14"/>
       <c r="D44" s="15" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="49.5">
       <c r="A45" s="14" t="s">
         <v>6</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C45" s="14" t="s">
         <v>7</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="99" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="99">
       <c r="A46" s="14" t="s">
         <v>6</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C46" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="132" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="132">
       <c r="A47" s="14" t="s">
         <v>6</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C47" s="14" t="s">
         <v>9</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="66">
       <c r="A48" s="14" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C48" s="14" t="s">
         <v>7</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="82.5">
       <c r="A49" s="14" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C49" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="49.5">
       <c r="A50" s="14" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C50" s="14" t="s">
         <v>9</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="49.5">
       <c r="A51" s="25" t="s">
         <v>4</v>
       </c>
       <c r="B51" s="25" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="C51" s="25"/>
       <c r="D51" s="8" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="E51" s="24" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="49.5">
       <c r="A52" s="25" t="s">
         <v>4</v>
       </c>
       <c r="B52" s="25" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="C52" s="25"/>
       <c r="D52" s="8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E52" s="24" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="99" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="99">
       <c r="A53" s="25" t="s">
         <v>5</v>
       </c>
       <c r="B53" s="25" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="C53" s="25"/>
       <c r="D53" s="8" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="E53" s="24" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="49.5">
       <c r="A54" s="25" t="s">
         <v>6</v>
       </c>
       <c r="B54" s="25" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="C54" s="25" t="s">
         <v>7</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E54" s="24" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="99" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="99">
       <c r="A55" s="25" t="s">
         <v>6</v>
       </c>
       <c r="B55" s="25" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="C55" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="E55" s="24" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="132" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="132">
       <c r="A56" s="25" t="s">
         <v>6</v>
       </c>
       <c r="B56" s="25" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="C56" s="25" t="s">
         <v>9</v>
       </c>
       <c r="D56" s="26" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="E56" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="82.5">
       <c r="A57" s="25" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="C57" s="25" t="s">
         <v>7</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E57" s="24" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="132" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="132">
       <c r="A58" s="25" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B58" s="25" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="C58" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="49.5">
       <c r="A59" s="25" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B59" s="25" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="C59" s="25" t="s">
         <v>9</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="E59" s="24" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" s="11" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
       <c r="D60" s="19"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9">
       <c r="A61" s="11" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
@@ -3201,7 +3202,7 @@
       <c r="H61" s="22"/>
       <c r="I61" s="22"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
@@ -3212,7 +3213,7 @@
       <c r="H62" s="22"/>
       <c r="I62" s="22"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
@@ -3223,7 +3224,7 @@
       <c r="H63" s="22"/>
       <c r="I63" s="22"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
@@ -3234,7 +3235,7 @@
       <c r="H64" s="22"/>
       <c r="I64" s="22"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9">
       <c r="A65" s="18"/>
       <c r="B65" s="18"/>
       <c r="C65" s="18"/>
@@ -3245,7 +3246,7 @@
       <c r="H65" s="22"/>
       <c r="I65" s="22"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9">
       <c r="A66" s="18"/>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
@@ -3256,7 +3257,7 @@
       <c r="H66" s="22"/>
       <c r="I66" s="22"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9">
       <c r="A67" s="18"/>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
@@ -3267,10 +3268,10 @@
       <c r="H67" s="22"/>
       <c r="I67" s="22"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4">
       <c r="A82" s="27"/>
       <c r="D82" s="1" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A433989E-DB01-4FF6-823B-CB2AA37E267A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E854B20F-41FC-459F-981A-7FCC1AE0C086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="2550" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -408,15 +408,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만
- - 4월: 한화 임대차계약 체결로 구조 변경
- - 7월: 티맥스수내타워 관리비 집행 시작
-7월 1.5억: 용인 0.8억(51%), 분당 0.8억(49%)
- - 용인 0.8억(총 0.9억): 감가상각비 0.4억(총 0.45억), 건물관리수수료 0.27억(총 0.32억), 수도광열비 0.05억(총 0.08억), 보험료 0.06억(총 0.06억)
- - 분당 0.8억(총 2.5억): 임차료 0.45억(총 1.44억), 수광비 0.01억(총 0.03억: 챔버, 카페), 건물관리수수료 0.01억(총 0.4억: 관리비 0.59억 - 실비수입 0.2억), 건물관리수수료(티맥스) 0.3억(총 0.58억)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[인건비]
 주식보상비용 250백만 집행 (예산 외, 일회성)
 [지급수수료]
@@ -434,14 +425,6 @@
   </si>
   <si>
     <t>8월 누계</t>
-  </si>
-  <si>
-    <t>1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만
- - 4월: 한화 임대차계약 체결로 구조 변경
- - 7월: 티맥스수내타워 관리비 집행 시작 · 8월 동일 구조 유지
-8월 1.5억: 건물관리수수료 0.59억, 임차료 0.45억, 감가상각비 0.4억
- - 용인 0.8억(총 0.9억): 감가상각비 0.4억(총 0.45억), 건물관리수수료 0.27억(총 0.32억), 수도광열비 0.05억(총 0.08억), 보험료 0.06억(총 0.06억)
- - 분당 0.8억(총 2.5억): 임차료 0.45억(총 1.44억), 수광비 0.01억(총 0.03억: 챔버, 카페), 건물관리수수료 0.01억(총 0.4억: 관리비 0.59억 - 실비수입 0.2억), 건물관리수수료(티맥스) 0.3억(총 0.58억)</t>
   </si>
   <si>
     <t>예산 대비 실적 집행률: 합계 9,566백만(94%), 본사 7,166백만(92%), 법인 2,400백만(100%)
@@ -612,6 +595,18 @@
 1~5월 평균 476백만 대비 6월 60백만, 7월 45백만 초과 · 8월 66백만 하회
  - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만, 8월 79백만 집행 (누계 206백만)
  - HUS 8월 의료보험료 환급 -52백만, 유급휴가 충당금 회수 -28백만, 급여 -26백만 (2Q 7명 → 3Q 5명)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만
+ - 4월: 한화 임대차계약 체결로 구조 변경
+ - 7월: 티맥스수내타워 관리비 집행 시작</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만
+ - 4월: 한화 임대차계약 체결로 구조 변경
+ - 7월: 티맥스수내타워 관리비 집행 시작 · 8월 동일 구조 유지</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1448,7 +1443,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="222250" y="45582417"/>
+          <a:off x="222250" y="43910251"/>
           <a:ext cx="13005707" cy="4344006"/>
           <a:chOff x="179917" y="45603583"/>
           <a:chExt cx="13005707" cy="4344006"/>
@@ -1903,7 +1898,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="13260917" y="45709418"/>
+          <a:off x="13260917" y="44037251"/>
           <a:ext cx="6449325" cy="5420481"/>
           <a:chOff x="13260917" y="45497751"/>
           <a:chExt cx="6449325" cy="5420481"/>
@@ -2342,7 +2337,7 @@
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="49.5">
@@ -2354,7 +2349,7 @@
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="49.5">
@@ -2380,7 +2375,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="49.5">
@@ -2408,7 +2403,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="49.5">
@@ -2420,7 +2415,7 @@
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="49.5">
@@ -2432,7 +2427,7 @@
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="49.5">
@@ -2458,7 +2453,7 @@
         <v>7</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="49.5">
@@ -2498,7 +2493,7 @@
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="49.5">
@@ -2510,7 +2505,7 @@
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="49.5">
@@ -2536,7 +2531,7 @@
         <v>7</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="49.5">
@@ -2576,7 +2571,7 @@
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="49.5">
@@ -2588,7 +2583,7 @@
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="49.5">
@@ -2614,7 +2609,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="49.5">
@@ -2642,7 +2637,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="49.5">
@@ -2666,7 +2661,7 @@
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="49.5">
@@ -2692,7 +2687,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="49.5">
@@ -2720,7 +2715,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2747,7 +2742,7 @@
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E33" s="13" t="s">
         <v>46</v>
@@ -2816,7 +2811,7 @@
         <v>64</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="33">
@@ -2911,7 +2906,7 @@
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E43" s="13" t="s">
         <v>54</v>
@@ -2960,13 +2955,13 @@
         <v>8</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E46" s="13" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="132">
+    <row r="47" spans="1:5" ht="49.5">
       <c r="A47" s="14" t="s">
         <v>6</v>
       </c>
@@ -2977,7 +2972,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="E47" s="13" t="s">
         <v>59</v>
@@ -3039,11 +3034,11 @@
         <v>4</v>
       </c>
       <c r="B51" s="25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C51" s="25"/>
       <c r="D51" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E51" s="24" t="s">
         <v>54</v>
@@ -3054,11 +3049,11 @@
         <v>4</v>
       </c>
       <c r="B52" s="25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C52" s="25"/>
       <c r="D52" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E52" s="24" t="s">
         <v>54</v>
@@ -3069,11 +3064,11 @@
         <v>5</v>
       </c>
       <c r="B53" s="25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C53" s="25"/>
       <c r="D53" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E53" s="24" t="s">
         <v>57</v>
@@ -3084,13 +3079,13 @@
         <v>6</v>
       </c>
       <c r="B54" s="25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C54" s="25" t="s">
         <v>7</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E54" s="24" t="s">
         <v>58</v>
@@ -3101,30 +3096,30 @@
         <v>6</v>
       </c>
       <c r="B55" s="25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C55" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E55" s="24" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="132">
+    <row r="56" spans="1:9" ht="82.5">
       <c r="A56" s="25" t="s">
         <v>6</v>
       </c>
       <c r="B56" s="25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C56" s="25" t="s">
         <v>9</v>
       </c>
       <c r="D56" s="26" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="E56" s="24" t="s">
         <v>59</v>
@@ -3135,13 +3130,13 @@
         <v>44</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C57" s="25" t="s">
         <v>7</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E57" s="24" t="s">
         <v>60</v>
@@ -3152,13 +3147,13 @@
         <v>44</v>
       </c>
       <c r="B58" s="25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C58" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E58" s="24" t="s">
         <v>60</v>
@@ -3169,13 +3164,13 @@
         <v>44</v>
       </c>
       <c r="B59" s="25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C59" s="25" t="s">
         <v>9</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E59" s="24" t="s">
         <v>60</v>
@@ -3271,7 +3266,7 @@
     <row r="82" spans="1:4">
       <c r="A82" s="27"/>
       <c r="D82" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E854B20F-41FC-459F-981A-7FCC1AE0C086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1972058-882B-4E34-AEC0-1C8B5F653C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -374,12 +374,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[지급수수료]
-New Aura/iWedia 외주개발용역비 518백만 추가 집행 가능성 있음 (SW이슈로 지연)
-Charter Legal fee/B&amp;M Legal fee 127백만 집행 (소송 재개)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">1Q 월평균 278백만 → 2Q 월평균 126백만 (4월 한화 임대차 계약 영향)
 10월 사옥 이전 전까지 아래 비용 구조로 예상
@@ -437,20 +431,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>예산 대비 실적 집행률: 합계 2,976백만(120%), 본사 1,825백만(95%), 법인 1,152백만(204%)
- - 법인 초과: HBR 지급수수료 703백만 집행 — HBR Artur 세액공제 매각 중개수수료 650백만, HBR CTJ 법정 대표자 보수 54백만</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[인건비]
-주식보상비용 250백만 집행 (예산 외, 일회성)
-[지급수수료]
-8월 HBR 703백만 집행 (HBR Artur 세액공제 매각 중개수수료 650백만, HBR CTJ 법정 대표자 보수 54백만)
-합병 자문·평가 수수료 누계 482백만 집행 (7월 350백만, 8월 131백만)
-특허처리비 104백만 초과 집행 (VVC 예산 누락 영향)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만
  - 4월~: 분당 감가상각비 163백만 → 분당 임차료 월 45백만
  - 7월~: 티맥스수내타워 임대차 관리비 29백만(총 58백만) 신규 반영</t>
@@ -513,12 +493,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>- 누계 실적 8,043백만(집행률 95%) — 예산 내 집행
-- 본사 5,646백만(집행률 90%) 예산 대비 미집행 · 법인 2,397백만(집행률 110%) 초과 — 방향 엇갈림
-- 항목별 집행률: 예산 초과 HUMAX(공통) 116%, MOBILITY 143% / 예산 미집행 STB 72%, 건물 94%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>- 누계 실적 1,417백만(집행률 72%) — 예산 대비 541백만 미집행
 - 예산 대비 Media그룹 -522백만(외주개발용역비 -533) 주원인 · 월 배부액 493→483→441백만 완만한 감소</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -530,12 +504,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>- 누계 실적 10,568백만(집행률 95%) — 예산 내 집행
-- 본사 7,514백만(집행률 91%) 예산 대비 미집행 · 법인 3,055백만(집행률 109%) 초과 — 방향 엇갈림
-- 항목별 집행률: 예산 초과 HUMAX(공통) 115%, EVCS(국내) 107% / 예산 미집행 건물 81%, STB 83%, EVCS(해외) 92%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>- 누계 실적 1,982백만(집행률 83%) — 예산 대비 410백만 미집행
 - 예산 대비 Media그룹 -426백만(외주개발용역비 -533) 주원인 · HUK +79백만 초과
 - 4월 트렌드 왜곡: STB License Fee/Nagra 4월 -84백만 (선급비용 결산 조정 지연)</t>
@@ -548,12 +516,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>- 누계 실적 13,012백만(집행률 97%) — 예산 내 집행
-- 본사 9,318백만(집행률 93%) 예산 대비 미집행 · 법인 3,694백만(집행률 108%) 초과 — 방향 엇갈림
-- 항목별 집행률: 예산 초과 HUMAX(공통) 121%, EVCS(국내) 110% / 예산 미집행 건물 72%, STB 85%, EVCS(해외) 92%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>- 누계 실적 2,381백만(집행률 85%) — 예산 대비 425백만 미집행
 - 예산 대비 Media그룹 -469백만(외주개발용역비 -525) 주원인 · 보정 후 월 441~493백만 — 감소 추세 없음
 - 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)</t>
@@ -563,30 +525,6 @@
     <t>- 누계 실적 1,089백만(집행률 72%) — 예산 대비 416백만 미집행
 - 예산 대비 감가상각비 -326백만, 수도광열비 -168 미집행 주원인(임차료 +91 초과)
 - 1~3월 평균 278백만 → 4~5월 평균 128백만 — 4월부터 계단식 감소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>예산 대비 실적 집행률: 합계 15,549백만(97%), 본사 11,065백만(92%), 법인 4,484백만(112%)
- - 예산 초과: HUMAX(공통) 119%(주식보상 비용, VVC특허처리비 등) EVCS(국내) 108%
- - 예산 미집행: 건물 67%(1Q 94%, 2Q 41%), STB 90%, EVCS(해외) 94%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>예산 대비 실적 집행률: 합계 18,210백만(98%), 본사 13,097백만(94%), 법인 5,112백만(111%)
- - 예산 초과: HUMAX(공통) 127%(합병 자문·평가 수수료, 주식보상 비용, VVC특허처리비 등) EVCS(국내) 108%
- - 예산 미집행: 건물 64%(1Q 94%, 2Q 41%, 7월 50%), STB 94%, EVCS(해외) 91%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>예산 대비 실적 집행률: 합계 21,186백만(100%), 본사 14,922백만(94%), 법인 6,264백만(121%)
- - 예산 초과: HUMAX(공통) 141%(HBR 지급수수료, 합병 자문·평가 수수료 등) EVCS(국내) 108%
- - 예산 미집행: 건물 63%(1Q 94%, 2Q 41%, 3Q(7~8월) 51%), STB 95%, EVCS(해외) 90%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[지급수수료]
-외주개발용역비 누계 229백만(집행률 30%) — 예산 대비 523백만 미집행 (New Aura/iWedia SW이슈로 지연)
-Charter Legal fee/B&amp;M Legal fee 8월 79백만 추가 집행 (누계 206백만, 소송 재개)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -607,6 +545,68 @@
     <t>1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만
  - 4월: 한화 임대차계약 체결로 구조 변경
  - 7월: 티맥스수내타워 관리비 집행 시작 · 8월 동일 구조 유지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 8,043백만(집행률 95%) — 예산 내 집행
+- 본사 5,646백만(집행률 90%) 예산 대비 미집행 · 법인 2,397백만(집행률 110%) 초과 — 방향 엇갈림
+- 항목별 집행률: 예산 초과 MOBILITY 143%, HUMAX(공통) 116% / 예산 미집행 STB 72%, 건물 94%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 10,568백만(집행률 95%) — 예산 내 집행
+- 본사 7,514백만(집행률 91%) 예산 대비 미집행 · 법인 3,055백만(집행률 109%) 초과 — 방향 엇갈림
+- 항목별 집행률: 예산 초과 EVCS(국내) 107%, HUMAX(공통) 115% / 예산 미집행 STB 83%, EVCS(해외) 92%, 건물 81%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 13,012백만(집행률 97%) — 예산 내 집행
+- 본사 9,318백만(집행률 93%) 예산 대비 미집행 · 법인 3,694백만(집행률 108%) 초과 — 방향 엇갈림
+- 항목별 집행률: 예산 초과 EVCS(국내) 110%, HUMAX(공통) 121% / 예산 미집행 STB 85%, EVCS(해외) 92%, 건물 72%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 15,549백만(97%), 본사 11,065백만(92%), 법인 4,484백만(112%)
+ - 예산 초과: EVCS(국내) 108%, HUMAX(공통) 119%(주식보상 비용, VVC특허처리비 등)
+ - 예산 미집행: STB 90%, EVCS(해외) 94%, 건물 67%(1Q 94%, 2Q 41%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 18,210백만(98%), 본사 13,097백만(94%), 법인 5,112백만(111%)
+ - 예산 초과: EVCS(국내) 108%, HUMAX(공통) 127%(합병 자문·평가 수수료, 주식보상 비용, VVC특허처리비 등)
+ - 예산 미집행: STB 94%, EVCS(해외) 91%, 건물 64%(1Q 94%, 2Q 41%, 7월 50%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[지급수수료]
+New Aura/iWedia 외주개발용역비 518백만 추가 집행 가능성 있음 (SW이슈로 지연)
+Charter Legal fee/B&amp;M 127백만 집행 (소송 재개)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 2,976백만(120%), 본사 1,825백만(95%), 법인 1,152백만(204%)
+ - 법인 초과: HBR tax credit 매각 수수료 650백만, Ciro 성공보수 54백만</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 21,186백만(100%), 본사 14,922백만(94%), 법인 6,264백만(121%)
+ - 예산 초과: EVCS(국내) 108%, HUMAX(공통) 141%(HBR 지급수수료, 합병 자문·평가 수수료 등)
+ - 예산 미집행: STB 95%, EVCS(해외) 90%, 건물 63%(1Q 94%, 2Q 41%, 3Q(7~8월) 51%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[지급수수료]
+외주개발용역비 누계 229백만(집행률 30%) — 예산 대비 523백만 미집행 (New Aura/iWedia SW이슈로 지연)
+Charter Legal fee/B&amp;M 8월 79백만 추가 집행 (누계 206백만, 소송 재개)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[인건비]
+주식보상비용 250백만 집행 (예산 외, 일회성)
+[지급수수료]
+8월 HBR 703백만 집행 (tax credit 매각 수수료 650백만, Ciro 성공보수 54백만)
+합병 자문·평가 수수료 누계 506백만 집행 (1월 10백만, 4월 15백만, 7월 350백만, 8월 131백만)
+특허처리비 104백만 초과 집행 (VVC 예산 누락 영향)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="49.5">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="49.5">
@@ -2375,7 +2375,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="49.5">
@@ -2403,7 +2403,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="49.5">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="49.5">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="49.5">
@@ -2453,7 +2453,7 @@
         <v>7</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="49.5">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="49.5">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="6" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="49.5">
@@ -2531,7 +2531,7 @@
         <v>7</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="49.5">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="49.5">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="49.5">
@@ -2609,7 +2609,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="49.5">
@@ -2637,7 +2637,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="49.5">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="49.5">
@@ -2687,7 +2687,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="49.5">
@@ -2715,7 +2715,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2808,10 +2808,10 @@
         <v>9</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="33">
@@ -2938,7 +2938,7 @@
         <v>7</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="E45" s="13" t="s">
         <v>58</v>
@@ -2955,7 +2955,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E46" s="13" t="s">
         <v>58</v>
@@ -2972,7 +2972,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="E47" s="13" t="s">
         <v>59</v>
@@ -3023,7 +3023,7 @@
         <v>9</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E50" s="13" t="s">
         <v>60</v>
@@ -3034,11 +3034,11 @@
         <v>4</v>
       </c>
       <c r="B51" s="25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C51" s="25"/>
       <c r="D51" s="8" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="E51" s="24" t="s">
         <v>54</v>
@@ -3049,11 +3049,11 @@
         <v>4</v>
       </c>
       <c r="B52" s="25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C52" s="25"/>
       <c r="D52" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E52" s="24" t="s">
         <v>54</v>
@@ -3064,11 +3064,11 @@
         <v>5</v>
       </c>
       <c r="B53" s="25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C53" s="25"/>
       <c r="D53" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E53" s="24" t="s">
         <v>57</v>
@@ -3079,13 +3079,13 @@
         <v>6</v>
       </c>
       <c r="B54" s="25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C54" s="25" t="s">
         <v>7</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E54" s="24" t="s">
         <v>58</v>
@@ -3096,13 +3096,13 @@
         <v>6</v>
       </c>
       <c r="B55" s="25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C55" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="E55" s="24" t="s">
         <v>58</v>
@@ -3113,13 +3113,13 @@
         <v>6</v>
       </c>
       <c r="B56" s="25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C56" s="25" t="s">
         <v>9</v>
       </c>
       <c r="D56" s="26" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E56" s="24" t="s">
         <v>59</v>
@@ -3130,13 +3130,13 @@
         <v>44</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C57" s="25" t="s">
         <v>7</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E57" s="24" t="s">
         <v>60</v>
@@ -3147,13 +3147,13 @@
         <v>44</v>
       </c>
       <c r="B58" s="25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C58" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E58" s="24" t="s">
         <v>60</v>
@@ -3164,13 +3164,13 @@
         <v>44</v>
       </c>
       <c r="B59" s="25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C59" s="25" t="s">
         <v>9</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E59" s="24" t="s">
         <v>60</v>
@@ -3266,7 +3266,7 @@
     <row r="82" spans="1:4">
       <c r="A82" s="27"/>
       <c r="D82" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1972058-882B-4E34-AEC0-1C8B5F653C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B08E7BA-A611-42C8-A952-29D3769431D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -605,7 +605,7 @@
 주식보상비용 250백만 집행 (예산 외, 일회성)
 [지급수수료]
 8월 HBR 703백만 집행 (tax credit 매각 수수료 650백만, Ciro 성공보수 54백만)
-합병 자문·평가 수수료 누계 506백만 집행 (1월 10백만, 4월 15백만, 7월 350백만, 8월 131백만)
+합병 자문·평가 수수료 누계 482백만 집행 (7월 350백만, 8월 131백만)
 특허처리비 104백만 초과 집행 (VVC 예산 누락 영향)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B08E7BA-A611-42C8-A952-29D3769431D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B27966-5FAC-4C83-AF7A-002888462E6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -605,7 +605,7 @@
 주식보상비용 250백만 집행 (예산 외, 일회성)
 [지급수수료]
 8월 HBR 703백만 집행 (tax credit 매각 수수료 650백만, Ciro 성공보수 54백만)
-합병 자문·평가 수수료 누계 482백만 집행 (7월 350백만, 8월 131백만)
+합병 자문·평가 수수료 누계 506백만 집행 (1월 10백만, 4월 15백만, 7월 350백만, 8월 131백만)
 특허처리비 104백만 초과 집행 (VVC 예산 누락 영향)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -614,7 +614,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2305,7 +2305,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}">
   <dimension ref="A1:I82"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
     <col min="2" max="2" width="12.625" customWidth="1"/>
@@ -2314,7 +2314,7 @@
     <col min="5" max="5" width="9" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="49.5">
+    <row r="2" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="49.5">
+    <row r="3" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -2352,7 +2352,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="49.5">
+    <row r="4" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -2364,7 +2364,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="33">
+    <row r="5" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="49.5">
+    <row r="6" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -2392,7 +2392,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="33">
+    <row r="7" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -2406,7 +2406,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="49.5">
+    <row r="8" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>4</v>
       </c>
@@ -2418,7 +2418,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="49.5">
+    <row r="9" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>4</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="49.5">
+    <row r="10" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>5</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="33">
+    <row r="11" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>6</v>
       </c>
@@ -2456,7 +2456,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="49.5">
+    <row r="12" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>6</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="33">
+    <row r="13" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>6</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="49.5">
+    <row r="14" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>4</v>
       </c>
@@ -2496,7 +2496,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="49.5">
+    <row r="15" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>4</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="49.5">
+    <row r="16" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>5</v>
       </c>
@@ -2520,7 +2520,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="33">
+    <row r="17" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>6</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="49.5">
+    <row r="18" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>6</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="33">
+    <row r="19" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>6</v>
       </c>
@@ -2562,7 +2562,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="49.5">
+    <row r="20" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>4</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="49.5">
+    <row r="21" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>4</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="49.5">
+    <row r="22" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>5</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="49.5">
+    <row r="23" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>6</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="49.5">
+    <row r="24" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>6</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="49.5">
+    <row r="25" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>6</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="49.5">
+    <row r="26" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>4</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="49.5">
+    <row r="27" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>4</v>
       </c>
@@ -2664,7 +2664,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="49.5">
+    <row r="28" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>5</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="49.5">
+    <row r="29" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>6</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="49.5">
+    <row r="30" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>6</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="49.5">
+    <row r="31" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>6</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>4</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="49.5">
+    <row r="33" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>4</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="49.5">
+    <row r="34" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>5</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="33">
+    <row r="35" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>6</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="66">
+    <row r="36" spans="1:5" ht="66" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>6</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="99">
+    <row r="37" spans="1:5" ht="99" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>6</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="33">
+    <row r="38" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>45</v>
       </c>
@@ -2831,7 +2831,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="66">
+    <row r="39" spans="1:5" ht="66" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>44</v>
       </c>
@@ -2848,7 +2848,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="33">
+    <row r="40" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>44</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="33">
+    <row r="41" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>44</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
         <v>4</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="49.5">
+    <row r="43" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>4</v>
       </c>
@@ -2912,7 +2912,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="49.5">
+    <row r="44" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
         <v>5</v>
       </c>
@@ -2927,7 +2927,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="49.5">
+    <row r="45" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A45" s="14" t="s">
         <v>6</v>
       </c>
@@ -2944,7 +2944,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="99">
+    <row r="46" spans="1:5" ht="99" x14ac:dyDescent="0.3">
       <c r="A46" s="14" t="s">
         <v>6</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="49.5">
+    <row r="47" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A47" s="14" t="s">
         <v>6</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="66">
+    <row r="48" spans="1:5" ht="66" x14ac:dyDescent="0.3">
       <c r="A48" s="14" t="s">
         <v>44</v>
       </c>
@@ -2995,7 +2995,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="82.5">
+    <row r="49" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A49" s="14" t="s">
         <v>44</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="49.5">
+    <row r="50" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A50" s="14" t="s">
         <v>44</v>
       </c>
@@ -3029,7 +3029,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="49.5">
+    <row r="51" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A51" s="25" t="s">
         <v>4</v>
       </c>
@@ -3044,7 +3044,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="49.5">
+    <row r="52" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A52" s="25" t="s">
         <v>4</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="99">
+    <row r="53" spans="1:9" ht="99" x14ac:dyDescent="0.3">
       <c r="A53" s="25" t="s">
         <v>5</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="49.5">
+    <row r="54" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A54" s="25" t="s">
         <v>6</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="99">
+    <row r="55" spans="1:9" ht="99" x14ac:dyDescent="0.3">
       <c r="A55" s="25" t="s">
         <v>6</v>
       </c>
@@ -3108,7 +3108,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="82.5">
+    <row r="56" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A56" s="25" t="s">
         <v>6</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="82.5">
+    <row r="57" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A57" s="25" t="s">
         <v>44</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="132">
+    <row r="58" spans="1:9" ht="132" x14ac:dyDescent="0.3">
       <c r="A58" s="25" t="s">
         <v>44</v>
       </c>
@@ -3159,7 +3159,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="49.5">
+    <row r="59" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A59" s="25" t="s">
         <v>44</v>
       </c>
@@ -3176,7 +3176,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="11" t="s">
         <v>36</v>
       </c>
@@ -3184,7 +3184,7 @@
       <c r="C60" s="18"/>
       <c r="D60" s="19"/>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="11" t="s">
         <v>35</v>
       </c>
@@ -3197,7 +3197,7 @@
       <c r="H61" s="22"/>
       <c r="I61" s="22"/>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
@@ -3208,7 +3208,7 @@
       <c r="H62" s="22"/>
       <c r="I62" s="22"/>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
@@ -3219,7 +3219,7 @@
       <c r="H63" s="22"/>
       <c r="I63" s="22"/>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
@@ -3230,7 +3230,7 @@
       <c r="H64" s="22"/>
       <c r="I64" s="22"/>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="18"/>
       <c r="B65" s="18"/>
       <c r="C65" s="18"/>
@@ -3241,7 +3241,7 @@
       <c r="H65" s="22"/>
       <c r="I65" s="22"/>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="18"/>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
@@ -3252,7 +3252,7 @@
       <c r="H66" s="22"/>
       <c r="I66" s="22"/>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="18"/>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
@@ -3263,7 +3263,7 @@
       <c r="H67" s="22"/>
       <c r="I67" s="22"/>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="27"/>
       <c r="D82" s="1" t="s">
         <v>70</v>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B27966-5FAC-4C83-AF7A-002888462E6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{904A9398-C4A1-4A88-9A8A-8C50E6DEF234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView minimized="1" xWindow="7860" yWindow="4770" windowWidth="21600" windowHeight="11295" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$1:$D$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$1:$D$70</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="111">
   <si>
     <t>탭</t>
   </si>
@@ -608,6 +608,67 @@
 합병 자문·평가 수수료 누계 506백만 집행 (1월 10백만, 4월 15백만, 7월 350백만, 8월 131백만)
 특허처리비 104백만 초과 집행 (VVC 예산 누락 영향)</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9월</t>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 2,277백만(94%), 본사 1,721백만(95%), 법인 555백만(89%)
+ - 법인: 8월 HBR 704백만(tax credit 매각 수수료, Ciro 성공보수) → 9월 32백만으로 집행률 204% → 89%</t>
+  </si>
+  <si>
+    <t>9월 누계</t>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 23,463백만(100%), 본사 16,644백만(94%), 법인 6,819백만(118%)
+ - 예산 초과: HUMAX(공통) 138%(HBR 지급수수료, 합병 자문·평가 수수료 등), EVCS(국내) 107%
+ - 예산 미집행: STB 97%, EVCS(해외) 89%, 건물 61%(1Q 94%, 2Q 41%, 3Q 49%)</t>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 10,603백만(94%), 본사 7,997백만(93%), 법인 2,606백만(97%)
+국내/해외 비중: 1Q 국내 24%/해외 76%, 2Q 국내 29%/해외 71%, 3Q 국내 28%/해외 72%
+ - 개발 그룹 리소스 투입 변화: 해외→국내</t>
+  </si>
+  <si>
+    <t>[지급수수료]
+외주개발용역비 누계 260백만(집행률 33%) — 예산 대비 522백만 미집행 (New Aura/iWedia SW이슈로 지연)
+Charter Legal fee/B&amp;M 9월 64백만 추가 집행 (누계 270백만, 소송 진행)</t>
+  </si>
+  <si>
+    <t>[인건비]
+주식보상비용 250백만 집행 (예산 외, 일회성)
+[지급수수료]
+HBR 누계 1,201백만(집행률 312%) — 8월 703백만, 9월 32백만
+합병 자문·평가 수수료 누계 557백만 집행 (1월 10백만, 4월 15백만, 7월 350백만, 8월 131백만, 9월 51백만)
+특허처리비 누계 111백만(예산 8백만) 초과 집행 (VVC 예산 누락 영향)</t>
+  </si>
+  <si>
+    <t>1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만 → 9월 149백만
+ - 4월: 한화 임대차계약 체결로 구조 변경
+ - 7월: 티맥스수내타워 관리비 집행 시작 · 8~9월 동일 구조 유지</t>
+  </si>
+  <si>
+    <t>4월, 5월 트렌드 왜곡
+ - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
+1~5월 평균 476백만 대비 6월 60백만, 7월 45백만, 9월 59백만 초과 · 8월 66백만 하회
+ - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만, 8월 79백만, 9월 64백만 집행 (누계 270백만)
+ - HUS 8월 의료보험료 환급 -52백만, 유급휴가 충당금 회수 -28백만, 급여 -26백만 (2Q 7명 → 3Q 5명)</t>
+  </si>
+  <si>
+    <t>일회성 증가 항목
+ - 1월: 26년 외부감사 착수금 200백만
+ - 3월, 5월: 주식보상비용 3월 34백만, 5월 216백만
+ - 7월: 합병 자문·평가 수수료 350백만 (KB증권, 이촌회계법인)
+*(참고) 잔금 1억 (KB증권, 합병기일 후)
+ - 8월: HBR Artur 세액공제 매각 중개수수료 650백만, HBR CTJ 법정 대표자 보수 54백만, 홀딩스 합병 자문 수수료 131백만
+*(참고) 잔금 Artur 670백만, CTJ 45백만
+ - 9월: 합병 관련 수수료 51백만 (법무법인 광장, 보현회계법인, 한국예탁결제원)
+1~6월 평균 611백만 대비 7월 269백만, 8월 747백만 초과 · 9월 79백만 하회</t>
+  </si>
+  <si>
+    <t>계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만 → 9월 149백만
+ - 4월~: 분당 감가상각비 163백만 → 분당 임차료 월 45백만
+ - 7월~: 티맥스수내타워 임대차 관리비 29백만(총 58백만) 신규 반영</t>
   </si>
 </sst>
 </file>
@@ -857,7 +918,7 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -888,13 +949,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>158750</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>84667</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>4487333</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1421,13 +1482,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>222250</xdr:colOff>
-      <xdr:row>81</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>105834</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>517374</xdr:colOff>
-      <xdr:row>102</xdr:row>
+      <xdr:row>111</xdr:row>
       <xdr:rowOff>4840</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -1443,7 +1504,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="222250" y="43910251"/>
+          <a:off x="222250" y="51646667"/>
           <a:ext cx="13005707" cy="4344006"/>
           <a:chOff x="179917" y="45603583"/>
           <a:chExt cx="13005707" cy="4344006"/>
@@ -1876,13 +1937,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>550334</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>21168</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>120492</xdr:colOff>
-      <xdr:row>107</xdr:row>
+      <xdr:row>116</xdr:row>
       <xdr:rowOff>149982</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -1898,7 +1959,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="13260917" y="44037251"/>
+          <a:off x="13260917" y="51773668"/>
           <a:ext cx="6449325" cy="5420481"/>
           <a:chOff x="13260917" y="45497751"/>
           <a:chExt cx="6449325" cy="5420481"/>
@@ -2304,7 +2365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}">
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
@@ -2995,7 +3056,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A49" s="14" t="s">
         <v>44</v>
       </c>
@@ -3012,7 +3073,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A50" s="14" t="s">
         <v>44</v>
       </c>
@@ -3029,7 +3090,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A51" s="25" t="s">
         <v>4</v>
       </c>
@@ -3044,7 +3105,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A52" s="25" t="s">
         <v>4</v>
       </c>
@@ -3059,7 +3120,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="99" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" ht="99" x14ac:dyDescent="0.3">
       <c r="A53" s="25" t="s">
         <v>5</v>
       </c>
@@ -3074,7 +3135,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A54" s="25" t="s">
         <v>6</v>
       </c>
@@ -3091,7 +3152,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="99" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" ht="99" x14ac:dyDescent="0.3">
       <c r="A55" s="25" t="s">
         <v>6</v>
       </c>
@@ -3108,7 +3169,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A56" s="25" t="s">
         <v>6</v>
       </c>
@@ -3125,7 +3186,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A57" s="25" t="s">
         <v>44</v>
       </c>
@@ -3142,7 +3203,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="132" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" ht="132" x14ac:dyDescent="0.3">
       <c r="A58" s="25" t="s">
         <v>44</v>
       </c>
@@ -3159,7 +3220,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A59" s="25" t="s">
         <v>44</v>
       </c>
@@ -3176,101 +3237,316 @@
         <v>60</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="11" t="s">
+    <row r="60" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+      <c r="A60" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C60" s="14"/>
+      <c r="D60" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="E60" s="24"/>
+    </row>
+    <row r="61" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A61" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B61" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C61" s="14"/>
+      <c r="D61" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E61" s="24"/>
+    </row>
+    <row r="62" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A62" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C62" s="14"/>
+      <c r="D62" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E62" s="24"/>
+    </row>
+    <row r="63" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A63" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C63" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E63" s="24"/>
+    </row>
+    <row r="64" spans="1:5" ht="99" x14ac:dyDescent="0.3">
+      <c r="A64" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B64" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C64" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E64" s="24"/>
+    </row>
+    <row r="65" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A65" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C65" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="E65" s="24"/>
+    </row>
+    <row r="66" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A66" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C66" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E66" s="24"/>
+    </row>
+    <row r="67" spans="1:9" ht="148.5" x14ac:dyDescent="0.3">
+      <c r="A67" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B67" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C67" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="E67" s="24"/>
+    </row>
+    <row r="68" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A68" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B68" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="E68" s="24"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B60" s="18"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="19"/>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="11" t="s">
+      <c r="B69" s="18"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="19"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B61" s="18"/>
-      <c r="C61" s="18"/>
-      <c r="D61" s="20"/>
-      <c r="E61" s="21"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="22"/>
-      <c r="H61" s="22"/>
-      <c r="I61" s="22"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="18"/>
-      <c r="B62" s="18"/>
-      <c r="C62" s="18"/>
-      <c r="D62" s="19"/>
-      <c r="E62" s="21"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22"/>
-      <c r="H62" s="22"/>
-      <c r="I62" s="22"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="18"/>
-      <c r="B63" s="18"/>
-      <c r="C63" s="18"/>
-      <c r="D63" s="19"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="22"/>
-      <c r="H63" s="22"/>
-      <c r="I63" s="22"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="18"/>
-      <c r="B64" s="18"/>
-      <c r="C64" s="18"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="22"/>
-      <c r="G64" s="22"/>
-      <c r="H64" s="22"/>
-      <c r="I64" s="22"/>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="18"/>
-      <c r="B65" s="18"/>
-      <c r="C65" s="18"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
-      <c r="H65" s="22"/>
-      <c r="I65" s="22"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" s="18"/>
-      <c r="B66" s="18"/>
-      <c r="C66" s="18"/>
-      <c r="D66" s="19"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="22"/>
-      <c r="G66" s="22"/>
-      <c r="H66" s="22"/>
-      <c r="I66" s="22"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="18"/>
-      <c r="B67" s="18"/>
-      <c r="C67" s="18"/>
-      <c r="D67" s="19"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22"/>
-      <c r="H67" s="22"/>
-      <c r="I67" s="22"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="20"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="22"/>
+      <c r="I70" s="22"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A71" s="18"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="19"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A72" s="18"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="18"/>
+      <c r="D72" s="19"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="22"/>
+      <c r="G72" s="22"/>
+      <c r="H72" s="22"/>
+      <c r="I72" s="22"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A73" s="18"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="22"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A74" s="18"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="19"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="22"/>
+      <c r="G74" s="22"/>
+      <c r="H74" s="22"/>
+      <c r="I74" s="22"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A75" s="18"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="19"/>
+      <c r="E75" s="21"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A76" s="18"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="19"/>
+      <c r="E76" s="21"/>
+      <c r="F76" s="22"/>
+      <c r="G76" s="22"/>
+      <c r="H76" s="22"/>
+      <c r="I76" s="22"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" s="18"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="19"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A78" s="18"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="18"/>
+      <c r="D78" s="19"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A79" s="18"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="18"/>
+      <c r="D79" s="19"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A80" s="18"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="18"/>
+      <c r="D80" s="19"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="18"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="18"/>
+      <c r="D81" s="19"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="27"/>
-      <c r="D82" s="1" t="s">
+      <c r="A82" s="18"/>
+      <c r="B82" s="18"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="19"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="18"/>
+      <c r="B83" s="18"/>
+      <c r="C83" s="18"/>
+      <c r="D83" s="19"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" s="18"/>
+      <c r="B84" s="18"/>
+      <c r="C84" s="18"/>
+      <c r="D84" s="19"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" s="18"/>
+      <c r="B85" s="18"/>
+      <c r="C85" s="18"/>
+      <c r="D85" s="19"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="18"/>
+      <c r="B86" s="18"/>
+      <c r="C86" s="18"/>
+      <c r="D86" s="19"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="18"/>
+      <c r="B87" s="18"/>
+      <c r="C87" s="18"/>
+      <c r="D87" s="19"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" s="18"/>
+      <c r="B88" s="18"/>
+      <c r="C88" s="18"/>
+      <c r="D88" s="19"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" s="18"/>
+      <c r="B89" s="18"/>
+      <c r="C89" s="18"/>
+      <c r="D89" s="19"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" s="18"/>
+      <c r="B90" s="18"/>
+      <c r="C90" s="18"/>
+      <c r="D90" s="19"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" s="27"/>
+      <c r="B91" s="18"/>
+      <c r="C91" s="18"/>
+      <c r="D91" s="19" t="s">
         <v>70</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D61" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}"/>
+  <autoFilter ref="A1:D70" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{904A9398-C4A1-4A88-9A8A-8C50E6DEF234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D23EA2-AD41-4F3E-A650-E0E35F2E4770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="7860" yWindow="4770" windowWidth="21600" windowHeight="11295" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -613,34 +613,12 @@
     <t>9월</t>
   </si>
   <si>
-    <t>예산 대비 실적 집행률: 합계 2,277백만(94%), 본사 1,721백만(95%), 법인 555백만(89%)
- - 법인: 8월 HBR 704백만(tax credit 매각 수수료, Ciro 성공보수) → 9월 32백만으로 집행률 204% → 89%</t>
-  </si>
-  <si>
     <t>9월 누계</t>
   </si>
   <si>
     <t>예산 대비 실적 집행률: 합계 23,463백만(100%), 본사 16,644백만(94%), 법인 6,819백만(118%)
  - 예산 초과: HUMAX(공통) 138%(HBR 지급수수료, 합병 자문·평가 수수료 등), EVCS(국내) 107%
  - 예산 미집행: STB 97%, EVCS(해외) 89%, 건물 61%(1Q 94%, 2Q 41%, 3Q 49%)</t>
-  </si>
-  <si>
-    <t>예산 대비 실적 집행률: 합계 10,603백만(94%), 본사 7,997백만(93%), 법인 2,606백만(97%)
-국내/해외 비중: 1Q 국내 24%/해외 76%, 2Q 국내 29%/해외 71%, 3Q 국내 28%/해외 72%
- - 개발 그룹 리소스 투입 변화: 해외→국내</t>
-  </si>
-  <si>
-    <t>[지급수수료]
-외주개발용역비 누계 260백만(집행률 33%) — 예산 대비 522백만 미집행 (New Aura/iWedia SW이슈로 지연)
-Charter Legal fee/B&amp;M 9월 64백만 추가 집행 (누계 270백만, 소송 진행)</t>
-  </si>
-  <si>
-    <t>[인건비]
-주식보상비용 250백만 집행 (예산 외, 일회성)
-[지급수수료]
-HBR 누계 1,201백만(집행률 312%) — 8월 703백만, 9월 32백만
-합병 자문·평가 수수료 누계 557백만 집행 (1월 10백만, 4월 15백만, 7월 350백만, 8월 131백만, 9월 51백만)
-특허처리비 누계 111백만(예산 8백만) 초과 집행 (VVC 예산 누락 영향)</t>
   </si>
   <si>
     <t>1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만 → 9월 149백만
@@ -653,6 +631,37 @@
 1~5월 평균 476백만 대비 6월 60백만, 7월 45백만, 9월 59백만 초과 · 8월 66백만 하회
  - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만, 8월 79백만, 9월 64백만 집행 (누계 270백만)
  - HUS 8월 의료보험료 환급 -52백만, 유급휴가 충당금 회수 -28백만, 급여 -26백만 (2Q 7명 → 3Q 5명)</t>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 2,277백만(94%), 본사 1,721백만(95%), 법인 555백만(89%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[지급수수료]
+외주개발용역비 누계 260백만(집행률 33%) — 예산 대비 522백만 미집행 (New Aura/iWedia SW이슈로 지연)
+Charter Legal fee/B&amp;M 9월 64백만 추가 집행 (누계 270백만, 예산 외)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[인건비]
+주식보상비용 250백만 집행 (예산 외, 일회성)
+[지급수수료]
+HBR 누계 1,201백만(집행률 312%) — 8월 703백만(tax credit 매각 수수료 650백만, Ciro 성공보수 54백만), 9월 32백만
+합병 자문·평가 수수료 누계 557백만 집행 (1월 10백만, 4월 15백만, 7월 350백만, 8월 131백만, 9월 51백만)
+특허처리비 누계 103백만 초과 집행 (VVC 예산 누락 영향)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 10,603백만(94%), 본사 7,997백만(93%), 법인 2,606백만(97%)
+국내/해외 비중: 1Q 국내 24%/해외 76%, 2Q 국내 29%/해외 71%, 3Q 국내 28%/해외 72%
+ - 개발 그룹 리소스 투입 변화: 해외→국내 (국내 VAS 기준 및 PnC 개발 업무 증가)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분기별 추이: 1Q 월평균 278백만 → 2Q 월평균 126백만 → 3Q 월평균 152백만
+ - 4월~: 분당 감가상각비 163백만 → 분당 임차료 월 45백만
+ - 7월~: 티맥스수내타워 임대차 관리비 29백만(총 58백만) 신규 반영</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>일회성 증가 항목
@@ -662,20 +671,15 @@
 *(참고) 잔금 1억 (KB증권, 합병기일 후)
  - 8월: HBR Artur 세액공제 매각 중개수수료 650백만, HBR CTJ 법정 대표자 보수 54백만, 홀딩스 합병 자문 수수료 131백만
 *(참고) 잔금 Artur 670백만, CTJ 45백만
- - 9월: 합병 관련 수수료 51백만 (법무법인 광장, 보현회계법인, 한국예탁결제원)
-1~6월 평균 611백만 대비 7월 269백만, 8월 747백만 초과 · 9월 79백만 하회</t>
-  </si>
-  <si>
-    <t>계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만 → 9월 149백만
- - 4월~: 분당 감가상각비 163백만 → 분당 임차료 월 45백만
- - 7월~: 티맥스수내타워 임대차 관리비 29백만(총 58백만) 신규 반영</t>
+ - 9월: 합병 관련 수수료 51백만 (법무법인 광장, 보현회계법인, 한국예탁결제원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1504,8 +1508,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="222250" y="51646667"/>
-          <a:ext cx="13005707" cy="4344006"/>
+          <a:off x="222250" y="51302709"/>
+          <a:ext cx="13001474" cy="4299556"/>
           <a:chOff x="179917" y="45603583"/>
           <a:chExt cx="13005707" cy="4344006"/>
         </a:xfrm>
@@ -1959,8 +1963,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="13260917" y="51773668"/>
-          <a:ext cx="6449325" cy="5420481"/>
+          <a:off x="13256684" y="51427593"/>
+          <a:ext cx="6428158" cy="5367564"/>
           <a:chOff x="13260917" y="45497751"/>
           <a:chExt cx="6449325" cy="5420481"/>
         </a:xfrm>
@@ -2366,7 +2370,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}">
   <dimension ref="A1:I91"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
     <col min="2" max="2" width="12.625" customWidth="1"/>
@@ -2375,7 +2379,7 @@
     <col min="5" max="5" width="9" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2389,7 +2393,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="49.5">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -2401,7 +2405,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="49.5">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -2413,7 +2417,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="49.5">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -2425,7 +2429,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="33">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -2439,7 +2443,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="49.5">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -2453,7 +2457,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="33">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -2467,7 +2471,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="49.5">
       <c r="A8" s="5" t="s">
         <v>4</v>
       </c>
@@ -2479,7 +2483,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="49.5">
       <c r="A9" s="5" t="s">
         <v>4</v>
       </c>
@@ -2491,7 +2495,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="49.5">
       <c r="A10" s="5" t="s">
         <v>5</v>
       </c>
@@ -2503,7 +2507,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="33">
       <c r="A11" s="5" t="s">
         <v>6</v>
       </c>
@@ -2517,7 +2521,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="49.5">
       <c r="A12" s="5" t="s">
         <v>6</v>
       </c>
@@ -2531,7 +2535,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="33">
       <c r="A13" s="5" t="s">
         <v>6</v>
       </c>
@@ -2545,7 +2549,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="49.5">
       <c r="A14" s="4" t="s">
         <v>4</v>
       </c>
@@ -2557,7 +2561,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="49.5">
       <c r="A15" s="4" t="s">
         <v>4</v>
       </c>
@@ -2569,7 +2573,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="49.5">
       <c r="A16" s="4" t="s">
         <v>5</v>
       </c>
@@ -2581,7 +2585,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="33">
       <c r="A17" s="4" t="s">
         <v>6</v>
       </c>
@@ -2595,7 +2599,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="49.5">
       <c r="A18" s="4" t="s">
         <v>6</v>
       </c>
@@ -2609,7 +2613,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="33">
       <c r="A19" s="4" t="s">
         <v>6</v>
       </c>
@@ -2623,7 +2627,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="49.5">
       <c r="A20" s="5" t="s">
         <v>4</v>
       </c>
@@ -2635,7 +2639,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="49.5">
       <c r="A21" s="5" t="s">
         <v>4</v>
       </c>
@@ -2647,7 +2651,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="49.5">
       <c r="A22" s="5" t="s">
         <v>5</v>
       </c>
@@ -2659,7 +2663,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="49.5">
       <c r="A23" s="5" t="s">
         <v>6</v>
       </c>
@@ -2673,7 +2677,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="49.5">
       <c r="A24" s="5" t="s">
         <v>6</v>
       </c>
@@ -2687,7 +2691,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="49.5">
       <c r="A25" s="5" t="s">
         <v>6</v>
       </c>
@@ -2701,7 +2705,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="49.5">
       <c r="A26" s="4" t="s">
         <v>4</v>
       </c>
@@ -2713,7 +2717,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="49.5">
       <c r="A27" s="4" t="s">
         <v>4</v>
       </c>
@@ -2725,7 +2729,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="49.5">
       <c r="A28" s="4" t="s">
         <v>5</v>
       </c>
@@ -2737,7 +2741,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="49.5">
       <c r="A29" s="4" t="s">
         <v>6</v>
       </c>
@@ -2751,7 +2755,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="49.5">
       <c r="A30" s="4" t="s">
         <v>6</v>
       </c>
@@ -2765,7 +2769,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="49.5">
       <c r="A31" s="4" t="s">
         <v>6</v>
       </c>
@@ -2779,7 +2783,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
         <v>4</v>
       </c>
@@ -2794,7 +2798,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="49.5">
       <c r="A33" s="5" t="s">
         <v>4</v>
       </c>
@@ -2809,7 +2813,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="49.5">
       <c r="A34" s="5" t="s">
         <v>5</v>
       </c>
@@ -2824,7 +2828,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="33">
       <c r="A35" s="5" t="s">
         <v>6</v>
       </c>
@@ -2841,7 +2845,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" ht="66">
       <c r="A36" s="5" t="s">
         <v>6</v>
       </c>
@@ -2858,7 +2862,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="99" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="99">
       <c r="A37" s="5" t="s">
         <v>6</v>
       </c>
@@ -2875,7 +2879,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="33">
       <c r="A38" s="5" t="s">
         <v>45</v>
       </c>
@@ -2892,7 +2896,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" ht="66">
       <c r="A39" s="5" t="s">
         <v>44</v>
       </c>
@@ -2909,7 +2913,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="33">
       <c r="A40" s="5" t="s">
         <v>44</v>
       </c>
@@ -2926,7 +2930,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" ht="33">
       <c r="A41" s="5" t="s">
         <v>44</v>
       </c>
@@ -2943,7 +2947,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5">
       <c r="A42" s="14" t="s">
         <v>4</v>
       </c>
@@ -2958,7 +2962,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" ht="49.5">
       <c r="A43" s="14" t="s">
         <v>4</v>
       </c>
@@ -2973,7 +2977,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" ht="49.5">
       <c r="A44" s="14" t="s">
         <v>5</v>
       </c>
@@ -2988,7 +2992,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" ht="49.5">
       <c r="A45" s="14" t="s">
         <v>6</v>
       </c>
@@ -3005,7 +3009,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="99" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" ht="99">
       <c r="A46" s="14" t="s">
         <v>6</v>
       </c>
@@ -3022,7 +3026,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" ht="49.5">
       <c r="A47" s="14" t="s">
         <v>6</v>
       </c>
@@ -3039,7 +3043,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" ht="66">
       <c r="A48" s="14" t="s">
         <v>44</v>
       </c>
@@ -3056,7 +3060,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" ht="82.5">
       <c r="A49" s="14" t="s">
         <v>44</v>
       </c>
@@ -3073,7 +3077,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" ht="49.5">
       <c r="A50" s="14" t="s">
         <v>44</v>
       </c>
@@ -3090,7 +3094,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" ht="49.5">
       <c r="A51" s="25" t="s">
         <v>4</v>
       </c>
@@ -3105,7 +3109,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" ht="49.5">
       <c r="A52" s="25" t="s">
         <v>4</v>
       </c>
@@ -3120,7 +3124,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="99" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" ht="99">
       <c r="A53" s="25" t="s">
         <v>5</v>
       </c>
@@ -3135,7 +3139,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="49.5">
       <c r="A54" s="25" t="s">
         <v>6</v>
       </c>
@@ -3152,7 +3156,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="99" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" ht="99">
       <c r="A55" s="25" t="s">
         <v>6</v>
       </c>
@@ -3169,7 +3173,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" ht="82.5">
       <c r="A56" s="25" t="s">
         <v>6</v>
       </c>
@@ -3186,7 +3190,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" ht="82.5">
       <c r="A57" s="25" t="s">
         <v>44</v>
       </c>
@@ -3203,7 +3207,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="132" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" ht="132">
       <c r="A58" s="25" t="s">
         <v>44</v>
       </c>
@@ -3220,7 +3224,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" ht="49.5">
       <c r="A59" s="25" t="s">
         <v>44</v>
       </c>
@@ -3237,7 +3241,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5">
       <c r="A60" s="14" t="s">
         <v>4</v>
       </c>
@@ -3246,127 +3250,127 @@
       </c>
       <c r="C60" s="14"/>
       <c r="D60" s="15" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E60" s="24"/>
     </row>
-    <row r="61" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" ht="49.5">
       <c r="A61" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C61" s="14"/>
       <c r="D61" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E61" s="24"/>
     </row>
-    <row r="62" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" ht="49.5">
       <c r="A62" s="14" t="s">
         <v>5</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="15" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E62" s="24"/>
     </row>
-    <row r="63" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" ht="49.5">
       <c r="A63" s="14" t="s">
         <v>6</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C63" s="14" t="s">
         <v>7</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E63" s="24"/>
     </row>
-    <row r="64" spans="1:5" ht="99" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" ht="99">
       <c r="A64" s="14" t="s">
         <v>6</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C64" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E64" s="24"/>
     </row>
-    <row r="65" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" ht="49.5">
       <c r="A65" s="14" t="s">
         <v>6</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C65" s="14" t="s">
         <v>9</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E65" s="24"/>
     </row>
-    <row r="66" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" ht="82.5">
       <c r="A66" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C66" s="14" t="s">
         <v>7</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E66" s="24"/>
     </row>
-    <row r="67" spans="1:9" ht="148.5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" ht="132">
       <c r="A67" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C67" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E67" s="24"/>
     </row>
-    <row r="68" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" ht="49.5">
       <c r="A68" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C68" s="14" t="s">
         <v>9</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E68" s="24"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9">
       <c r="A69" s="11" t="s">
         <v>36</v>
       </c>
@@ -3374,7 +3378,7 @@
       <c r="C69" s="18"/>
       <c r="D69" s="19"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9">
       <c r="A70" s="11" t="s">
         <v>35</v>
       </c>
@@ -3387,7 +3391,7 @@
       <c r="H70" s="22"/>
       <c r="I70" s="22"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9">
       <c r="A71" s="18"/>
       <c r="B71" s="18"/>
       <c r="C71" s="18"/>
@@ -3398,7 +3402,7 @@
       <c r="H71" s="22"/>
       <c r="I71" s="22"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9">
       <c r="A72" s="18"/>
       <c r="B72" s="18"/>
       <c r="C72" s="18"/>
@@ -3409,7 +3413,7 @@
       <c r="H72" s="22"/>
       <c r="I72" s="22"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9">
       <c r="A73" s="18"/>
       <c r="B73" s="18"/>
       <c r="C73" s="18"/>
@@ -3420,7 +3424,7 @@
       <c r="H73" s="22"/>
       <c r="I73" s="22"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9">
       <c r="A74" s="18"/>
       <c r="B74" s="18"/>
       <c r="C74" s="18"/>
@@ -3431,7 +3435,7 @@
       <c r="H74" s="22"/>
       <c r="I74" s="22"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9">
       <c r="A75" s="18"/>
       <c r="B75" s="18"/>
       <c r="C75" s="18"/>
@@ -3442,7 +3446,7 @@
       <c r="H75" s="22"/>
       <c r="I75" s="22"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9">
       <c r="A76" s="18"/>
       <c r="B76" s="18"/>
       <c r="C76" s="18"/>
@@ -3453,91 +3457,91 @@
       <c r="H76" s="22"/>
       <c r="I76" s="22"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9">
       <c r="A77" s="18"/>
       <c r="B77" s="18"/>
       <c r="C77" s="18"/>
       <c r="D77" s="19"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9">
       <c r="A78" s="18"/>
       <c r="B78" s="18"/>
       <c r="C78" s="18"/>
       <c r="D78" s="19"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9">
       <c r="A79" s="18"/>
       <c r="B79" s="18"/>
       <c r="C79" s="18"/>
       <c r="D79" s="19"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9">
       <c r="A80" s="18"/>
       <c r="B80" s="18"/>
       <c r="C80" s="18"/>
       <c r="D80" s="19"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4">
       <c r="A81" s="18"/>
       <c r="B81" s="18"/>
       <c r="C81" s="18"/>
       <c r="D81" s="19"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4">
       <c r="A82" s="18"/>
       <c r="B82" s="18"/>
       <c r="C82" s="18"/>
       <c r="D82" s="19"/>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4">
       <c r="A83" s="18"/>
       <c r="B83" s="18"/>
       <c r="C83" s="18"/>
       <c r="D83" s="19"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4">
       <c r="A84" s="18"/>
       <c r="B84" s="18"/>
       <c r="C84" s="18"/>
       <c r="D84" s="19"/>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4">
       <c r="A85" s="18"/>
       <c r="B85" s="18"/>
       <c r="C85" s="18"/>
       <c r="D85" s="19"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4">
       <c r="A86" s="18"/>
       <c r="B86" s="18"/>
       <c r="C86" s="18"/>
       <c r="D86" s="19"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4">
       <c r="A87" s="18"/>
       <c r="B87" s="18"/>
       <c r="C87" s="18"/>
       <c r="D87" s="19"/>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4">
       <c r="A88" s="18"/>
       <c r="B88" s="18"/>
       <c r="C88" s="18"/>
       <c r="D88" s="19"/>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4">
       <c r="A89" s="18"/>
       <c r="B89" s="18"/>
       <c r="C89" s="18"/>
       <c r="D89" s="19"/>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4">
       <c r="A90" s="18"/>
       <c r="B90" s="18"/>
       <c r="C90" s="18"/>
       <c r="D90" s="19"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4">
       <c r="A91" s="27"/>
       <c r="B91" s="18"/>
       <c r="C91" s="18"/>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D23EA2-AD41-4F3E-A650-E0E35F2E4770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031840C9-91B8-43B9-9006-7E288BD31DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -626,13 +626,6 @@
  - 7월: 티맥스수내타워 관리비 집행 시작 · 8~9월 동일 구조 유지</t>
   </si>
   <si>
-    <t>4월, 5월 트렌드 왜곡
- - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
-1~5월 평균 476백만 대비 6월 60백만, 7월 45백만, 9월 59백만 초과 · 8월 66백만 하회
- - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만, 8월 79백만, 9월 64백만 집행 (누계 270백만)
- - HUS 8월 의료보험료 환급 -52백만, 유급휴가 충당금 회수 -28백만, 급여 -26백만 (2Q 7명 → 3Q 5명)</t>
-  </si>
-  <si>
     <t>예산 대비 실적 집행률: 합계 2,277백만(94%), 본사 1,721백만(95%), 법인 555백만(89%)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -664,14 +657,24 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>일회성 증가 항목
+    <t>7월, 8월, 9월 합병 자문·평가 수수료
+ - 7월 350백만 (KB증권, 이촌회계법인)
+ - 8월 131백만 (홀딩스 합병 자문)
+ - 9월 51백만 (법무법인 광장 36백만, 보현회계법인 착수금 15백만)
+*(참고) 누계 557백만 (1월 10백만, 4월 15백만 포함) · 잔금 1억 (KB증권, 합병기일 후)
+그 외 일회성 증가 항목
  - 1월: 26년 외부감사 착수금 200백만
  - 3월, 5월: 주식보상비용 3월 34백만, 5월 216백만
- - 7월: 합병 자문·평가 수수료 350백만 (KB증권, 이촌회계법인)
-*(참고) 잔금 1억 (KB증권, 합병기일 후)
- - 8월: HBR Artur 세액공제 매각 중개수수료 650백만, HBR CTJ 법정 대표자 보수 54백만, 홀딩스 합병 자문 수수료 131백만
-*(참고) 잔금 Artur 670백만, CTJ 45백만
- - 9월: 합병 관련 수수료 51백만 (법무법인 광장, 보현회계법인, 한국예탁결제원)</t>
+ - 8월: HBR Artur 세액공제 매각 중개수수료 650백만, HBR CTJ 법정 대표자 보수 54백만
+*(참고) 잔금 Artur 670백만, CTJ 45백만</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4월, 5월 트렌드 왜곡
+ - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
+일회성 증감 항목
+ - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만, 8월 79백만, 9월 64백만 집행 (누계 270백만)
+ - HUS 8월 의료보험료 환급 -52백만, 유급휴가 충당금 회수 -28백만, 급여 -26백만 (2Q 7명 → 3Q 5명)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1508,7 +1511,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="222250" y="51302709"/>
+          <a:off x="222250" y="51721809"/>
           <a:ext cx="13001474" cy="4299556"/>
           <a:chOff x="179917" y="45603583"/>
           <a:chExt cx="13005707" cy="4344006"/>
@@ -1963,7 +1966,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="13256684" y="51427593"/>
+          <a:off x="13256684" y="51846693"/>
           <a:ext cx="6428158" cy="5367564"/>
           <a:chOff x="13260917" y="45497751"/>
           <a:chExt cx="6449325" cy="5420481"/>
@@ -3250,7 +3253,7 @@
       </c>
       <c r="C60" s="14"/>
       <c r="D60" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E60" s="24"/>
     </row>
@@ -3276,7 +3279,7 @@
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E62" s="24"/>
     </row>
@@ -3291,7 +3294,7 @@
         <v>7</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E63" s="24"/>
     </row>
@@ -3306,7 +3309,7 @@
         <v>8</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E64" s="24"/>
     </row>
@@ -3336,11 +3339,11 @@
         <v>7</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E66" s="24"/>
     </row>
-    <row r="67" spans="1:9" ht="132">
+    <row r="67" spans="1:9" ht="165">
       <c r="A67" s="14" t="s">
         <v>44</v>
       </c>
@@ -3351,7 +3354,7 @@
         <v>8</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E67" s="24"/>
     </row>
@@ -3366,7 +3369,7 @@
         <v>9</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E68" s="24"/>
     </row>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031840C9-91B8-43B9-9006-7E288BD31DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2A5ECA-607C-4FD0-97A1-B56338796A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -657,24 +657,24 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>7월, 8월, 9월 합병 자문·평가 수수료
+    <t>4월, 5월 트렌드 왜곡
+ - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
+일회성 증감 항목
+ - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만, 8월 79백만, 9월 64백만 집행 (누계 270백만)
+ - HUS 8월 의료보험료 환급 -52백만, 유급휴가 충당금 회수 -28백만, 급여 -26백만 (2Q 7명 → 3Q 5명)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>합병 자문·평가 수수료 누계 557백만
  - 7월 350백만 (KB증권, 이촌회계법인)
  - 8월 131백만 (홀딩스 합병 자문)
  - 9월 51백만 (법무법인 광장 36백만, 보현회계법인 착수금 15백만)
-*(참고) 누계 557백만 (1월 10백만, 4월 15백만 포함) · 잔금 1억 (KB증권, 합병기일 후)
+*(참고) 잔금 1억 (KB증권, 합병기일 후)
 그 외 일회성 증가 항목
  - 1월: 26년 외부감사 착수금 200백만
  - 3월, 5월: 주식보상비용 3월 34백만, 5월 216백만
  - 8월: HBR Artur 세액공제 매각 중개수수료 650백만, HBR CTJ 법정 대표자 보수 54백만
 *(참고) 잔금 Artur 670백만, CTJ 45백만</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4월, 5월 트렌드 왜곡
- - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
-일회성 증감 항목
- - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만, 8월 79백만, 9월 64백만 집행 (누계 270백만)
- - HUS 8월 의료보험료 환급 -52백만, 유급휴가 충당금 회수 -28백만, 급여 -26백만 (2Q 7명 → 3Q 5명)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3339,7 +3339,7 @@
         <v>7</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E66" s="24"/>
     </row>
@@ -3354,7 +3354,7 @@
         <v>8</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E67" s="24"/>
     </row>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2A5ECA-607C-4FD0-97A1-B56338796A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3463384F-74EB-43E0-BE05-7E0FDDBA0781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -630,12 +630,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[지급수수료]
-외주개발용역비 누계 260백만(집행률 33%) — 예산 대비 522백만 미집행 (New Aura/iWedia SW이슈로 지연)
-Charter Legal fee/B&amp;M 9월 64백만 추가 집행 (누계 270백만, 예산 외)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[인건비]
 주식보상비용 250백만 집행 (예산 외, 일회성)
 [지급수수료]
@@ -675,6 +669,12 @@
  - 3월, 5월: 주식보상비용 3월 34백만, 5월 216백만
  - 8월: HBR Artur 세액공제 매각 중개수수료 650백만, HBR CTJ 법정 대표자 보수 54백만
 *(참고) 잔금 Artur 670백만, CTJ 45백만</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[지급수수료]
+외주개발용역비 누계 260백만(집행률 33%) — 예산 대비 522백만 미집행 (New Aura/iWedia SW이슈로 지연)
+Charter Legal fee/B&amp;M 누계 270백만 집행 (6월 72백만, 7월 55백만, 8월 79백만, 9월 64백만) — 예산 외</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E62" s="24"/>
     </row>
@@ -3294,7 +3294,7 @@
         <v>7</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E63" s="24"/>
     </row>
@@ -3309,7 +3309,7 @@
         <v>8</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E64" s="24"/>
     </row>
@@ -3339,7 +3339,7 @@
         <v>7</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E66" s="24"/>
     </row>
@@ -3354,7 +3354,7 @@
         <v>8</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E67" s="24"/>
     </row>
@@ -3369,7 +3369,7 @@
         <v>9</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E68" s="24"/>
     </row>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3463384F-74EB-43E0-BE05-7E0FDDBA0781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E7A41B-29CD-4305-88D1-F83031D003EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -528,14 +528,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4월, 5월 트렌드 왜곡
- - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
-1~5월 평균 476백만 대비 6월 60백만, 7월 45백만 초과 · 8월 66백만 하회
- - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만, 8월 79백만 집행 (누계 206백만)
- - HUS 8월 의료보험료 환급 -52백만, 유급휴가 충당금 회수 -28백만, 급여 -26백만 (2Q 7명 → 3Q 5명)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만
  - 4월: 한화 임대차계약 체결로 구조 변경
  - 7월: 티맥스수내타워 관리비 집행 시작</t>
@@ -648,14 +640,6 @@
     <t>분기별 추이: 1Q 월평균 278백만 → 2Q 월평균 126백만 → 3Q 월평균 152백만
  - 4월~: 분당 감가상각비 163백만 → 분당 임차료 월 45백만
  - 7월~: 티맥스수내타워 임대차 관리비 29백만(총 58백만) 신규 반영</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4월, 5월 트렌드 왜곡
- - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
-일회성 증감 항목
- - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만, 8월 79백만, 9월 64백만 집행 (누계 270백만)
- - HUS 8월 의료보험료 환급 -52백만, 유급휴가 충당금 회수 -28백만, 급여 -26백만 (2Q 7명 → 3Q 5명)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -675,6 +659,24 @@
     <t>[지급수수료]
 외주개발용역비 누계 260백만(집행률 33%) — 예산 대비 522백만 미집행 (New Aura/iWedia SW이슈로 지연)
 Charter Legal fee/B&amp;M 누계 270백만 집행 (6월 72백만, 7월 55백만, 8월 79백만, 9월 64백만) — 예산 외</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4월, 5월 트렌드 왜곡
+ - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
+일회성 증감 항목
+ - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만, 8월 79백만, 9월 64백만 집행 (누계 270백만)
+ - HUS 8월 의료보험료 환급 -52백만, 유급휴가 충당금 회수 -28백만
+ - HUS 급여 2Q 월평균 59백만 → 3Q 월평균 55백만 (2Q 7명 → 3Q 5명)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4월, 5월 트렌드 왜곡
+ - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
+일회성 증감 항목
+ - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만, 8월 79백만 집행 (누계 206백만)
+ - HUS 8월 의료보험료 환급 -52백만, 유급휴가 충당금 회수 -28백만
+ - HUS 급여 8월 45백만 (2Q 월평균 59백만) — 2Q 7명 → 3Q 5명</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1511,7 +1513,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="222250" y="51721809"/>
+          <a:off x="222250" y="52140909"/>
           <a:ext cx="13001474" cy="4299556"/>
           <a:chOff x="179917" y="45603583"/>
           <a:chExt cx="13005707" cy="4344006"/>
@@ -1966,7 +1968,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="13256684" y="51846693"/>
+          <a:off x="13256684" y="52265793"/>
           <a:ext cx="6428158" cy="5367564"/>
           <a:chOff x="13260917" y="45497751"/>
           <a:chExt cx="6449325" cy="5420481"/>
@@ -2573,7 +2575,7 @@
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="49.5">
@@ -2651,7 +2653,7 @@
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="49.5">
@@ -2729,7 +2731,7 @@
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="49.5">
@@ -2810,7 +2812,7 @@
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E33" s="13" t="s">
         <v>46</v>
@@ -2974,7 +2976,7 @@
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E43" s="13" t="s">
         <v>54</v>
@@ -3006,7 +3008,7 @@
         <v>7</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E45" s="13" t="s">
         <v>58</v>
@@ -3040,7 +3042,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E47" s="13" t="s">
         <v>59</v>
@@ -3106,7 +3108,7 @@
       </c>
       <c r="C51" s="25"/>
       <c r="D51" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E51" s="24" t="s">
         <v>54</v>
@@ -3121,7 +3123,7 @@
       </c>
       <c r="C52" s="25"/>
       <c r="D52" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E52" s="24" t="s">
         <v>54</v>
@@ -3153,7 +3155,7 @@
         <v>7</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E54" s="24" t="s">
         <v>58</v>
@@ -3170,7 +3172,7 @@
         <v>8</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E55" s="24" t="s">
         <v>58</v>
@@ -3187,13 +3189,13 @@
         <v>9</v>
       </c>
       <c r="D56" s="26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E56" s="24" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="82.5">
+    <row r="57" spans="1:5" ht="99">
       <c r="A57" s="25" t="s">
         <v>44</v>
       </c>
@@ -3204,7 +3206,7 @@
         <v>7</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="E57" s="24" t="s">
         <v>60</v>
@@ -3249,11 +3251,11 @@
         <v>4</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C60" s="14"/>
       <c r="D60" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E60" s="24"/>
     </row>
@@ -3262,11 +3264,11 @@
         <v>4</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C61" s="14"/>
       <c r="D61" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E61" s="24"/>
     </row>
@@ -3275,11 +3277,11 @@
         <v>5</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E62" s="24"/>
     </row>
@@ -3288,13 +3290,13 @@
         <v>6</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C63" s="14" t="s">
         <v>7</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E63" s="24"/>
     </row>
@@ -3303,13 +3305,13 @@
         <v>6</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C64" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E64" s="24"/>
     </row>
@@ -3318,28 +3320,28 @@
         <v>6</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C65" s="14" t="s">
         <v>9</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E65" s="24"/>
     </row>
-    <row r="66" spans="1:9" ht="82.5">
+    <row r="66" spans="1:9" ht="99">
       <c r="A66" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C66" s="14" t="s">
         <v>7</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E66" s="24"/>
     </row>
@@ -3348,13 +3350,13 @@
         <v>44</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C67" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E67" s="24"/>
     </row>
@@ -3363,13 +3365,13 @@
         <v>44</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C68" s="14" t="s">
         <v>9</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E68" s="24"/>
     </row>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E7A41B-29CD-4305-88D1-F83031D003EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DF8EED-3BFF-44C3-8315-2D516A53EF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -608,35 +608,6 @@
     <t>9월 누계</t>
   </si>
   <si>
-    <t>예산 대비 실적 집행률: 합계 23,463백만(100%), 본사 16,644백만(94%), 법인 6,819백만(118%)
- - 예산 초과: HUMAX(공통) 138%(HBR 지급수수료, 합병 자문·평가 수수료 등), EVCS(국내) 107%
- - 예산 미집행: STB 97%, EVCS(해외) 89%, 건물 61%(1Q 94%, 2Q 41%, 3Q 49%)</t>
-  </si>
-  <si>
-    <t>1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만 → 9월 149백만
- - 4월: 한화 임대차계약 체결로 구조 변경
- - 7월: 티맥스수내타워 관리비 집행 시작 · 8~9월 동일 구조 유지</t>
-  </si>
-  <si>
-    <t>예산 대비 실적 집행률: 합계 2,277백만(94%), 본사 1,721백만(95%), 법인 555백만(89%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[인건비]
-주식보상비용 250백만 집행 (예산 외, 일회성)
-[지급수수료]
-HBR 누계 1,201백만(집행률 312%) — 8월 703백만(tax credit 매각 수수료 650백만, Ciro 성공보수 54백만), 9월 32백만
-합병 자문·평가 수수료 누계 557백만 집행 (1월 10백만, 4월 15백만, 7월 350백만, 8월 131백만, 9월 51백만)
-특허처리비 누계 103백만 초과 집행 (VVC 예산 누락 영향)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>예산 대비 실적 집행률: 합계 10,603백만(94%), 본사 7,997백만(93%), 법인 2,606백만(97%)
-국내/해외 비중: 1Q 국내 24%/해외 76%, 2Q 국내 29%/해외 71%, 3Q 국내 28%/해외 72%
- - 개발 그룹 리소스 투입 변화: 해외→국내 (국내 VAS 기준 및 PnC 개발 업무 증가)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>분기별 추이: 1Q 월평균 278백만 → 2Q 월평균 126백만 → 3Q 월평균 152백만
  - 4월~: 분당 감가상각비 163백만 → 분당 임차료 월 45백만
  - 7월~: 티맥스수내타워 임대차 관리비 29백만(총 58백만) 신규 반영</t>
@@ -677,6 +648,37 @@
  - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만, 8월 79백만 집행 (누계 206백만)
  - HUS 8월 의료보험료 환급 -52백만, 유급휴가 충당금 회수 -28백만
  - HUS 급여 8월 45백만 (2Q 월평균 59백만) — 2Q 7명 → 3Q 5명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 2,277백만(94%), 본사 1,722백만(96%), 법인 555백만(89%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 23,463백만(100%), 본사 16,644백만(94%), 법인 6,819백만(118%)
+ - 예산 초과: HUMAX(공통) 138%(HBR 지급수수료, 합병 자문·평가 수수료 등), EVCS(국내) 107%
+ - 예산 미집행: STB 97%, EVCS(해외) 90%, 건물 61%(1Q 94%, 2Q 41%, 3Q 49%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 10,606백만(94%), 본사 8,000백만(93%), 법인 2,606백만(97%)
+국내/해외 비중: 1Q 국내 24%/해외 76%, 2Q 국내 29%/해외 71%, 3Q 국내 28%/해외 72%
+ - 개발 그룹 리소스 투입 변화: 해외→국내 (국내 VAS 기준 및 PnC 개발 업무 증가)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[인건비]
+주식보상비용 250백만 집행 (예산 외, 일회성)
+[지급수수료]
+HBR 누계 1,201백만(집행률 312%) — 8월 734백만(tax credit 매각 수수료 650백만, Ciro 성공보수 54백만 등), 9월 32백만
+합병 자문·평가 수수료 누계 557백만 집행 (1월 10백만, 4월 15백만, 7월 350백만, 8월 131백만, 9월 51백만)
+특허처리비 누계 103백만 초과 집행 (VVC 예산 누락 영향)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만 → 9월 150백만
+ - 4월: 한화 임대차계약 체결로 구조 변경
+ - 7월: 티맥스수내타워 관리비 집행 시작 · 8~9월 동일 구조 유지</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3206,7 +3208,7 @@
         <v>7</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E57" s="24" t="s">
         <v>60</v>
@@ -3255,7 +3257,7 @@
       </c>
       <c r="C60" s="14"/>
       <c r="D60" s="15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E60" s="24"/>
     </row>
@@ -3268,7 +3270,7 @@
       </c>
       <c r="C61" s="14"/>
       <c r="D61" s="15" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E61" s="24"/>
     </row>
@@ -3281,7 +3283,7 @@
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="15" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E62" s="24"/>
     </row>
@@ -3296,7 +3298,7 @@
         <v>7</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E63" s="24"/>
     </row>
@@ -3311,7 +3313,7 @@
         <v>8</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E64" s="24"/>
     </row>
@@ -3326,7 +3328,7 @@
         <v>9</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="E65" s="24"/>
     </row>
@@ -3341,7 +3343,7 @@
         <v>7</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E66" s="24"/>
     </row>
@@ -3356,7 +3358,7 @@
         <v>8</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E67" s="24"/>
     </row>
@@ -3371,7 +3373,7 @@
         <v>9</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E68" s="24"/>
     </row>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DF8EED-3BFF-44C3-8315-2D516A53EF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A7A42E-46CC-4965-B4BB-6EBEB1F491FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -655,12 +655,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>예산 대비 실적 집행률: 합계 23,463백만(100%), 본사 16,644백만(94%), 법인 6,819백만(118%)
- - 예산 초과: HUMAX(공통) 138%(HBR 지급수수료, 합병 자문·평가 수수료 등), EVCS(국내) 107%
- - 예산 미집행: STB 97%, EVCS(해외) 90%, 건물 61%(1Q 94%, 2Q 41%, 3Q 49%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>예산 대비 실적 집행률: 합계 10,606백만(94%), 본사 8,000백만(93%), 법인 2,606백만(97%)
 국내/해외 비중: 1Q 국내 24%/해외 76%, 2Q 국내 29%/해외 71%, 3Q 국내 28%/해외 72%
  - 개발 그룹 리소스 투입 변화: 해외→국내 (국내 VAS 기준 및 PnC 개발 업무 증가)</t>
@@ -679,6 +673,17 @@
     <t>1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만 → 9월 150백만
  - 4월: 한화 임대차계약 체결로 구조 변경
  - 7월: 티맥스수내타워 관리비 집행 시작 · 8~9월 동일 구조 유지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 23,463백만(100%), 본사 16,644백만(94%), 법인 6,819백만(118%)
+ - 예산 초과: HUMAX(공통) 138%(HBR 지급수수료, 합병 자문·평가 수수료 등), EVCS(국내) 107%
+ - 예산 미집행: STB 97%, EVCS(해외) 90%, 건물 61%(1Q 94%, 2Q 41%, 3Q 49%)
+본사 예산 대비 1,082백만 미달 · 법인 1,038백만 초과
+ - 본사: 건물 1,067, EVCS(해외) 819, STB 327 미달 — HUMAX(공통) 923, EVCS(국내) 193 초과로 상계
+ - 본사 예산 외·초과 집행 1,162백만 제외 시 실질 미달 2,244백만
+*합병·상장 수수료 539, Charter Legal fee 270, 주식보상비용 250, 특허처리비 103
+ - 법인: HBR 817 초과(tax credit 매각 수수료 650, Ciro 성공보수 54) · STB 171, MOBILITY 119</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1515,7 +1520,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="222250" y="52140909"/>
+          <a:off x="222250" y="53188659"/>
           <a:ext cx="13001474" cy="4299556"/>
           <a:chOff x="179917" y="45603583"/>
           <a:chExt cx="13005707" cy="4344006"/>
@@ -1970,7 +1975,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="13256684" y="52265793"/>
+          <a:off x="13256684" y="53313543"/>
           <a:ext cx="6428158" cy="5367564"/>
           <a:chOff x="13260917" y="45497751"/>
           <a:chExt cx="6449325" cy="5420481"/>
@@ -3261,7 +3266,7 @@
       </c>
       <c r="E60" s="24"/>
     </row>
-    <row r="61" spans="1:5" ht="49.5">
+    <row r="61" spans="1:5" ht="132">
       <c r="A61" s="14" t="s">
         <v>4</v>
       </c>
@@ -3270,7 +3275,7 @@
       </c>
       <c r="C61" s="14"/>
       <c r="D61" s="15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E61" s="24"/>
     </row>
@@ -3283,7 +3288,7 @@
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E62" s="24"/>
     </row>
@@ -3313,7 +3318,7 @@
         <v>8</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E64" s="24"/>
     </row>
@@ -3328,7 +3333,7 @@
         <v>9</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E65" s="24"/>
     </row>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A7A42E-46CC-4965-B4BB-6EBEB1F491FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE53E92-CE6A-4113-B113-89D4E94EF0F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="보류(10월 반영)" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$1:$D$70</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="138">
   <si>
     <t>탭</t>
   </si>
@@ -655,6 +656,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>예산 대비 실적 집행률: 합계 23,463백만(100%), 본사 16,644백만(94%), 법인 6,819백만(118%)
+ - 예산 초과: HUMAX(공통) 138%(HBR 지급수수료, 합병 자문·평가 수수료 등), EVCS(국내) 107%
+ - 예산 미집행: STB 97%, EVCS(해외) 90%, 건물 61%(1Q 94%, 2Q 41%, 3Q 49%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>예산 대비 실적 집행률: 합계 10,606백만(94%), 본사 8,000백만(93%), 법인 2,606백만(97%)
 국내/해외 비중: 1Q 국내 24%/해외 76%, 2Q 국내 29%/해외 71%, 3Q 국내 28%/해외 72%
  - 개발 그룹 리소스 투입 변화: 해외→국내 (국내 VAS 기준 및 PnC 개발 업무 증가)</t>
@@ -676,15 +683,89 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>예산 대비 실적 집행률: 합계 23,463백만(100%), 본사 16,644백만(94%), 법인 6,819백만(118%)
- - 예산 초과: HUMAX(공통) 138%(HBR 지급수수료, 합병 자문·평가 수수료 등), EVCS(국내) 107%
- - 예산 미집행: STB 97%, EVCS(해외) 90%, 건물 61%(1Q 94%, 2Q 41%, 3Q 49%)
-본사 예산 대비 1,082백만 미달 · 법인 1,038백만 초과
+    <t>항목</t>
+  </si>
+  <si>
+    <t>내용</t>
+  </si>
+  <si>
+    <t>반영 시점</t>
+  </si>
+  <si>
+    <t>10월 보고부터 (사장님 지시). 그때 아래 문구를 'Humax합계 / N월 누계' 행 끝에 붙인다.</t>
+  </si>
+  <si>
+    <t>넣을 자리</t>
+  </si>
+  <si>
+    <t>첫 번째 시트 · 탭 Humax합계 · 기간 N월 누계 (9월 기준으로는 61행)</t>
+  </si>
+  <si>
+    <t>문구 (9월 기준)</t>
+  </si>
+  <si>
+    <t>본사 예산 대비 1,082백만 미달 · 법인 1,038백만 초과
  - 본사: 건물 1,067, EVCS(해외) 819, STB 327 미달 — HUMAX(공통) 923, EVCS(국내) 193 초과로 상계
  - 본사 예산 외·초과 집행 1,162백만 제외 시 실질 미달 2,244백만
 *합병·상장 수수료 539, Charter Legal fee 270, 주식보상비용 250, 특허처리비 103
  - 법인: HBR 817 초과(tax credit 매각 수수료 650, Ciro 성공보수 54) · STB 171, MOBILITY 119</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[산출 기준] 미달·초과액</t>
+  </si>
+  <si>
+    <t>본사 = 누계 예산 − 누계 실적 (A+B 배부 기준). 9월: 17,726 − 16,644 = 1,082 / 법인: 6,819 − 5,781 = 1,038</t>
+  </si>
+  <si>
+    <t>[산출 기준] 항목별</t>
+  </si>
+  <si>
+    <t>본사·법인 각각 STB·MOBILITY·EVCS(국내)·EVCS(해외)·HUMAX(공통)·건물로 쪼개 실적−예산</t>
+  </si>
+  <si>
+    <t>[산출 기준] 예산 외·초과</t>
+  </si>
+  <si>
+    <t>26BP에 없던 건과 예산을 넘긴 건만 더한다. 9월 기준 4건 = 1,162백만</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 합병·상장 수수료</t>
+  </si>
+  <si>
+    <t>539 — memo에 '합병'이 들어간 건 + 한국거래소 변경상장수수료. 4~9월</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · Charter Legal fee/B&amp;M</t>
+  </si>
+  <si>
+    <t>270 — 거래처 Bird &amp; Marella. 6~9월. 예산 없음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 주식보상비용</t>
+  </si>
+  <si>
+    <t>250 — 소계정 (판관)주식보상비용. 3·5월. 예산 없음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 특허처리비</t>
+  </si>
+  <si>
+    <t>103 — 실적 111 − 예산 8</t>
+  </si>
+  <si>
+    <t>[제외한 것]</t>
+  </si>
+  <si>
+    <t>외부감사 수수료(누계 586)처럼 26BP에 예산이 잡혀 있는 항목은 넣지 않는다</t>
+  </si>
+  <si>
+    <t>[주의] 인쇄</t>
+  </si>
+  <si>
+    <t>이 4줄을 넣으면 1번 시트가 626 → 680px가 된다. 한 페이지 한계는 702px이라 여유 22px뿐 —</t>
+  </si>
+  <si>
+    <t>한 줄 더 붙일 일이 생기면 위쪽 '예산 초과 / 예산 미집행' 두 줄을 줄여야 한다</t>
   </si>
 </sst>
 </file>
@@ -852,7 +933,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -936,6 +1017,12 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1520,7 +1607,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="222250" y="53188659"/>
+          <a:off x="222250" y="52140909"/>
           <a:ext cx="13001474" cy="4299556"/>
           <a:chOff x="179917" y="45603583"/>
           <a:chExt cx="13005707" cy="4344006"/>
@@ -1975,7 +2062,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="13256684" y="53313543"/>
+          <a:off x="13256684" y="52265793"/>
           <a:ext cx="6428158" cy="5367564"/>
           <a:chOff x="13260917" y="45497751"/>
           <a:chExt cx="6449325" cy="5420481"/>
@@ -3266,7 +3353,7 @@
       </c>
       <c r="E60" s="24"/>
     </row>
-    <row r="61" spans="1:5" ht="132">
+    <row r="61" spans="1:5" ht="49.5">
       <c r="A61" s="14" t="s">
         <v>4</v>
       </c>
@@ -3275,7 +3362,7 @@
       </c>
       <c r="C61" s="14"/>
       <c r="D61" s="15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E61" s="24"/>
     </row>
@@ -3288,7 +3375,7 @@
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E62" s="24"/>
     </row>
@@ -3318,7 +3405,7 @@
         <v>8</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E64" s="24"/>
     </row>
@@ -3333,7 +3420,7 @@
         <v>9</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E65" s="24"/>
     </row>
@@ -3568,4 +3655,131 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{840A5107-8D41-4CE9-9495-60E7B9563011}">
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
+    <col min="2" max="2" width="110.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="28" customFormat="1">
+      <c r="A1" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="181.5">
+      <c r="A2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="132">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="409.5">
+      <c r="A4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="B5" s="1"/>
+    </row>
+    <row r="6" spans="1:2" ht="198">
+      <c r="A6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="198">
+      <c r="A7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="132">
+      <c r="A8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="132">
+      <c r="A9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="99">
+      <c r="A10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="99">
+      <c r="A11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="49.5">
+      <c r="A12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="132">
+      <c r="A13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="181.5">
+      <c r="A14" t="s">
+        <v>135</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="148.5">
+      <c r="B15" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE53E92-CE6A-4113-B113-89D4E94EF0F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99F4B17-F892-46BD-AB46-38CE6DB7577C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -704,68 +704,70 @@
     <t>문구 (9월 기준)</t>
   </si>
   <si>
-    <t>본사 예산 대비 1,082백만 미달 · 법인 1,038백만 초과
- - 본사: 건물 1,067, EVCS(해외) 819, STB 327 미달 — HUMAX(공통) 923, EVCS(국내) 193 초과로 상계
- - 본사 예산 외·초과 집행 1,162백만 제외 시 실질 미달 2,244백만
+    <t>본사 = 누계 예산 − 누계 실적 (A+B 배부 기준). 9월: 17,726 − 16,644 = 1,082 / 법인: 6,819 − 5,781 = 1,038</t>
+  </si>
+  <si>
+    <t>[산출 기준] 항목별</t>
+  </si>
+  <si>
+    <t>본사·법인 각각 STB·MOBILITY·EVCS(국내)·EVCS(해외)·HUMAX(공통)·건물로 쪼개 실적−예산</t>
+  </si>
+  <si>
+    <t>[산출 기준] 예산 외·초과</t>
+  </si>
+  <si>
+    <t>26BP에 없던 건과 예산을 넘긴 건만 더한다. 9월 기준 4건 = 1,162백만</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 합병·상장 수수료</t>
+  </si>
+  <si>
+    <t>539 — memo에 '합병'이 들어간 건 + 한국거래소 변경상장수수료. 4~9월</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · Charter Legal fee/B&amp;M</t>
+  </si>
+  <si>
+    <t>270 — 거래처 Bird &amp; Marella. 6~9월. 예산 없음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 주식보상비용</t>
+  </si>
+  <si>
+    <t>250 — 소계정 (판관)주식보상비용. 3·5월. 예산 없음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 특허처리비</t>
+  </si>
+  <si>
+    <t>103 — 실적 111 − 예산 8</t>
+  </si>
+  <si>
+    <t>[제외한 것]</t>
+  </si>
+  <si>
+    <t>외부감사 수수료(누계 586)처럼 26BP에 예산이 잡혀 있는 항목은 넣지 않는다</t>
+  </si>
+  <si>
+    <t>[주의] 인쇄</t>
+  </si>
+  <si>
+    <t>이 4줄을 넣으면 1번 시트가 626 → 680px가 된다. 한 페이지 한계는 702px이라 여유 22px뿐 —</t>
+  </si>
+  <si>
+    <t>한 줄 더 붙일 일이 생기면 위쪽 '예산 초과 / 예산 미집행' 두 줄을 줄여야 한다</t>
+  </si>
+  <si>
+    <t>본사 예산 대비 1,082백만 미집행 · 법인 1,038백만 초과
+ - 본사: 건물 1,067, EVCS(해외) 819, STB 327 미집행 — HUMAX(공통) 923, EVCS(국내) 193 초과로 상계
+ - 본사 예산 외·초과 집행 1,162백만 제외 시 실질 미집행 2,244백만
 *합병·상장 수수료 539, Charter Legal fee 270, 주식보상비용 250, 특허처리비 103
  - 법인: HBR 817 초과(tax credit 매각 수수료 650, Ciro 성공보수 54) · STB 171, MOBILITY 119</t>
-  </si>
-  <si>
-    <t>[산출 기준] 미달·초과액</t>
-  </si>
-  <si>
-    <t>본사 = 누계 예산 − 누계 실적 (A+B 배부 기준). 9월: 17,726 − 16,644 = 1,082 / 법인: 6,819 − 5,781 = 1,038</t>
-  </si>
-  <si>
-    <t>[산출 기준] 항목별</t>
-  </si>
-  <si>
-    <t>본사·법인 각각 STB·MOBILITY·EVCS(국내)·EVCS(해외)·HUMAX(공통)·건물로 쪼개 실적−예산</t>
-  </si>
-  <si>
-    <t>[산출 기준] 예산 외·초과</t>
-  </si>
-  <si>
-    <t>26BP에 없던 건과 예산을 넘긴 건만 더한다. 9월 기준 4건 = 1,162백만</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  · 합병·상장 수수료</t>
-  </si>
-  <si>
-    <t>539 — memo에 '합병'이 들어간 건 + 한국거래소 변경상장수수료. 4~9월</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  · Charter Legal fee/B&amp;M</t>
-  </si>
-  <si>
-    <t>270 — 거래처 Bird &amp; Marella. 6~9월. 예산 없음</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  · 주식보상비용</t>
-  </si>
-  <si>
-    <t>250 — 소계정 (판관)주식보상비용. 3·5월. 예산 없음</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  · 특허처리비</t>
-  </si>
-  <si>
-    <t>103 — 실적 111 − 예산 8</t>
-  </si>
-  <si>
-    <t>[제외한 것]</t>
-  </si>
-  <si>
-    <t>외부감사 수수료(누계 586)처럼 26BP에 예산이 잡혀 있는 항목은 넣지 않는다</t>
-  </si>
-  <si>
-    <t>[주의] 인쇄</t>
-  </si>
-  <si>
-    <t>이 4줄을 넣으면 1번 시트가 626 → 680px가 된다. 한 페이지 한계는 702px이라 여유 22px뿐 —</t>
-  </si>
-  <si>
-    <t>한 줄 더 붙일 일이 생기면 위쪽 '예산 초과 / 예산 미집행' 두 줄을 줄여야 한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[산출 기준] 미집행·초과액</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3690,12 +3692,12 @@
         <v>116</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.5">
+    <row r="4" spans="1:2" ht="82.5">
       <c r="A4" t="s">
         <v>117</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3703,79 +3705,79 @@
     </row>
     <row r="6" spans="1:2" ht="198">
       <c r="A6" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="198">
       <c r="A7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="132">
       <c r="A8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="132">
       <c r="A9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="99">
       <c r="A10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="99">
       <c r="A11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="49.5">
       <c r="A12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="132">
       <c r="A13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="181.5">
       <c r="A14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="148.5">
       <c r="B15" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99F4B17-F892-46BD-AB46-38CE6DB7577C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C968CA7E-BF19-4563-920E-BCC8AD7703F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="보류(10월 반영)" sheetId="2" r:id="rId2"/>
+    <sheet name="보류(10월 반영)" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$1:$D$70</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="151">
   <si>
     <t>탭</t>
   </si>
@@ -707,39 +707,6 @@
     <t>본사 = 누계 예산 − 누계 실적 (A+B 배부 기준). 9월: 17,726 − 16,644 = 1,082 / 법인: 6,819 − 5,781 = 1,038</t>
   </si>
   <si>
-    <t>[산출 기준] 항목별</t>
-  </si>
-  <si>
-    <t>본사·법인 각각 STB·MOBILITY·EVCS(국내)·EVCS(해외)·HUMAX(공통)·건물로 쪼개 실적−예산</t>
-  </si>
-  <si>
-    <t>[산출 기준] 예산 외·초과</t>
-  </si>
-  <si>
-    <t>26BP에 없던 건과 예산을 넘긴 건만 더한다. 9월 기준 4건 = 1,162백만</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  · 합병·상장 수수료</t>
-  </si>
-  <si>
-    <t>539 — memo에 '합병'이 들어간 건 + 한국거래소 변경상장수수료. 4~9월</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  · Charter Legal fee/B&amp;M</t>
-  </si>
-  <si>
-    <t>270 — 거래처 Bird &amp; Marella. 6~9월. 예산 없음</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  · 주식보상비용</t>
-  </si>
-  <si>
-    <t>250 — 소계정 (판관)주식보상비용. 3·5월. 예산 없음</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  · 특허처리비</t>
-  </si>
-  <si>
     <t>103 — 실적 111 − 예산 8</t>
   </si>
   <si>
@@ -752,22 +719,92 @@
     <t>[주의] 인쇄</t>
   </si>
   <si>
-    <t>이 4줄을 넣으면 1번 시트가 626 → 680px가 된다. 한 페이지 한계는 702px이라 여유 22px뿐 —</t>
-  </si>
-  <si>
-    <t>한 줄 더 붙일 일이 생기면 위쪽 '예산 초과 / 예산 미집행' 두 줄을 줄여야 한다</t>
-  </si>
-  <si>
     <t>본사 예산 대비 1,082백만 미집행 · 법인 1,038백만 초과
- - 본사: 건물 1,067, EVCS(해외) 819, STB 327 미집행 — HUMAX(공통) 923, EVCS(국내) 193 초과로 상계
- - 본사 예산 외·초과 집행 1,162백만 제외 시 실질 미집행 2,244백만
-*합병·상장 수수료 539, Charter Legal fee 270, 주식보상비용 250, 특허처리비 103
- - 법인: HBR 817 초과(tax credit 매각 수수료 650, Ciro 성공보수 54) · STB 171, MOBILITY 119</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[산출 기준] 미집행·초과액</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+ - 본사 예산 외·초과 집행 1,180백만 제외 시 실질 미집행 2,262백만
+*[초과] 합병 자문·평가 수수료 557백만, Charter B&amp;M Legal fee 270백만, 주식보상비용 250백만, 특허처리비 초과액 103백만
+*[미집행] New Aura/iWedia 518백만, 건물 배부액 1,067백만, 전시회참가비용 232백만, 사업그룹 여비교통비 159백만
+ - 법인: HBR 817백만 초과 (tax credit 매각 수수료 650백만, Ciro 성공보수 54백만), HUK 급여 238백만 초과</t>
+  </si>
+  <si>
+    <t>[산출] 미집행·초과액</t>
+  </si>
+  <si>
+    <t>[산출] 실질 미집행</t>
+  </si>
+  <si>
+    <t>미집행액 + 예산 외·초과 집행액. 9월: 1,082 + 1,180 = 2,262</t>
+  </si>
+  <si>
+    <t>[초과] 합병 자문·평가</t>
+  </si>
+  <si>
+    <t>557 — 1월 광장 10(25년 4Q 고문료), 4월 광장 15, 7월 KB증권 200+이촌 150,</t>
+  </si>
+  <si>
+    <t>8월 KB증권 100+선진인쇄 22+광장 9, 9월 광장 36+보현 15. 전부 HUMAX(공통) 100% 배부 = 전액 본사.</t>
+  </si>
+  <si>
+    <t>※ memo에 '합병'만으로 거르면 1·4월 광장 건(고문료/자문료)이 빠진다 — 광장 건은 전부 포함할 것</t>
+  </si>
+  <si>
+    <t>[초과] Charter B&amp;M</t>
+  </si>
+  <si>
+    <t>270 — 거래처 Bird &amp; Marella, 6~9월, STB 배부, 예산 없음</t>
+  </si>
+  <si>
+    <t>[초과] 주식보상비용</t>
+  </si>
+  <si>
+    <t>250 — 소계정 (판관)주식보상비용, 3·5월, 예산 없음</t>
+  </si>
+  <si>
+    <t>[초과] 특허처리비</t>
+  </si>
+  <si>
+    <t>[미집행] New Aura/iWedia</t>
+  </si>
+  <si>
+    <t>518 — 예산 쪽에서 본다. 26년 예산(BP) 거래처 iWedia, 9월 누계 예산 518.2(연간 810),</t>
+  </si>
+  <si>
+    <t>STB 100% 배부, 실적 0. ※ 실적 테이블에는 거래처가 없으므로 예산표를 봐야 한다</t>
+  </si>
+  <si>
+    <t>[미집행] 건물 배부액</t>
+  </si>
+  <si>
+    <t>1,067 — 본사 건물 예산 2,734 − 실적 1,667</t>
+  </si>
+  <si>
+    <t>[미집행] 전시회참가비용</t>
+  </si>
+  <si>
+    <t>232 — 9월 누계 예산 240 − 실적 8 (미집행액 기준으로 적는다)</t>
+  </si>
+  <si>
+    <t>[미집행] 사업그룹 여비교통비</t>
+  </si>
+  <si>
+    <t>159 — 9월 누계 예산 192 − 실적 34</t>
+  </si>
+  <si>
+    <t>[법인] HBR</t>
+  </si>
+  <si>
+    <t>817 — 누계 실적 1,201 − 예산 384</t>
+  </si>
+  <si>
+    <t>[법인] HUK 급여</t>
+  </si>
+  <si>
+    <t>238 — 누계 실적 1,854 − 예산 1,617 (집행률 115%, HDG 합산 기준)</t>
+  </si>
+  <si>
+    <t>4줄 기준 1번 시트가 626 → 680px. 한 페이지 한계 702px — 줄을 더 늘리려면 위쪽</t>
+  </si>
+  <si>
+    <t>예산 초과 / 예산 미집행' 두 줄을 줄여야 한다</t>
   </si>
 </sst>
 </file>
@@ -935,7 +972,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1024,6 +1061,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3660,8 +3700,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{840A5107-8D41-4CE9-9495-60E7B9563011}">
-  <dimension ref="A1:B15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DB64AB9-C938-41EE-BA0E-3A8B4B189A0F}">
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="22.625" customWidth="1"/>
@@ -3692,12 +3732,12 @@
         <v>116</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="82.5">
+    <row r="4" spans="1:2" ht="409.5">
       <c r="A4" t="s">
         <v>117</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3705,79 +3745,146 @@
     </row>
     <row r="6" spans="1:2" ht="198">
       <c r="A6" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="198">
+    <row r="7" spans="1:2" ht="115.5">
       <c r="A7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="B8" s="1"/>
+    </row>
+    <row r="9" spans="1:2" ht="148.5">
+      <c r="A9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="214.5">
+      <c r="B10" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="198">
+      <c r="B11" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="115.5">
+      <c r="A12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="99">
+      <c r="A13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="49.5">
+      <c r="A14" t="s">
+        <v>135</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B7" s="1" t="s">
+    </row>
+    <row r="15" spans="1:2">
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16" spans="1:2" ht="181.5">
+      <c r="A16" t="s">
+        <v>136</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="148.5">
+      <c r="B17" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="99">
+      <c r="A18" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="115.5">
+      <c r="A19" t="s">
+        <v>141</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="66">
+      <c r="A20" t="s">
+        <v>143</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="B21" s="1"/>
+    </row>
+    <row r="22" spans="1:2" ht="66">
+      <c r="A22" t="s">
+        <v>145</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="148.5">
+      <c r="A23" t="s">
+        <v>147</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="B24" s="1"/>
+    </row>
+    <row r="25" spans="1:2" ht="132">
+      <c r="A25" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="132">
-      <c r="A8" t="s">
+      <c r="B25" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B8" s="1" t="s">
+    </row>
+    <row r="26" spans="1:2" ht="148.5">
+      <c r="A26" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="132">
-      <c r="A9" t="s">
-        <v>123</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="99">
-      <c r="A10" t="s">
-        <v>125</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="99">
-      <c r="A11" t="s">
-        <v>127</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="49.5">
-      <c r="A12" t="s">
-        <v>129</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="132">
-      <c r="A13" t="s">
-        <v>131</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="181.5">
-      <c r="A14" t="s">
-        <v>133</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="148.5">
-      <c r="B15" s="1" t="s">
-        <v>135</v>
+      <c r="B26" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="82.5">
+      <c r="B27" s="30" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C968CA7E-BF19-4563-920E-BCC8AD7703F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F804CD8-7677-4C15-AE25-DD5762432C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -438,17 +438,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>일회성 증가 항목
- - 1월: 26년 외부감사 착수금 200백만
- - 3월, 5월: 주식보상비용 3월 34백만, 5월 216백만
- - 7월: 합병 자문·평가 수수료 350백만 (KB증권, 이촌회계법인)
-*(참고) 잔금 1억 (KB증권, 합병기일 후)
- - 8월: HBR Artur 세액공제 매각 중개수수료 650백만, HBR CTJ 법정 대표자 보수 54백만, 홀딩스 합병 자문 수수료 131백만
-*(참고) 잔금 Artur 670백만, CTJ 45백만
-1~6월 평균 611백만 대비 7월 269백만, 8월 747백만 초과</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>- 당월 실적 2,818백만(집행률 88%) — 예산 대비 미집행
 - 본사 2,020백만(집행률 83%) 미집행 주도 · 법인 798백만(집행률 102%) 예산 수준
 - STB 493백만(집행률 49%) 최저 · HUMAX(공통) 760백만 — 외부감사 착수금 200백만 반영</t>
@@ -612,6 +601,196 @@
     <t>분기별 추이: 1Q 월평균 278백만 → 2Q 월평균 126백만 → 3Q 월평균 152백만
  - 4월~: 분당 감가상각비 163백만 → 분당 임차료 월 45백만
  - 7월~: 티맥스수내타워 임대차 관리비 29백만(총 58백만) 신규 반영</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[지급수수료]
+외주개발용역비 누계 260백만(집행률 33%) — 예산 대비 522백만 미집행 (New Aura/iWedia SW이슈로 지연)
+Charter Legal fee/B&amp;M 누계 270백만 집행 (6월 72백만, 7월 55백만, 8월 79백만, 9월 64백만) — 예산 외</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4월, 5월 트렌드 왜곡
+ - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
+일회성 증감 항목
+ - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만, 8월 79백만, 9월 64백만 집행 (누계 270백만)
+ - HUS 8월 의료보험료 환급 -52백만, 유급휴가 충당금 회수 -28백만
+ - HUS 급여 2Q 월평균 59백만 → 3Q 월평균 55백만 (2Q 7명 → 3Q 5명)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4월, 5월 트렌드 왜곡
+ - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
+일회성 증감 항목
+ - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만, 8월 79백만 집행 (누계 206백만)
+ - HUS 8월 의료보험료 환급 -52백만, 유급휴가 충당금 회수 -28백만
+ - HUS 급여 8월 45백만 (2Q 월평균 59백만) — 2Q 7명 → 3Q 5명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 2,277백만(94%), 본사 1,722백만(96%), 법인 555백만(89%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 23,463백만(100%), 본사 16,644백만(94%), 법인 6,819백만(118%)
+ - 예산 초과: HUMAX(공통) 138%(HBR 지급수수료, 합병 자문·평가 수수료 등), EVCS(국내) 107%
+ - 예산 미집행: STB 97%, EVCS(해외) 90%, 건물 61%(1Q 94%, 2Q 41%, 3Q 49%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 10,606백만(94%), 본사 8,000백만(93%), 법인 2,606백만(97%)
+국내/해외 비중: 1Q 국내 24%/해외 76%, 2Q 국내 29%/해외 71%, 3Q 국내 28%/해외 72%
+ - 개발 그룹 리소스 투입 변화: 해외→국내 (국내 VAS 기준 및 PnC 개발 업무 증가)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[인건비]
+주식보상비용 250백만 집행 (예산 외, 일회성)
+[지급수수료]
+HBR 누계 1,201백만(집행률 312%) — 8월 734백만(tax credit 매각 수수료 650백만, Ciro 성공보수 54백만 등), 9월 32백만
+합병 자문·평가 수수료 누계 557백만 집행 (1월 10백만, 4월 15백만, 7월 350백만, 8월 131백만, 9월 51백만)
+특허처리비 누계 103백만 초과 집행 (VVC 예산 누락 영향)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만 → 9월 150백만
+ - 4월: 한화 임대차계약 체결로 구조 변경
+ - 7월: 티맥스수내타워 관리비 집행 시작 · 8~9월 동일 구조 유지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항목</t>
+  </si>
+  <si>
+    <t>내용</t>
+  </si>
+  <si>
+    <t>반영 시점</t>
+  </si>
+  <si>
+    <t>10월 보고부터 (사장님 지시). 그때 아래 문구를 'Humax합계 / N월 누계' 행 끝에 붙인다.</t>
+  </si>
+  <si>
+    <t>넣을 자리</t>
+  </si>
+  <si>
+    <t>첫 번째 시트 · 탭 Humax합계 · 기간 N월 누계 (9월 기준으로는 61행)</t>
+  </si>
+  <si>
+    <t>문구 (9월 기준)</t>
+  </si>
+  <si>
+    <t>본사 = 누계 예산 − 누계 실적 (A+B 배부 기준). 9월: 17,726 − 16,644 = 1,082 / 법인: 6,819 − 5,781 = 1,038</t>
+  </si>
+  <si>
+    <t>103 — 실적 111 − 예산 8</t>
+  </si>
+  <si>
+    <t>[제외한 것]</t>
+  </si>
+  <si>
+    <t>외부감사 수수료(누계 586)처럼 26BP에 예산이 잡혀 있는 항목은 넣지 않는다</t>
+  </si>
+  <si>
+    <t>[주의] 인쇄</t>
+  </si>
+  <si>
+    <t>본사 예산 대비 1,082백만 미집행 · 법인 1,038백만 초과
+ - 본사 예산 외·초과 집행 1,180백만 제외 시 실질 미집행 2,262백만
+*[초과] 합병 자문·평가 수수료 557백만, Charter B&amp;M Legal fee 270백만, 주식보상비용 250백만, 특허처리비 초과액 103백만
+*[미집행] New Aura/iWedia 518백만, 건물 배부액 1,067백만, 전시회참가비용 232백만, 사업그룹 여비교통비 159백만
+ - 법인: HBR 817백만 초과 (tax credit 매각 수수료 650백만, Ciro 성공보수 54백만), HUK 급여 238백만 초과</t>
+  </si>
+  <si>
+    <t>[산출] 미집행·초과액</t>
+  </si>
+  <si>
+    <t>[산출] 실질 미집행</t>
+  </si>
+  <si>
+    <t>미집행액 + 예산 외·초과 집행액. 9월: 1,082 + 1,180 = 2,262</t>
+  </si>
+  <si>
+    <t>[초과] 합병 자문·평가</t>
+  </si>
+  <si>
+    <t>557 — 1월 광장 10(25년 4Q 고문료), 4월 광장 15, 7월 KB증권 200+이촌 150,</t>
+  </si>
+  <si>
+    <t>8월 KB증권 100+선진인쇄 22+광장 9, 9월 광장 36+보현 15. 전부 HUMAX(공통) 100% 배부 = 전액 본사.</t>
+  </si>
+  <si>
+    <t>※ memo에 '합병'만으로 거르면 1·4월 광장 건(고문료/자문료)이 빠진다 — 광장 건은 전부 포함할 것</t>
+  </si>
+  <si>
+    <t>[초과] Charter B&amp;M</t>
+  </si>
+  <si>
+    <t>270 — 거래처 Bird &amp; Marella, 6~9월, STB 배부, 예산 없음</t>
+  </si>
+  <si>
+    <t>[초과] 주식보상비용</t>
+  </si>
+  <si>
+    <t>250 — 소계정 (판관)주식보상비용, 3·5월, 예산 없음</t>
+  </si>
+  <si>
+    <t>[초과] 특허처리비</t>
+  </si>
+  <si>
+    <t>[미집행] New Aura/iWedia</t>
+  </si>
+  <si>
+    <t>518 — 예산 쪽에서 본다. 26년 예산(BP) 거래처 iWedia, 9월 누계 예산 518.2(연간 810),</t>
+  </si>
+  <si>
+    <t>STB 100% 배부, 실적 0. ※ 실적 테이블에는 거래처가 없으므로 예산표를 봐야 한다</t>
+  </si>
+  <si>
+    <t>[미집행] 건물 배부액</t>
+  </si>
+  <si>
+    <t>1,067 — 본사 건물 예산 2,734 − 실적 1,667</t>
+  </si>
+  <si>
+    <t>[미집행] 전시회참가비용</t>
+  </si>
+  <si>
+    <t>232 — 9월 누계 예산 240 − 실적 8 (미집행액 기준으로 적는다)</t>
+  </si>
+  <si>
+    <t>[미집행] 사업그룹 여비교통비</t>
+  </si>
+  <si>
+    <t>159 — 9월 누계 예산 192 − 실적 34</t>
+  </si>
+  <si>
+    <t>[법인] HBR</t>
+  </si>
+  <si>
+    <t>817 — 누계 실적 1,201 − 예산 384</t>
+  </si>
+  <si>
+    <t>[법인] HUK 급여</t>
+  </si>
+  <si>
+    <t>238 — 누계 실적 1,854 − 예산 1,617 (집행률 115%, HDG 합산 기준)</t>
+  </si>
+  <si>
+    <t>4줄 기준 1번 시트가 626 → 680px. 한 페이지 한계 702px — 줄을 더 늘리려면 위쪽</t>
+  </si>
+  <si>
+    <t>예산 초과 / 예산 미집행' 두 줄을 줄여야 한다</t>
+  </si>
+  <si>
+    <t>일회성 증가 항목
+ - 1월: 26년 외부감사 착수금 200백만
+ - 3월, 5월: 주식보상비용 3월 34백만, 5월 216백만
+ - 7월: 합병 자문·평가 수수료 350백만 (KB증권, 이촌회계법인)
+*(참고) 잔금 1억 (KB증권, 합병기일 후)
+ - 8월: HBR tax credit 매각 수수료 650백만, Ciro 성공보수 54백만 등, 홀딩스 합병 자문 수수료 131백만
+*(참고) 잔금 tax credit 670백만, Ciro 45백만
+1~6월 평균 611백만 대비 7월 269백만, 8월 747백만 초과</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -623,188 +802,9 @@
 그 외 일회성 증가 항목
  - 1월: 26년 외부감사 착수금 200백만
  - 3월, 5월: 주식보상비용 3월 34백만, 5월 216백만
- - 8월: HBR Artur 세액공제 매각 중개수수료 650백만, HBR CTJ 법정 대표자 보수 54백만
-*(참고) 잔금 Artur 670백만, CTJ 45백만</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[지급수수료]
-외주개발용역비 누계 260백만(집행률 33%) — 예산 대비 522백만 미집행 (New Aura/iWedia SW이슈로 지연)
-Charter Legal fee/B&amp;M 누계 270백만 집행 (6월 72백만, 7월 55백만, 8월 79백만, 9월 64백만) — 예산 외</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4월, 5월 트렌드 왜곡
- - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
-일회성 증감 항목
- - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만, 8월 79백만, 9월 64백만 집행 (누계 270백만)
- - HUS 8월 의료보험료 환급 -52백만, 유급휴가 충당금 회수 -28백만
- - HUS 급여 2Q 월평균 59백만 → 3Q 월평균 55백만 (2Q 7명 → 3Q 5명)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4월, 5월 트렌드 왜곡
- - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
-일회성 증감 항목
- - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만, 8월 79백만 집행 (누계 206백만)
- - HUS 8월 의료보험료 환급 -52백만, 유급휴가 충당금 회수 -28백만
- - HUS 급여 8월 45백만 (2Q 월평균 59백만) — 2Q 7명 → 3Q 5명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>예산 대비 실적 집행률: 합계 2,277백만(94%), 본사 1,722백만(96%), 법인 555백만(89%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>예산 대비 실적 집행률: 합계 23,463백만(100%), 본사 16,644백만(94%), 법인 6,819백만(118%)
- - 예산 초과: HUMAX(공통) 138%(HBR 지급수수료, 합병 자문·평가 수수료 등), EVCS(국내) 107%
- - 예산 미집행: STB 97%, EVCS(해외) 90%, 건물 61%(1Q 94%, 2Q 41%, 3Q 49%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>예산 대비 실적 집행률: 합계 10,606백만(94%), 본사 8,000백만(93%), 법인 2,606백만(97%)
-국내/해외 비중: 1Q 국내 24%/해외 76%, 2Q 국내 29%/해외 71%, 3Q 국내 28%/해외 72%
- - 개발 그룹 리소스 투입 변화: 해외→국내 (국내 VAS 기준 및 PnC 개발 업무 증가)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[인건비]
-주식보상비용 250백만 집행 (예산 외, 일회성)
-[지급수수료]
-HBR 누계 1,201백만(집행률 312%) — 8월 734백만(tax credit 매각 수수료 650백만, Ciro 성공보수 54백만 등), 9월 32백만
-합병 자문·평가 수수료 누계 557백만 집행 (1월 10백만, 4월 15백만, 7월 350백만, 8월 131백만, 9월 51백만)
-특허처리비 누계 103백만 초과 집행 (VVC 예산 누락 영향)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만 → 9월 150백만
- - 4월: 한화 임대차계약 체결로 구조 변경
- - 7월: 티맥스수내타워 관리비 집행 시작 · 8~9월 동일 구조 유지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>항목</t>
-  </si>
-  <si>
-    <t>내용</t>
-  </si>
-  <si>
-    <t>반영 시점</t>
-  </si>
-  <si>
-    <t>10월 보고부터 (사장님 지시). 그때 아래 문구를 'Humax합계 / N월 누계' 행 끝에 붙인다.</t>
-  </si>
-  <si>
-    <t>넣을 자리</t>
-  </si>
-  <si>
-    <t>첫 번째 시트 · 탭 Humax합계 · 기간 N월 누계 (9월 기준으로는 61행)</t>
-  </si>
-  <si>
-    <t>문구 (9월 기준)</t>
-  </si>
-  <si>
-    <t>본사 = 누계 예산 − 누계 실적 (A+B 배부 기준). 9월: 17,726 − 16,644 = 1,082 / 법인: 6,819 − 5,781 = 1,038</t>
-  </si>
-  <si>
-    <t>103 — 실적 111 − 예산 8</t>
-  </si>
-  <si>
-    <t>[제외한 것]</t>
-  </si>
-  <si>
-    <t>외부감사 수수료(누계 586)처럼 26BP에 예산이 잡혀 있는 항목은 넣지 않는다</t>
-  </si>
-  <si>
-    <t>[주의] 인쇄</t>
-  </si>
-  <si>
-    <t>본사 예산 대비 1,082백만 미집행 · 법인 1,038백만 초과
- - 본사 예산 외·초과 집행 1,180백만 제외 시 실질 미집행 2,262백만
-*[초과] 합병 자문·평가 수수료 557백만, Charter B&amp;M Legal fee 270백만, 주식보상비용 250백만, 특허처리비 초과액 103백만
-*[미집행] New Aura/iWedia 518백만, 건물 배부액 1,067백만, 전시회참가비용 232백만, 사업그룹 여비교통비 159백만
- - 법인: HBR 817백만 초과 (tax credit 매각 수수료 650백만, Ciro 성공보수 54백만), HUK 급여 238백만 초과</t>
-  </si>
-  <si>
-    <t>[산출] 미집행·초과액</t>
-  </si>
-  <si>
-    <t>[산출] 실질 미집행</t>
-  </si>
-  <si>
-    <t>미집행액 + 예산 외·초과 집행액. 9월: 1,082 + 1,180 = 2,262</t>
-  </si>
-  <si>
-    <t>[초과] 합병 자문·평가</t>
-  </si>
-  <si>
-    <t>557 — 1월 광장 10(25년 4Q 고문료), 4월 광장 15, 7월 KB증권 200+이촌 150,</t>
-  </si>
-  <si>
-    <t>8월 KB증권 100+선진인쇄 22+광장 9, 9월 광장 36+보현 15. 전부 HUMAX(공통) 100% 배부 = 전액 본사.</t>
-  </si>
-  <si>
-    <t>※ memo에 '합병'만으로 거르면 1·4월 광장 건(고문료/자문료)이 빠진다 — 광장 건은 전부 포함할 것</t>
-  </si>
-  <si>
-    <t>[초과] Charter B&amp;M</t>
-  </si>
-  <si>
-    <t>270 — 거래처 Bird &amp; Marella, 6~9월, STB 배부, 예산 없음</t>
-  </si>
-  <si>
-    <t>[초과] 주식보상비용</t>
-  </si>
-  <si>
-    <t>250 — 소계정 (판관)주식보상비용, 3·5월, 예산 없음</t>
-  </si>
-  <si>
-    <t>[초과] 특허처리비</t>
-  </si>
-  <si>
-    <t>[미집행] New Aura/iWedia</t>
-  </si>
-  <si>
-    <t>518 — 예산 쪽에서 본다. 26년 예산(BP) 거래처 iWedia, 9월 누계 예산 518.2(연간 810),</t>
-  </si>
-  <si>
-    <t>STB 100% 배부, 실적 0. ※ 실적 테이블에는 거래처가 없으므로 예산표를 봐야 한다</t>
-  </si>
-  <si>
-    <t>[미집행] 건물 배부액</t>
-  </si>
-  <si>
-    <t>1,067 — 본사 건물 예산 2,734 − 실적 1,667</t>
-  </si>
-  <si>
-    <t>[미집행] 전시회참가비용</t>
-  </si>
-  <si>
-    <t>232 — 9월 누계 예산 240 − 실적 8 (미집행액 기준으로 적는다)</t>
-  </si>
-  <si>
-    <t>[미집행] 사업그룹 여비교통비</t>
-  </si>
-  <si>
-    <t>159 — 9월 누계 예산 192 − 실적 34</t>
-  </si>
-  <si>
-    <t>[법인] HBR</t>
-  </si>
-  <si>
-    <t>817 — 누계 실적 1,201 − 예산 384</t>
-  </si>
-  <si>
-    <t>[법인] HUK 급여</t>
-  </si>
-  <si>
-    <t>238 — 누계 실적 1,854 − 예산 1,617 (집행률 115%, HDG 합산 기준)</t>
-  </si>
-  <si>
-    <t>4줄 기준 1번 시트가 626 → 680px. 한 페이지 한계 702px — 줄을 더 늘리려면 위쪽</t>
-  </si>
-  <si>
-    <t>예산 초과 / 예산 미집행' 두 줄을 줄여야 한다</t>
+ - 8월: HBR tax credit 매각 수수료 650백만, Ciro 성공보수 54백만 등
+*(참고) 잔금 tax credit 670백만, Ciro 45백만</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="49.5">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="49.5">
@@ -2581,7 +2581,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="49.5">
@@ -2609,7 +2609,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="49.5">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="49.5">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="49.5">
@@ -2659,7 +2659,7 @@
         <v>7</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="49.5">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="49.5">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="49.5">
@@ -2737,7 +2737,7 @@
         <v>7</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="49.5">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="49.5">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="49.5">
@@ -2815,7 +2815,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="49.5">
@@ -2843,7 +2843,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="49.5">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="49.5">
@@ -2893,7 +2893,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="49.5">
@@ -2921,7 +2921,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E33" s="13" t="s">
         <v>46</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E43" s="13" t="s">
         <v>54</v>
@@ -3144,7 +3144,7 @@
         <v>7</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E45" s="13" t="s">
         <v>58</v>
@@ -3178,7 +3178,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E47" s="13" t="s">
         <v>59</v>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="C51" s="25"/>
       <c r="D51" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E51" s="24" t="s">
         <v>54</v>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="C52" s="25"/>
       <c r="D52" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E52" s="24" t="s">
         <v>54</v>
@@ -3291,7 +3291,7 @@
         <v>7</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E54" s="24" t="s">
         <v>58</v>
@@ -3308,7 +3308,7 @@
         <v>8</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E55" s="24" t="s">
         <v>58</v>
@@ -3325,7 +3325,7 @@
         <v>9</v>
       </c>
       <c r="D56" s="26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E56" s="24" t="s">
         <v>59</v>
@@ -3342,7 +3342,7 @@
         <v>7</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E57" s="24" t="s">
         <v>60</v>
@@ -3359,7 +3359,7 @@
         <v>8</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>72</v>
+        <v>149</v>
       </c>
       <c r="E58" s="24" t="s">
         <v>60</v>
@@ -3387,11 +3387,11 @@
         <v>4</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C60" s="14"/>
       <c r="D60" s="15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E60" s="24"/>
     </row>
@@ -3400,11 +3400,11 @@
         <v>4</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C61" s="14"/>
       <c r="D61" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E61" s="24"/>
     </row>
@@ -3413,11 +3413,11 @@
         <v>5</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E62" s="24"/>
     </row>
@@ -3426,13 +3426,13 @@
         <v>6</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C63" s="14" t="s">
         <v>7</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E63" s="24"/>
     </row>
@@ -3441,13 +3441,13 @@
         <v>6</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C64" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E64" s="24"/>
     </row>
@@ -3456,13 +3456,13 @@
         <v>6</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C65" s="14" t="s">
         <v>9</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E65" s="24"/>
     </row>
@@ -3471,13 +3471,13 @@
         <v>44</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C66" s="14" t="s">
         <v>7</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E66" s="24"/>
     </row>
@@ -3486,13 +3486,13 @@
         <v>44</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C67" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="E67" s="24"/>
     </row>
@@ -3501,13 +3501,13 @@
         <v>44</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C68" s="14" t="s">
         <v>9</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E68" s="24"/>
     </row>
@@ -3710,34 +3710,34 @@
   <sheetData>
     <row r="1" spans="1:2" s="28" customFormat="1">
       <c r="A1" s="28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="181.5">
       <c r="A2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="132">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="409.5">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3745,18 +3745,18 @@
     </row>
     <row r="6" spans="1:2" ht="198">
       <c r="A6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="115.5">
       <c r="A7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3764,44 +3764,44 @@
     </row>
     <row r="9" spans="1:2" ht="148.5">
       <c r="A9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="214.5">
       <c r="B10" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="198">
       <c r="B11" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="115.5">
       <c r="A12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="99">
       <c r="A13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="49.5">
       <c r="A14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3809,39 +3809,39 @@
     </row>
     <row r="16" spans="1:2" ht="181.5">
       <c r="A16" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="148.5">
       <c r="B17" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="99">
       <c r="A18" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="115.5">
       <c r="A19" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="66">
       <c r="A20" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3849,18 +3849,18 @@
     </row>
     <row r="22" spans="1:2" ht="66">
       <c r="A22" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="148.5">
       <c r="A23" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3868,23 +3868,23 @@
     </row>
     <row r="25" spans="1:2" ht="132">
       <c r="A25" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="148.5">
       <c r="A26" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="82.5">
       <c r="B27" s="30" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F804CD8-7677-4C15-AE25-DD5762432C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D345F707-1732-4B7B-AFF9-EC9F2B7688A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="보류(10월 반영)" sheetId="3" r:id="rId2"/>
+    <sheet name="보류(10월 반영)" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$1:$D$70</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="157">
   <si>
     <t>탭</t>
   </si>
@@ -668,21 +668,9 @@
     <t>반영 시점</t>
   </si>
   <si>
-    <t>10월 보고부터 (사장님 지시). 그때 아래 문구를 'Humax합계 / N월 누계' 행 끝에 붙인다.</t>
-  </si>
-  <si>
     <t>넣을 자리</t>
   </si>
   <si>
-    <t>첫 번째 시트 · 탭 Humax합계 · 기간 N월 누계 (9월 기준으로는 61행)</t>
-  </si>
-  <si>
-    <t>문구 (9월 기준)</t>
-  </si>
-  <si>
-    <t>본사 = 누계 예산 − 누계 실적 (A+B 배부 기준). 9월: 17,726 − 16,644 = 1,082 / 법인: 6,819 − 5,781 = 1,038</t>
-  </si>
-  <si>
     <t>103 — 실적 111 − 예산 8</t>
   </si>
   <si>
@@ -695,13 +683,6 @@
     <t>[주의] 인쇄</t>
   </si>
   <si>
-    <t>본사 예산 대비 1,082백만 미집행 · 법인 1,038백만 초과
- - 본사 예산 외·초과 집행 1,180백만 제외 시 실질 미집행 2,262백만
-*[초과] 합병 자문·평가 수수료 557백만, Charter B&amp;M Legal fee 270백만, 주식보상비용 250백만, 특허처리비 초과액 103백만
-*[미집행] New Aura/iWedia 518백만, 건물 배부액 1,067백만, 전시회참가비용 232백만, 사업그룹 여비교통비 159백만
- - 법인: HBR 817백만 초과 (tax credit 매각 수수료 650백만, Ciro 성공보수 54백만), HUK 급여 238백만 초과</t>
-  </si>
-  <si>
     <t>[산출] 미집행·초과액</t>
   </si>
   <si>
@@ -714,15 +695,6 @@
     <t>[초과] 합병 자문·평가</t>
   </si>
   <si>
-    <t>557 — 1월 광장 10(25년 4Q 고문료), 4월 광장 15, 7월 KB증권 200+이촌 150,</t>
-  </si>
-  <si>
-    <t>8월 KB증권 100+선진인쇄 22+광장 9, 9월 광장 36+보현 15. 전부 HUMAX(공통) 100% 배부 = 전액 본사.</t>
-  </si>
-  <si>
-    <t>※ memo에 '합병'만으로 거르면 1·4월 광장 건(고문료/자문료)이 빠진다 — 광장 건은 전부 포함할 것</t>
-  </si>
-  <si>
     <t>[초과] Charter B&amp;M</t>
   </si>
   <si>
@@ -732,33 +704,21 @@
     <t>[초과] 주식보상비용</t>
   </si>
   <si>
-    <t>250 — 소계정 (판관)주식보상비용, 3·5월, 예산 없음</t>
-  </si>
-  <si>
     <t>[초과] 특허처리비</t>
   </si>
   <si>
     <t>[미집행] New Aura/iWedia</t>
   </si>
   <si>
-    <t>518 — 예산 쪽에서 본다. 26년 예산(BP) 거래처 iWedia, 9월 누계 예산 518.2(연간 810),</t>
-  </si>
-  <si>
     <t>STB 100% 배부, 실적 0. ※ 실적 테이블에는 거래처가 없으므로 예산표를 봐야 한다</t>
   </si>
   <si>
     <t>[미집행] 건물 배부액</t>
   </si>
   <si>
-    <t>1,067 — 본사 건물 예산 2,734 − 실적 1,667</t>
-  </si>
-  <si>
     <t>[미집행] 전시회참가비용</t>
   </si>
   <si>
-    <t>232 — 9월 누계 예산 240 − 실적 8 (미집행액 기준으로 적는다)</t>
-  </si>
-  <si>
     <t>[미집행] 사업그룹 여비교통비</t>
   </si>
   <si>
@@ -768,16 +728,7 @@
     <t>[법인] HBR</t>
   </si>
   <si>
-    <t>817 — 누계 실적 1,201 − 예산 384</t>
-  </si>
-  <si>
     <t>[법인] HUK 급여</t>
-  </si>
-  <si>
-    <t>238 — 누계 실적 1,854 − 예산 1,617 (집행률 115%, HDG 합산 기준)</t>
-  </si>
-  <si>
-    <t>4줄 기준 1번 시트가 626 → 680px. 한 페이지 한계 702px — 줄을 더 늘리려면 위쪽</t>
   </si>
   <si>
     <t>예산 초과 / 예산 미집행' 두 줄을 줄여야 한다</t>
@@ -805,6 +756,79 @@
  - 8월: HBR tax credit 매각 수수료 650백만, Ciro 성공보수 54백만 등
 *(참고) 잔금 tax credit 670백만, Ciro 45백만</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10월 보고부터. 사용자가 따로 말하지 않아도 코멘트 갱신 시 자동 포함한다 (2026-10-22 지시).</t>
+  </si>
+  <si>
+    <t>첫 번째 시트 · 탭 Humax합계 · 기간 N월 누계 (9월 기준 61행) 끝에 이어 붙인다</t>
+  </si>
+  <si>
+    <t>대시보드 문구 (9월)</t>
+  </si>
+  <si>
+    <t>본사 예산 대비 1,082백만 미집행 · 법인 1,038백만 초과
+ - 본사 예산 외·초과 집행 1,180백만 고려 시 실질 미집행 2,262백만
+*[미집행] New Aura/iWedia 518백만, 건물 배부액 1,067백만(4월~: 계약 변경으로 수도광열비·감가상각비 등 감소), 전시회참가비용 232백만, 사업그룹 여비교통비 159백만
+*[초과] 합병 자문·평가 수수료 557백만, Charter B&amp;M Legal fee 270백만, 주식보상비용 250백만, 특허처리비 103백만
+ - 법인: HBR tax credit 매각 수수료 650백만, Ciro 성공보수 54백만, HUK 급여 238백만(Bonus 153백만)</t>
+  </si>
+  <si>
+    <t>메일 문구 (9월, 발송본)</t>
+  </si>
+  <si>
+    <t>Humax 9월 누계 실적 기준 특이사항은 아래와 같습니다.
+· 본사 16,644백만(94%)로 예산 대비 1,082백만 미집행
+  기존 초과 집행 금액 1,180백만 고려 시 실제 미집행 금액은 2,262백만 규모로 파악됩니다.
+  [미집행] New Aura/iWedia 518백만, 건물 배부액 1,067백만(4월~: 계약 변경으로 수도광열비, 감가상각비 등 감소), 전시회참가비용 232백만(신제품 출시 지연으로 미참가), 사업그룹 여비교통비 159백만
+  [초과] 합병 자문·평가 수수료 557백만, Charter B&amp;M Legal fee 270백만, 주식보상비용 250백만, 특허처리비 103백만
+· 법인 6,819백만(118%)로 예산 대비 1,038백만 초과 집행
+  [초과] HBR tax credit 매각 수수료 650백만, Ciro 성공보수 54백만, HUK 급여 238백만 (Bonus 153백만 포함: 실적 204백만, 예산 51백만)</t>
+  </si>
+  <si>
+    <t>누계 예산 − 누계 실적. (A+B) 배부 기준(계열사 배부 C는 제외), 본사/법인은 effectiveAllocHq 기준.</t>
+  </si>
+  <si>
+    <t>9월: 본사 17,726.4 − 16,644.0 = 1,082.4 (93.89%) / 법인 6,819.0 − 5,781.3 = 1,037.8 (117.95%)</t>
+  </si>
+  <si>
+    <t>557 — 1월 광장 10, 4월 광장 15, 7월 KB증권 200+이촌 150, 8월 KB증권 100+선진인쇄 22+광장 9,</t>
+  </si>
+  <si>
+    <t>9월 광장 36+보현 15. HUMAX(공통) 100% 배부 = 전액 본사.</t>
+  </si>
+  <si>
+    <t>※ memo '합병'만으로 거르면 1·4월 광장 건(고문료/자문료)이 빠진다 — 광장 건은 거래처로 거를 것</t>
+  </si>
+  <si>
+    <t>250 — (판관)주식보상비용, 3·5월, 예산 없음</t>
+  </si>
+  <si>
+    <t>518 — 예산표에서 본다. 26년 예산(BP) 거래처 iWedia, 9월 누계 예산 518.2(연간 810),</t>
+  </si>
+  <si>
+    <t>1,067 — 본사 건물 예산 2,734 − 실적 1,667. 월 278(1Q) → 126(2Q) → 152(3Q)</t>
+  </si>
+  <si>
+    <t>감가상각비 203 → 40 (4월~ 분당이 임차료 월 45로 전환, 용인 40은 계속) · 수도광열비 원장총액이</t>
+  </si>
+  <si>
+    <t>월 92~132 → 4~13으로 줄어 건물 배부도 사라짐 · 7월~ 티맥스수내타워 관리비로 지급수수료 +26</t>
+  </si>
+  <si>
+    <t>232 — 9월 누계 예산 240 − 실적 8. ※ '신제품 출시 지연' 사유는 원장 근거 없음(사용자 기재)</t>
+  </si>
+  <si>
+    <t>817 초과 — 누계 실적 1,201 − 예산 384. 8월 tax credit 매각 수수료 650, Ciro 성공보수 54</t>
+  </si>
+  <si>
+    <t>238 초과 — 실적 1,854 − 예산 1,617(115%). 상여금 실적 204 vs 예산 51 = 153이 대부분</t>
+  </si>
+  <si>
+    <t>1월 86(London/SK Seo Bonus), 2월 118(CS/London Bonus). 3월 이후는 예산에 붙어 있음</t>
+  </si>
+  <si>
+    <t>4줄 기준 1번 시트가 626 → 680px, 한 페이지 한계 702px. 줄을 더 늘리려면 위쪽</t>
   </si>
 </sst>
 </file>
@@ -3359,7 +3383,7 @@
         <v>8</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="E58" s="24" t="s">
         <v>60</v>
@@ -3492,7 +3516,7 @@
         <v>8</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="E67" s="24"/>
     </row>
@@ -3700,8 +3724,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DB64AB9-C938-41EE-BA0E-3A8B4B189A0F}">
-  <dimension ref="A1:B27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFD7736E-8B88-4FEA-8699-66433585A989}">
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="22.625" customWidth="1"/>
@@ -3716,175 +3740,203 @@
         <v>110</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="181.5">
+    <row r="2" spans="1:2" ht="165">
       <c r="A2" t="s">
         <v>111</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="148.5">
+      <c r="A3" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="132">
-      <c r="A3" t="s">
-        <v>113</v>
-      </c>
       <c r="B3" s="1" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="409.5">
       <c r="A4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="409.5">
+      <c r="A5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="B6" s="1"/>
+    </row>
+    <row r="7" spans="1:2" ht="181.5">
+      <c r="A7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="181.5">
+      <c r="B8" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="115.5">
+      <c r="A9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="B10" s="1"/>
+    </row>
+    <row r="11" spans="1:2" ht="181.5">
+      <c r="A11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="132">
+      <c r="B12" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="181.5">
+      <c r="B13" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="115.5">
+      <c r="A14" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="82.5">
+      <c r="A15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="49.5">
+      <c r="A16" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="B17" s="1"/>
+    </row>
+    <row r="18" spans="1:2" ht="181.5">
+      <c r="A18" t="s">
+        <v>125</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="148.5">
+      <c r="B19" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="181.5">
+      <c r="A20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="181.5">
+      <c r="B21" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="198">
+      <c r="B22" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="165">
+      <c r="A23" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="66">
+      <c r="A24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="B25" s="1"/>
+    </row>
+    <row r="26" spans="1:2" ht="181.5">
+      <c r="A26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="181.5">
+      <c r="A27" t="s">
+        <v>132</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="181.5">
+      <c r="B28" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="B29" s="1"/>
+    </row>
+    <row r="30" spans="1:2" ht="132">
+      <c r="A30" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="B5" s="1"/>
-    </row>
-    <row r="6" spans="1:2" ht="198">
-      <c r="A6" t="s">
-        <v>122</v>
-      </c>
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="31" spans="1:2" ht="148.5">
+      <c r="A31" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="115.5">
-      <c r="A7" t="s">
-        <v>123</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="B8" s="1"/>
-    </row>
-    <row r="9" spans="1:2" ht="148.5">
-      <c r="A9" t="s">
-        <v>125</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="214.5">
-      <c r="B10" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="198">
-      <c r="B11" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="115.5">
-      <c r="A12" t="s">
-        <v>129</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="99">
-      <c r="A13" t="s">
-        <v>131</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="49.5">
-      <c r="A14" t="s">
+      <c r="B31" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="82.5">
+      <c r="B32" s="30" t="s">
         <v>133</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="B15" s="1"/>
-    </row>
-    <row r="16" spans="1:2" ht="181.5">
-      <c r="A16" t="s">
-        <v>134</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="148.5">
-      <c r="B17" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="99">
-      <c r="A18" t="s">
-        <v>137</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="115.5">
-      <c r="A19" t="s">
-        <v>139</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="66">
-      <c r="A20" t="s">
-        <v>141</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="B21" s="1"/>
-    </row>
-    <row r="22" spans="1:2" ht="66">
-      <c r="A22" t="s">
-        <v>143</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="148.5">
-      <c r="A23" t="s">
-        <v>145</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="B24" s="1"/>
-    </row>
-    <row r="25" spans="1:2" ht="132">
-      <c r="A25" t="s">
-        <v>118</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="148.5">
-      <c r="A26" t="s">
-        <v>120</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="82.5">
-      <c r="B27" s="30" t="s">
-        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D345F707-1732-4B7B-AFF9-EC9F2B7688A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58207BC-7573-473A-9475-14D07664165C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -644,15 +644,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[인건비]
-주식보상비용 250백만 집행 (예산 외, 일회성)
-[지급수수료]
-HBR 누계 1,201백만(집행률 312%) — 8월 734백만(tax credit 매각 수수료 650백만, Ciro 성공보수 54백만 등), 9월 32백만
-합병 자문·평가 수수료 누계 557백만 집행 (1월 10백만, 4월 15백만, 7월 350백만, 8월 131백만, 9월 51백만)
-특허처리비 누계 103백만 초과 집행 (VVC 예산 누락 영향)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만 → 8월 152백만 → 9월 150백만
  - 4월: 한화 임대차계약 체결로 구조 변경
  - 7월: 티맥스수내타워 관리비 집행 시작 · 8~9월 동일 구조 유지</t>
@@ -829,6 +820,16 @@
   </si>
   <si>
     <t>4줄 기준 1번 시트가 626 → 680px, 한 페이지 한계 702px. 줄을 더 늘리려면 위쪽</t>
+  </si>
+  <si>
+    <t>[인건비]
+주식보상비용 250백만 집행 (예산 외, 일회성)
+[지급수수료]
+합병 자문·평가 수수료 누계 557백만 집행 (1월 10백만, 4월 15백만, 7월 350백만, 8월 131백만, 9월 51백만)
+특허처리비 누계 103백만 초과 집행 (VVC 예산 누락 영향)
+[법인 HBR]
+누계 1,201백만(집행률 312%) — 지급수수료 820백만(8월 tax credit 매각 수수료 650백만, Ciro 성공보수 54백만 등), 급여 231백만</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1673,7 +1674,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="222250" y="52140909"/>
+          <a:off x="222250" y="52350459"/>
           <a:ext cx="13001474" cy="4299556"/>
           <a:chOff x="179917" y="45603583"/>
           <a:chExt cx="13005707" cy="4344006"/>
@@ -2128,7 +2129,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="13256684" y="52265793"/>
+          <a:off x="13256684" y="52475343"/>
           <a:ext cx="6428158" cy="5367564"/>
           <a:chOff x="13260917" y="45497751"/>
           <a:chExt cx="6449325" cy="5420481"/>
@@ -3383,7 +3384,7 @@
         <v>8</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E58" s="24" t="s">
         <v>60</v>
@@ -3460,7 +3461,7 @@
       </c>
       <c r="E63" s="24"/>
     </row>
-    <row r="64" spans="1:5" ht="99">
+    <row r="64" spans="1:5" ht="115.5">
       <c r="A64" s="14" t="s">
         <v>6</v>
       </c>
@@ -3471,7 +3472,7 @@
         <v>8</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>107</v>
+        <v>156</v>
       </c>
       <c r="E64" s="24"/>
     </row>
@@ -3486,7 +3487,7 @@
         <v>9</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E65" s="24"/>
     </row>
@@ -3516,7 +3517,7 @@
         <v>8</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E67" s="24"/>
     </row>
@@ -3734,209 +3735,209 @@
   <sheetData>
     <row r="1" spans="1:2" s="28" customFormat="1">
       <c r="A1" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="29" t="s">
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="165">
-      <c r="A2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="148.5">
-      <c r="A3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="4" spans="1:2" ht="99">
+      <c r="A4" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="409.5">
-      <c r="A4" t="s">
+      <c r="B4" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="181.5">
+      <c r="A5" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="409.5">
-      <c r="A5" t="s">
+      <c r="B5" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:2" ht="181.5">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="B8" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
         <v>117</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="181.5">
-      <c r="B8" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="115.5">
-      <c r="A9" t="s">
+      <c r="B9" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:2" ht="181.5">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="B12" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="B13" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
         <v>120</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="132">
-      <c r="B12" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="181.5">
-      <c r="B13" s="1" t="s">
+      <c r="B14" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="115.5">
-      <c r="A14" t="s">
-        <v>121</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="82.5">
-      <c r="A15" t="s">
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
         <v>123</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="49.5">
-      <c r="A16" t="s">
-        <v>124</v>
-      </c>
       <c r="B16" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="B17" s="1"/>
     </row>
-    <row r="18" spans="1:2" ht="181.5">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="B19" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B18" s="1" t="s">
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="148.5">
-      <c r="B19" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="181.5">
-      <c r="A20" t="s">
+    <row r="21" spans="1:2">
+      <c r="B21" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="B22" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
         <v>127</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="181.5">
-      <c r="B21" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="198">
-      <c r="B22" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="165">
-      <c r="A23" t="s">
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
         <v>128</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="66">
-      <c r="A24" t="s">
+      <c r="B24" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="B25" s="1"/>
     </row>
-    <row r="26" spans="1:2" ht="181.5">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
+        <v>130</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
         <v>131</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="181.5">
-      <c r="A27" t="s">
-        <v>132</v>
-      </c>
-      <c r="B27" s="1" t="s">
+    <row r="28" spans="1:2">
+      <c r="B28" s="1" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="181.5">
-      <c r="B28" s="1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="B29" s="1"/>
     </row>
-    <row r="30" spans="1:2" ht="132">
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B30" s="1" t="s">
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" ht="148.5">
-      <c r="A31" t="s">
-        <v>116</v>
-      </c>
       <c r="B31" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="82.5">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="B32" s="30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58207BC-7573-473A-9475-14D07664165C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1BAF33-7F86-473E-BE65-AEBEBB507C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -825,10 +825,9 @@
     <t>[인건비]
 주식보상비용 250백만 집행 (예산 외, 일회성)
 [지급수수료]
+HBR 누계 820백만 — 8월 721백만(tax credit 매각 수수료 650백만, Ciro 성공보수 54백만 등), 9월 15백만
 합병 자문·평가 수수료 누계 557백만 집행 (1월 10백만, 4월 15백만, 7월 350백만, 8월 131백만, 9월 51백만)
-특허처리비 누계 103백만 초과 집행 (VVC 예산 누락 영향)
-[법인 HBR]
-누계 1,201백만(집행률 312%) — 지급수수료 820백만(8월 tax credit 매각 수수료 650백만, Ciro 성공보수 54백만 등), 급여 231백만</t>
+특허처리비 누계 103백만 초과 집행 (VVC 예산 누락 영향)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1674,7 +1673,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="222250" y="52350459"/>
+          <a:off x="222250" y="52140909"/>
           <a:ext cx="13001474" cy="4299556"/>
           <a:chOff x="179917" y="45603583"/>
           <a:chExt cx="13005707" cy="4344006"/>
@@ -2129,7 +2128,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="13256684" y="52475343"/>
+          <a:off x="13256684" y="52265793"/>
           <a:ext cx="6428158" cy="5367564"/>
           <a:chOff x="13260917" y="45497751"/>
           <a:chExt cx="6449325" cy="5420481"/>
@@ -3461,7 +3460,7 @@
       </c>
       <c r="E63" s="24"/>
     </row>
-    <row r="64" spans="1:5" ht="115.5">
+    <row r="64" spans="1:5" ht="99">
       <c r="A64" s="14" t="s">
         <v>6</v>
       </c>
